--- a/data/auto/sales/raw/kia_2026_retail_sales_by_model_market.xlsx
+++ b/data/auto/sales/raw/kia_2026_retail_sales_by_model_market.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hkmccloud.sharepoint.com/sites/o365m_KBAA/Shared Documents/AutoDocs/120.IR Site 관련/10.월판매마감/96.2026년/6월/홈페이지 첨부용/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hkmccloud.sharepoint.com/sites/o365m_KBAA/Shared Documents/AutoDocs/120.IR Site 관련/10.월판매마감/96.2026년/7월/홈페이지 첨부용/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D3C2397-955A-4CB7-8A13-3FB034F08A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="8_{7274A7BC-474D-4926-811C-A87BF30D5709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F80349BD-30CF-46E3-BB09-83CA09C4F304}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="891" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2253,11 +2253,11 @@
       <c r="F6" s="19"/>
       <c r="G6" s="74">
         <f>Jan!G6+Feb!G6+Mar!G6+Apr!G6+May!G6+June!G6+July!G6+Aug!G6+Sep!G6+Oct!G6+Nov!G6+Dec!G6</f>
-        <v>70604</v>
+        <v>84335</v>
       </c>
       <c r="H6" s="75">
         <f>Jan!H6+Feb!H6+Mar!H6+Apr!H6+May!H6+June!H6+July!H6+Aug!H6+Sep!H6+Oct!H6+Nov!H6+Dec!H6</f>
-        <v>11995</v>
+        <v>15403</v>
       </c>
       <c r="I6" s="76">
         <f>Jan!I6+Feb!I6+Mar!I6+Apr!I6+May!I6+June!I6+July!I6+Aug!I6+Sep!I6+Oct!I6+Nov!I6+Dec!I6</f>
@@ -2273,27 +2273,27 @@
       </c>
       <c r="L6" s="77">
         <f>Jan!L6+Feb!L6+Mar!L6+Apr!L6+May!L6+June!L6+July!L6+Aug!L6+Sep!L6+Oct!L6+Nov!L6+Dec!L6</f>
-        <v>32779</v>
+        <v>38066</v>
       </c>
       <c r="M6" s="77">
         <f>Jan!M6+Feb!M6+Mar!M6+Apr!M6+May!M6+June!M6+July!M6+Aug!M6+Sep!M6+Oct!M6+Nov!M6+Dec!M6</f>
-        <v>519</v>
+        <v>1028</v>
       </c>
       <c r="N6" s="77">
         <f>Jan!N6+Feb!N6+Mar!N6+Apr!N6+May!N6+June!N6+July!N6+Aug!N6+Sep!N6+Oct!N6+Nov!N6+Dec!N6</f>
-        <v>10251</v>
+        <v>12331</v>
       </c>
       <c r="O6" s="77">
         <f>Jan!O6+Feb!O6+Mar!O6+Apr!O6+May!O6+June!O6+July!O6+Aug!O6+Sep!O6+Oct!O6+Nov!O6+Dec!O6</f>
-        <v>4057</v>
+        <v>4778</v>
       </c>
       <c r="P6" s="77">
         <f>Jan!P6+Feb!P6+Mar!P6+Apr!P6+May!P6+June!P6+July!P6+Aug!P6+Sep!P6+Oct!P6+Nov!P6+Dec!P6</f>
-        <v>6628</v>
+        <v>7744</v>
       </c>
       <c r="Q6" s="77">
         <f>Jan!Q6+Feb!Q6+Mar!Q6+Apr!Q6+May!Q6+June!Q6+July!Q6+Aug!Q6+Sep!Q6+Oct!Q6+Nov!Q6+Dec!Q6</f>
-        <v>4375</v>
+        <v>4985</v>
       </c>
       <c r="R6" s="77">
         <f>Jan!R6+Feb!R6+Mar!R6+Apr!R6+May!R6+June!R6+July!R6+Aug!R6+Sep!R6+Oct!R6+Nov!R6+Dec!R6</f>
@@ -2314,11 +2314,11 @@
       <c r="F7" s="19"/>
       <c r="G7" s="79">
         <f>Jan!G7+Feb!G7+Mar!G7+Apr!G7+May!G7+June!G7+July!G7+Aug!G7+Sep!G7+Oct!G7+Nov!G7+Dec!G7</f>
-        <v>18662</v>
+        <v>22506</v>
       </c>
       <c r="H7" s="80">
         <f>Jan!H7+Feb!H7+Mar!H7+Apr!H7+May!H7+June!H7+July!H7+Aug!H7+Sep!H7+Oct!H7+Nov!H7+Dec!H7</f>
-        <v>18662</v>
+        <v>22506</v>
       </c>
       <c r="I7" s="81">
         <f>Jan!I7+Feb!I7+Mar!I7+Apr!I7+May!I7+June!I7+July!I7+Aug!I7+Sep!I7+Oct!I7+Nov!I7+Dec!I7</f>
@@ -2375,11 +2375,11 @@
       <c r="F8" s="19"/>
       <c r="G8" s="79">
         <f>Jan!G8+Feb!G8+Mar!G8+Apr!G8+May!G8+June!G8+July!G8+Aug!G8+Sep!G8+Oct!G8+Nov!G8+Dec!G8</f>
-        <v>5718</v>
+        <v>7052</v>
       </c>
       <c r="H8" s="80">
         <f>Jan!H8+Feb!H8+Mar!H8+Apr!H8+May!H8+June!H8+July!H8+Aug!H8+Sep!H8+Oct!H8+Nov!H8+Dec!H8</f>
-        <v>5718</v>
+        <v>7052</v>
       </c>
       <c r="I8" s="81">
         <f>Jan!I8+Feb!I8+Mar!I8+Apr!I8+May!I8+June!I8+July!I8+Aug!I8+Sep!I8+Oct!I8+Nov!I8+Dec!I8</f>
@@ -2436,7 +2436,7 @@
       <c r="F9" s="19"/>
       <c r="G9" s="79">
         <f>Jan!G9+Feb!G9+Mar!G9+Apr!G9+May!G9+June!G9+July!G9+Aug!G9+Sep!G9+Oct!G9+Nov!G9+Dec!G9</f>
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H9" s="80">
         <f>Jan!H9+Feb!H9+Mar!H9+Apr!H9+May!H9+June!H9+July!H9+Aug!H9+Sep!H9+Oct!H9+Nov!H9+Dec!H9</f>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="M9" s="82">
         <f>Jan!M9+Feb!M9+Mar!M9+Apr!M9+May!M9+June!M9+July!M9+Aug!M9+Sep!M9+Oct!M9+Nov!M9+Dec!M9</f>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N9" s="82">
         <f>Jan!N9+Feb!N9+Mar!N9+Apr!N9+May!N9+June!N9+July!N9+Aug!N9+Sep!N9+Oct!N9+Nov!N9+Dec!N9</f>
@@ -2497,15 +2497,15 @@
       <c r="F10" s="19"/>
       <c r="G10" s="79">
         <f>Jan!G10+Feb!G10+Mar!G10+Apr!G10+May!G10+June!G10+July!G10+Aug!G10+Sep!G10+Oct!G10+Nov!G10+Dec!G10</f>
-        <v>57074</v>
+        <v>66480</v>
       </c>
       <c r="H10" s="80">
         <f>Jan!H10+Feb!H10+Mar!H10+Apr!H10+May!H10+June!H10+July!H10+Aug!H10+Sep!H10+Oct!H10+Nov!H10+Dec!H10</f>
-        <v>15747</v>
+        <v>18109</v>
       </c>
       <c r="I10" s="81">
         <f>Jan!I10+Feb!I10+Mar!I10+Apr!I10+May!I10+June!I10+July!I10+Aug!I10+Sep!I10+Oct!I10+Nov!I10+Dec!I10</f>
-        <v>38394</v>
+        <v>45088</v>
       </c>
       <c r="J10" s="82">
         <f>Jan!J10+Feb!J10+Mar!J10+Apr!J10+May!J10+June!J10+July!J10+Aug!J10+Sep!J10+Oct!J10+Nov!J10+Dec!J10</f>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="M10" s="82">
         <f>Jan!M10+Feb!M10+Mar!M10+Apr!M10+May!M10+June!M10+July!M10+Aug!M10+Sep!M10+Oct!M10+Nov!M10+Dec!M10</f>
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N10" s="82">
         <f>Jan!N10+Feb!N10+Mar!N10+Apr!N10+May!N10+June!N10+July!N10+Aug!N10+Sep!N10+Oct!N10+Nov!N10+Dec!N10</f>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="O10" s="82">
         <f>Jan!O10+Feb!O10+Mar!O10+Apr!O10+May!O10+June!O10+July!O10+Aug!O10+Sep!O10+Oct!O10+Nov!O10+Dec!O10</f>
-        <v>2863</v>
+        <v>3207</v>
       </c>
       <c r="P10" s="82">
         <f>Jan!P10+Feb!P10+Mar!P10+Apr!P10+May!P10+June!P10+July!P10+Aug!P10+Sep!P10+Oct!P10+Nov!P10+Dec!P10</f>
@@ -2558,11 +2558,11 @@
       <c r="F11" s="19"/>
       <c r="G11" s="79">
         <f>Jan!G11+Feb!G11+Mar!G11+Apr!G11+May!G11+June!G11+July!G11+Aug!G11+Sep!G11+Oct!G11+Nov!G11+Dec!G11</f>
-        <v>11390</v>
+        <v>12711</v>
       </c>
       <c r="H11" s="80">
         <f>Jan!H11+Feb!H11+Mar!H11+Apr!H11+May!H11+June!H11+July!H11+Aug!H11+Sep!H11+Oct!H11+Nov!H11+Dec!H11</f>
-        <v>10965</v>
+        <v>12224</v>
       </c>
       <c r="I11" s="81">
         <f>Jan!I11+Feb!I11+Mar!I11+Apr!I11+May!I11+June!I11+July!I11+Aug!I11+Sep!I11+Oct!I11+Nov!I11+Dec!I11</f>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="M11" s="82">
         <f>Jan!M11+Feb!M11+Mar!M11+Apr!M11+May!M11+June!M11+July!M11+Aug!M11+Sep!M11+Oct!M11+Nov!M11+Dec!M11</f>
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="N11" s="82">
         <f>Jan!N11+Feb!N11+Mar!N11+Apr!N11+May!N11+June!N11+July!N11+Aug!N11+Sep!N11+Oct!N11+Nov!N11+Dec!N11</f>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="O11" s="82">
         <f>Jan!O11+Feb!O11+Mar!O11+Apr!O11+May!O11+June!O11+July!O11+Aug!O11+Sep!O11+Oct!O11+Nov!O11+Dec!O11</f>
-        <v>369</v>
+        <v>421</v>
       </c>
       <c r="P11" s="82">
         <f>Jan!P11+Feb!P11+Mar!P11+Apr!P11+May!P11+June!P11+July!P11+Aug!P11+Sep!P11+Oct!P11+Nov!P11+Dec!P11</f>
@@ -2619,11 +2619,11 @@
       <c r="F12" s="19"/>
       <c r="G12" s="79">
         <f>Jan!G12+Feb!G12+Mar!G12+Apr!G12+May!G12+June!G12+July!G12+Aug!G12+Sep!G12+Oct!G12+Nov!G12+Dec!G12</f>
-        <v>738</v>
+        <v>796</v>
       </c>
       <c r="H12" s="80">
         <f>Jan!H12+Feb!H12+Mar!H12+Apr!H12+May!H12+June!H12+July!H12+Aug!H12+Sep!H12+Oct!H12+Nov!H12+Dec!H12</f>
-        <v>734</v>
+        <v>791</v>
       </c>
       <c r="I12" s="81">
         <f>Jan!I12+Feb!I12+Mar!I12+Apr!I12+May!I12+June!I12+July!I12+Aug!I12+Sep!I12+Oct!I12+Nov!I12+Dec!I12</f>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="M12" s="82">
         <f>Jan!M12+Feb!M12+Mar!M12+Apr!M12+May!M12+June!M12+July!M12+Aug!M12+Sep!M12+Oct!M12+Nov!M12+Dec!M12</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N12" s="82">
         <f>Jan!N12+Feb!N12+Mar!N12+Apr!N12+May!N12+June!N12+July!N12+Aug!N12+Sep!N12+Oct!N12+Nov!N12+Dec!N12</f>
@@ -2680,7 +2680,7 @@
       <c r="F13" s="19"/>
       <c r="G13" s="79">
         <f>Jan!G13+Feb!G13+Mar!G13+Apr!G13+May!G13+June!G13+July!G13+Aug!G13+Sep!G13+Oct!G13+Nov!G13+Dec!G13</f>
-        <v>38695</v>
+        <v>45006</v>
       </c>
       <c r="H13" s="80">
         <f>Jan!H13+Feb!H13+Mar!H13+Apr!H13+May!H13+June!H13+July!H13+Aug!H13+Sep!H13+Oct!H13+Nov!H13+Dec!H13</f>
@@ -2700,27 +2700,27 @@
       </c>
       <c r="L13" s="82">
         <f>Jan!L13+Feb!L13+Mar!L13+Apr!L13+May!L13+June!L13+July!L13+Aug!L13+Sep!L13+Oct!L13+Nov!L13+Dec!L13</f>
-        <v>30527</v>
+        <v>35042</v>
       </c>
       <c r="M13" s="82">
         <f>Jan!M13+Feb!M13+Mar!M13+Apr!M13+May!M13+June!M13+July!M13+Aug!M13+Sep!M13+Oct!M13+Nov!M13+Dec!M13</f>
-        <v>493</v>
+        <v>578</v>
       </c>
       <c r="N13" s="82">
         <f>Jan!N13+Feb!N13+Mar!N13+Apr!N13+May!N13+June!N13+July!N13+Aug!N13+Sep!N13+Oct!N13+Nov!N13+Dec!N13</f>
-        <v>2748</v>
+        <v>3166</v>
       </c>
       <c r="O13" s="82">
         <f>Jan!O13+Feb!O13+Mar!O13+Apr!O13+May!O13+June!O13+July!O13+Aug!O13+Sep!O13+Oct!O13+Nov!O13+Dec!O13</f>
-        <v>156</v>
+        <v>551</v>
       </c>
       <c r="P13" s="82">
         <f>Jan!P13+Feb!P13+Mar!P13+Apr!P13+May!P13+June!P13+July!P13+Aug!P13+Sep!P13+Oct!P13+Nov!P13+Dec!P13</f>
-        <v>447</v>
+        <v>515</v>
       </c>
       <c r="Q13" s="82">
         <f>Jan!Q13+Feb!Q13+Mar!Q13+Apr!Q13+May!Q13+June!Q13+July!Q13+Aug!Q13+Sep!Q13+Oct!Q13+Nov!Q13+Dec!Q13</f>
-        <v>4324</v>
+        <v>5154</v>
       </c>
       <c r="R13" s="82">
         <f>Jan!R13+Feb!R13+Mar!R13+Apr!R13+May!R13+June!R13+July!R13+Aug!R13+Sep!R13+Oct!R13+Nov!R13+Dec!R13</f>
@@ -2741,19 +2741,19 @@
       <c r="F14" s="19"/>
       <c r="G14" s="79">
         <f>Jan!G14+Feb!G14+Mar!G14+Apr!G14+May!G14+June!G14+July!G14+Aug!G14+Sep!G14+Oct!G14+Nov!G14+Dec!G14</f>
-        <v>73010</v>
+        <v>92458</v>
       </c>
       <c r="H14" s="80">
         <f>Jan!H14+Feb!H14+Mar!H14+Apr!H14+May!H14+June!H14+July!H14+Aug!H14+Sep!H14+Oct!H14+Nov!H14+Dec!H14</f>
-        <v>23545</v>
+        <v>30972</v>
       </c>
       <c r="I14" s="81">
         <f>Jan!I14+Feb!I14+Mar!I14+Apr!I14+May!I14+June!I14+July!I14+Aug!I14+Sep!I14+Oct!I14+Nov!I14+Dec!I14</f>
-        <v>32504</v>
+        <v>41311</v>
       </c>
       <c r="J14" s="82">
         <f>Jan!J14+Feb!J14+Mar!J14+Apr!J14+May!J14+June!J14+July!J14+Aug!J14+Sep!J14+Oct!J14+Nov!J14+Dec!J14</f>
-        <v>8361</v>
+        <v>10074</v>
       </c>
       <c r="K14" s="82">
         <f>Jan!K14+Feb!K14+Mar!K14+Apr!K14+May!K14+June!K14+July!K14+Aug!K14+Sep!K14+Oct!K14+Nov!K14+Dec!K14</f>
@@ -2761,19 +2761,19 @@
       </c>
       <c r="L14" s="82">
         <f>Jan!L14+Feb!L14+Mar!L14+Apr!L14+May!L14+June!L14+July!L14+Aug!L14+Sep!L14+Oct!L14+Nov!L14+Dec!L14</f>
-        <v>833</v>
+        <v>1462</v>
       </c>
       <c r="M14" s="82">
         <f>Jan!M14+Feb!M14+Mar!M14+Apr!M14+May!M14+June!M14+July!M14+Aug!M14+Sep!M14+Oct!M14+Nov!M14+Dec!M14</f>
-        <v>560</v>
+        <v>596</v>
       </c>
       <c r="N14" s="82">
         <f>Jan!N14+Feb!N14+Mar!N14+Apr!N14+May!N14+June!N14+July!N14+Aug!N14+Sep!N14+Oct!N14+Nov!N14+Dec!N14</f>
-        <v>1993</v>
+        <v>2387</v>
       </c>
       <c r="O14" s="82">
         <f>Jan!O14+Feb!O14+Mar!O14+Apr!O14+May!O14+June!O14+July!O14+Aug!O14+Sep!O14+Oct!O14+Nov!O14+Dec!O14</f>
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="P14" s="82">
         <f>Jan!P14+Feb!P14+Mar!P14+Apr!P14+May!P14+June!P14+July!P14+Aug!P14+Sep!P14+Oct!P14+Nov!P14+Dec!P14</f>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="Q14" s="82">
         <f>Jan!Q14+Feb!Q14+Mar!Q14+Apr!Q14+May!Q14+June!Q14+July!Q14+Aug!Q14+Sep!Q14+Oct!Q14+Nov!Q14+Dec!Q14</f>
-        <v>5019</v>
+        <v>5457</v>
       </c>
       <c r="R14" s="82">
         <f>Jan!R14+Feb!R14+Mar!R14+Apr!R14+May!R14+June!R14+July!R14+Aug!R14+Sep!R14+Oct!R14+Nov!R14+Dec!R14</f>
@@ -2802,7 +2802,7 @@
       <c r="F15" s="19"/>
       <c r="G15" s="79">
         <f>Jan!G15+Feb!G15+Mar!G15+Apr!G15+May!G15+June!G15+July!G15+Aug!G15+Sep!G15+Oct!G15+Nov!G15+Dec!G15</f>
-        <v>3710</v>
+        <v>3732</v>
       </c>
       <c r="H15" s="80">
         <f>Jan!H15+Feb!H15+Mar!H15+Apr!H15+May!H15+June!H15+July!H15+Aug!H15+Sep!H15+Oct!H15+Nov!H15+Dec!H15</f>
@@ -2826,11 +2826,11 @@
       </c>
       <c r="M15" s="82">
         <f>Jan!M15+Feb!M15+Mar!M15+Apr!M15+May!M15+June!M15+July!M15+Aug!M15+Sep!M15+Oct!M15+Nov!M15+Dec!M15</f>
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="N15" s="82">
         <f>Jan!N15+Feb!N15+Mar!N15+Apr!N15+May!N15+June!N15+July!N15+Aug!N15+Sep!N15+Oct!N15+Nov!N15+Dec!N15</f>
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="O15" s="82">
         <f>Jan!O15+Feb!O15+Mar!O15+Apr!O15+May!O15+June!O15+July!O15+Aug!O15+Sep!O15+Oct!O15+Nov!O15+Dec!O15</f>
@@ -2863,47 +2863,47 @@
       <c r="F16" s="19"/>
       <c r="G16" s="79">
         <f>Jan!G16+Feb!G16+Mar!G16+Apr!G16+May!G16+June!G16+July!G16+Aug!G16+Sep!G16+Oct!G16+Nov!G16+Dec!G16</f>
-        <v>45850</v>
+        <v>52377</v>
       </c>
       <c r="H16" s="80">
         <f>Jan!H16+Feb!H16+Mar!H16+Apr!H16+May!H16+June!H16+July!H16+Aug!H16+Sep!H16+Oct!H16+Nov!H16+Dec!H16</f>
-        <v>8450</v>
+        <v>9757</v>
       </c>
       <c r="I16" s="81">
         <f>Jan!I16+Feb!I16+Mar!I16+Apr!I16+May!I16+June!I16+July!I16+Aug!I16+Sep!I16+Oct!I16+Nov!I16+Dec!I16</f>
-        <v>12114</v>
+        <v>13495</v>
       </c>
       <c r="J16" s="82">
         <f>Jan!J16+Feb!J16+Mar!J16+Apr!J16+May!J16+June!J16+July!J16+Aug!J16+Sep!J16+Oct!J16+Nov!J16+Dec!J16</f>
-        <v>2181</v>
+        <v>2536</v>
       </c>
       <c r="K16" s="82">
         <f>Jan!K16+Feb!K16+Mar!K16+Apr!K16+May!K16+June!K16+July!K16+Aug!K16+Sep!K16+Oct!K16+Nov!K16+Dec!K16</f>
-        <v>384</v>
+        <v>435</v>
       </c>
       <c r="L16" s="82">
         <f>Jan!L16+Feb!L16+Mar!L16+Apr!L16+May!L16+June!L16+July!L16+Aug!L16+Sep!L16+Oct!L16+Nov!L16+Dec!L16</f>
-        <v>18270</v>
+        <v>20778</v>
       </c>
       <c r="M16" s="82">
         <f>Jan!M16+Feb!M16+Mar!M16+Apr!M16+May!M16+June!M16+July!M16+Aug!M16+Sep!M16+Oct!M16+Nov!M16+Dec!M16</f>
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="N16" s="82">
         <f>Jan!N16+Feb!N16+Mar!N16+Apr!N16+May!N16+June!N16+July!N16+Aug!N16+Sep!N16+Oct!N16+Nov!N16+Dec!N16</f>
-        <v>1839</v>
+        <v>2388</v>
       </c>
       <c r="O16" s="82">
         <f>Jan!O16+Feb!O16+Mar!O16+Apr!O16+May!O16+June!O16+July!O16+Aug!O16+Sep!O16+Oct!O16+Nov!O16+Dec!O16</f>
-        <v>1930</v>
+        <v>2194</v>
       </c>
       <c r="P16" s="82">
         <f>Jan!P16+Feb!P16+Mar!P16+Apr!P16+May!P16+June!P16+July!P16+Aug!P16+Sep!P16+Oct!P16+Nov!P16+Dec!P16</f>
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="Q16" s="82">
         <f>Jan!Q16+Feb!Q16+Mar!Q16+Apr!Q16+May!Q16+June!Q16+July!Q16+Aug!Q16+Sep!Q16+Oct!Q16+Nov!Q16+Dec!Q16</f>
-        <v>454</v>
+        <v>522</v>
       </c>
       <c r="R16" s="82">
         <f>Jan!R16+Feb!R16+Mar!R16+Apr!R16+May!R16+June!R16+July!R16+Aug!R16+Sep!R16+Oct!R16+Nov!R16+Dec!R16</f>
@@ -2924,7 +2924,7 @@
       <c r="F17" s="19"/>
       <c r="G17" s="79">
         <f>Jan!G17+Feb!G17+Mar!G17+Apr!G17+May!G17+June!G17+July!G17+Aug!G17+Sep!G17+Oct!G17+Nov!G17+Dec!G17</f>
-        <v>7722</v>
+        <v>9485</v>
       </c>
       <c r="H17" s="80">
         <f>Jan!H17+Feb!H17+Mar!H17+Apr!H17+May!H17+June!H17+July!H17+Aug!H17+Sep!H17+Oct!H17+Nov!H17+Dec!H17</f>
@@ -2932,11 +2932,11 @@
       </c>
       <c r="I17" s="81">
         <f>Jan!I17+Feb!I17+Mar!I17+Apr!I17+May!I17+June!I17+July!I17+Aug!I17+Sep!I17+Oct!I17+Nov!I17+Dec!I17</f>
-        <v>1653</v>
+        <v>1994</v>
       </c>
       <c r="J17" s="82">
         <f>Jan!J17+Feb!J17+Mar!J17+Apr!J17+May!J17+June!J17+July!J17+Aug!J17+Sep!J17+Oct!J17+Nov!J17+Dec!J17</f>
-        <v>3268</v>
+        <v>3829</v>
       </c>
       <c r="K17" s="82">
         <f>Jan!K17+Feb!K17+Mar!K17+Apr!K17+May!K17+June!K17+July!K17+Aug!K17+Sep!K17+Oct!K17+Nov!K17+Dec!K17</f>
@@ -2944,15 +2944,15 @@
       </c>
       <c r="L17" s="82">
         <f>Jan!L17+Feb!L17+Mar!L17+Apr!L17+May!L17+June!L17+July!L17+Aug!L17+Sep!L17+Oct!L17+Nov!L17+Dec!L17</f>
-        <v>2693</v>
+        <v>3388</v>
       </c>
       <c r="M17" s="82">
         <f>Jan!M17+Feb!M17+Mar!M17+Apr!M17+May!M17+June!M17+July!M17+Aug!M17+Sep!M17+Oct!M17+Nov!M17+Dec!M17</f>
-        <v>56</v>
+        <v>219</v>
       </c>
       <c r="N17" s="82">
         <f>Jan!N17+Feb!N17+Mar!N17+Apr!N17+May!N17+June!N17+July!N17+Aug!N17+Sep!N17+Oct!N17+Nov!N17+Dec!N17</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O17" s="82">
         <f>Jan!O17+Feb!O17+Mar!O17+Apr!O17+May!O17+June!O17+July!O17+Aug!O17+Sep!O17+Oct!O17+Nov!O17+Dec!O17</f>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="P17" s="82">
         <f>Jan!P17+Feb!P17+Mar!P17+Apr!P17+May!P17+June!P17+July!P17+Aug!P17+Sep!P17+Oct!P17+Nov!P17+Dec!P17</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q17" s="82">
         <f>Jan!Q17+Feb!Q17+Mar!Q17+Apr!Q17+May!Q17+June!Q17+July!Q17+Aug!Q17+Sep!Q17+Oct!Q17+Nov!Q17+Dec!Q17</f>
@@ -2985,11 +2985,11 @@
       <c r="F18" s="19"/>
       <c r="G18" s="79">
         <f>Jan!G18+Feb!G18+Mar!G18+Apr!G18+May!G18+June!G18+July!G18+Aug!G18+Sep!G18+Oct!G18+Nov!G18+Dec!G18</f>
-        <v>51177</v>
+        <v>61587</v>
       </c>
       <c r="H18" s="80">
         <f>Jan!H18+Feb!H18+Mar!H18+Apr!H18+May!H18+June!H18+July!H18+Aug!H18+Sep!H18+Oct!H18+Nov!H18+Dec!H18</f>
-        <v>18431</v>
+        <v>21898</v>
       </c>
       <c r="I18" s="81">
         <f>Jan!I18+Feb!I18+Mar!I18+Apr!I18+May!I18+June!I18+July!I18+Aug!I18+Sep!I18+Oct!I18+Nov!I18+Dec!I18</f>
@@ -3005,27 +3005,27 @@
       </c>
       <c r="L18" s="82">
         <f>Jan!L18+Feb!L18+Mar!L18+Apr!L18+May!L18+June!L18+July!L18+Aug!L18+Sep!L18+Oct!L18+Nov!L18+Dec!L18</f>
-        <v>27121</v>
+        <v>32551</v>
       </c>
       <c r="M18" s="82">
         <f>Jan!M18+Feb!M18+Mar!M18+Apr!M18+May!M18+June!M18+July!M18+Aug!M18+Sep!M18+Oct!M18+Nov!M18+Dec!M18</f>
-        <v>1282</v>
+        <v>1696</v>
       </c>
       <c r="N18" s="82">
         <f>Jan!N18+Feb!N18+Mar!N18+Apr!N18+May!N18+June!N18+July!N18+Aug!N18+Sep!N18+Oct!N18+Nov!N18+Dec!N18</f>
-        <v>256</v>
+        <v>311</v>
       </c>
       <c r="O18" s="82">
         <f>Jan!O18+Feb!O18+Mar!O18+Apr!O18+May!O18+June!O18+July!O18+Aug!O18+Sep!O18+Oct!O18+Nov!O18+Dec!O18</f>
-        <v>673</v>
+        <v>846</v>
       </c>
       <c r="P18" s="82">
         <f>Jan!P18+Feb!P18+Mar!P18+Apr!P18+May!P18+June!P18+July!P18+Aug!P18+Sep!P18+Oct!P18+Nov!P18+Dec!P18</f>
-        <v>275</v>
+        <v>319</v>
       </c>
       <c r="Q18" s="82">
         <f>Jan!Q18+Feb!Q18+Mar!Q18+Apr!Q18+May!Q18+June!Q18+July!Q18+Aug!Q18+Sep!Q18+Oct!Q18+Nov!Q18+Dec!Q18</f>
-        <v>3139</v>
+        <v>3966</v>
       </c>
       <c r="R18" s="82">
         <f>Jan!R18+Feb!R18+Mar!R18+Apr!R18+May!R18+June!R18+July!R18+Aug!R18+Sep!R18+Oct!R18+Nov!R18+Dec!R18</f>
@@ -3046,11 +3046,11 @@
       <c r="F19" s="19"/>
       <c r="G19" s="79">
         <f>Jan!G19+Feb!G19+Mar!G19+Apr!G19+May!G19+June!G19+July!G19+Aug!G19+Sep!G19+Oct!G19+Nov!G19+Dec!G19</f>
-        <v>10041</v>
+        <v>11380</v>
       </c>
       <c r="H19" s="80">
         <f>Jan!H19+Feb!H19+Mar!H19+Apr!H19+May!H19+June!H19+July!H19+Aug!H19+Sep!H19+Oct!H19+Nov!H19+Dec!H19</f>
-        <v>7726</v>
+        <v>8575</v>
       </c>
       <c r="I19" s="81">
         <f>Jan!I19+Feb!I19+Mar!I19+Apr!I19+May!I19+June!I19+July!I19+Aug!I19+Sep!I19+Oct!I19+Nov!I19+Dec!I19</f>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="J19" s="82">
         <f>Jan!J19+Feb!J19+Mar!J19+Apr!J19+May!J19+June!J19+July!J19+Aug!J19+Sep!J19+Oct!J19+Nov!J19+Dec!J19</f>
-        <v>1284</v>
+        <v>1448</v>
       </c>
       <c r="K19" s="82">
         <f>Jan!K19+Feb!K19+Mar!K19+Apr!K19+May!K19+June!K19+July!K19+Aug!K19+Sep!K19+Oct!K19+Nov!K19+Dec!K19</f>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="L19" s="82">
         <f>Jan!L19+Feb!L19+Mar!L19+Apr!L19+May!L19+June!L19+July!L19+Aug!L19+Sep!L19+Oct!L19+Nov!L19+Dec!L19</f>
-        <v>726</v>
+        <v>1019</v>
       </c>
       <c r="M19" s="82">
         <f>Jan!M19+Feb!M19+Mar!M19+Apr!M19+May!M19+June!M19+July!M19+Aug!M19+Sep!M19+Oct!M19+Nov!M19+Dec!M19</f>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="Q19" s="82">
         <f>Jan!Q19+Feb!Q19+Mar!Q19+Apr!Q19+May!Q19+June!Q19+July!Q19+Aug!Q19+Sep!Q19+Oct!Q19+Nov!Q19+Dec!Q19</f>
-        <v>301</v>
+        <v>334</v>
       </c>
       <c r="R19" s="82">
         <f>Jan!R19+Feb!R19+Mar!R19+Apr!R19+May!R19+June!R19+July!R19+Aug!R19+Sep!R19+Oct!R19+Nov!R19+Dec!R19</f>
@@ -3107,11 +3107,11 @@
       <c r="F20" s="19"/>
       <c r="G20" s="79">
         <f>Jan!G20+Feb!G20+Mar!G20+Apr!G20+May!G20+June!G20+July!G20+Aug!G20+Sep!G20+Oct!G20+Nov!G20+Dec!G20</f>
-        <v>29950</v>
+        <v>36110</v>
       </c>
       <c r="H20" s="80">
         <f>Jan!H20+Feb!H20+Mar!H20+Apr!H20+May!H20+June!H20+July!H20+Aug!H20+Sep!H20+Oct!H20+Nov!H20+Dec!H20</f>
-        <v>15965</v>
+        <v>19399</v>
       </c>
       <c r="I20" s="81">
         <f>Jan!I20+Feb!I20+Mar!I20+Apr!I20+May!I20+June!I20+July!I20+Aug!I20+Sep!I20+Oct!I20+Nov!I20+Dec!I20</f>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="J20" s="82">
         <f>Jan!J20+Feb!J20+Mar!J20+Apr!J20+May!J20+June!J20+July!J20+Aug!J20+Sep!J20+Oct!J20+Nov!J20+Dec!J20</f>
-        <v>587</v>
+        <v>885</v>
       </c>
       <c r="K20" s="82">
         <f>Jan!K20+Feb!K20+Mar!K20+Apr!K20+May!K20+June!K20+July!K20+Aug!K20+Sep!K20+Oct!K20+Nov!K20+Dec!K20</f>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="L20" s="82">
         <f>Jan!L20+Feb!L20+Mar!L20+Apr!L20+May!L20+June!L20+July!L20+Aug!L20+Sep!L20+Oct!L20+Nov!L20+Dec!L20</f>
-        <v>13393</v>
+        <v>15818</v>
       </c>
       <c r="M20" s="82">
         <f>Jan!M20+Feb!M20+Mar!M20+Apr!M20+May!M20+June!M20+July!M20+Aug!M20+Sep!M20+Oct!M20+Nov!M20+Dec!M20</f>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="P20" s="82">
         <f>Jan!P20+Feb!P20+Mar!P20+Apr!P20+May!P20+June!P20+July!P20+Aug!P20+Sep!P20+Oct!P20+Nov!P20+Dec!P20</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q20" s="82">
         <f>Jan!Q20+Feb!Q20+Mar!Q20+Apr!Q20+May!Q20+June!Q20+July!Q20+Aug!Q20+Sep!Q20+Oct!Q20+Nov!Q20+Dec!Q20</f>
@@ -3168,11 +3168,11 @@
       <c r="F21" s="19"/>
       <c r="G21" s="79">
         <f>Jan!G21+Feb!G21+Mar!G21+Apr!G21+May!G21+June!G21+July!G21+Aug!G21+Sep!G21+Oct!G21+Nov!G21+Dec!G21</f>
-        <v>10966</v>
+        <v>12771</v>
       </c>
       <c r="H21" s="80">
         <f>Jan!H21+Feb!H21+Mar!H21+Apr!H21+May!H21+June!H21+July!H21+Aug!H21+Sep!H21+Oct!H21+Nov!H21+Dec!H21</f>
-        <v>5297</v>
+        <v>6367</v>
       </c>
       <c r="I21" s="81">
         <f>Jan!I21+Feb!I21+Mar!I21+Apr!I21+May!I21+June!I21+July!I21+Aug!I21+Sep!I21+Oct!I21+Nov!I21+Dec!I21</f>
@@ -3188,15 +3188,15 @@
       </c>
       <c r="L21" s="82">
         <f>Jan!L21+Feb!L21+Mar!L21+Apr!L21+May!L21+June!L21+July!L21+Aug!L21+Sep!L21+Oct!L21+Nov!L21+Dec!L21</f>
-        <v>5086</v>
+        <v>5782</v>
       </c>
       <c r="M21" s="82">
         <f>Jan!M21+Feb!M21+Mar!M21+Apr!M21+May!M21+June!M21+July!M21+Aug!M21+Sep!M21+Oct!M21+Nov!M21+Dec!M21</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N21" s="82">
         <f>Jan!N21+Feb!N21+Mar!N21+Apr!N21+May!N21+June!N21+July!N21+Aug!N21+Sep!N21+Oct!N21+Nov!N21+Dec!N21</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O21" s="82">
         <f>Jan!O21+Feb!O21+Mar!O21+Apr!O21+May!O21+June!O21+July!O21+Aug!O21+Sep!O21+Oct!O21+Nov!O21+Dec!O21</f>
@@ -3204,11 +3204,11 @@
       </c>
       <c r="P21" s="82">
         <f>Jan!P21+Feb!P21+Mar!P21+Apr!P21+May!P21+June!P21+July!P21+Aug!P21+Sep!P21+Oct!P21+Nov!P21+Dec!P21</f>
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="Q21" s="82">
         <f>Jan!Q21+Feb!Q21+Mar!Q21+Apr!Q21+May!Q21+June!Q21+July!Q21+Aug!Q21+Sep!Q21+Oct!Q21+Nov!Q21+Dec!Q21</f>
-        <v>314</v>
+        <v>343</v>
       </c>
       <c r="R21" s="82">
         <f>Jan!R21+Feb!R21+Mar!R21+Apr!R21+May!R21+June!R21+July!R21+Aug!R21+Sep!R21+Oct!R21+Nov!R21+Dec!R21</f>
@@ -3229,11 +3229,11 @@
       <c r="F22" s="19"/>
       <c r="G22" s="79">
         <f>Jan!G22+Feb!G22+Mar!G22+Apr!G22+May!G22+June!G22+July!G22+Aug!G22+Sep!G22+Oct!G22+Nov!G22+Dec!G22</f>
-        <v>8365</v>
+        <v>9873</v>
       </c>
       <c r="H22" s="80">
         <f>Jan!H22+Feb!H22+Mar!H22+Apr!H22+May!H22+June!H22+July!H22+Aug!H22+Sep!H22+Oct!H22+Nov!H22+Dec!H22</f>
-        <v>1552</v>
+        <v>1994</v>
       </c>
       <c r="I22" s="81">
         <f>Jan!I22+Feb!I22+Mar!I22+Apr!I22+May!I22+June!I22+July!I22+Aug!I22+Sep!I22+Oct!I22+Nov!I22+Dec!I22</f>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="J22" s="82">
         <f>Jan!J22+Feb!J22+Mar!J22+Apr!J22+May!J22+June!J22+July!J22+Aug!J22+Sep!J22+Oct!J22+Nov!J22+Dec!J22</f>
-        <v>1716</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="82">
         <f>Jan!K22+Feb!K22+Mar!K22+Apr!K22+May!K22+June!K22+July!K22+Aug!K22+Sep!K22+Oct!K22+Nov!K22+Dec!K22</f>
@@ -3249,31 +3249,31 @@
       </c>
       <c r="L22" s="82">
         <f>Jan!L22+Feb!L22+Mar!L22+Apr!L22+May!L22+June!L22+July!L22+Aug!L22+Sep!L22+Oct!L22+Nov!L22+Dec!L22</f>
-        <v>4826</v>
+        <v>5497</v>
       </c>
       <c r="M22" s="82">
         <f>Jan!M22+Feb!M22+Mar!M22+Apr!M22+May!M22+June!M22+July!M22+Aug!M22+Sep!M22+Oct!M22+Nov!M22+Dec!M22</f>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="N22" s="82">
         <f>Jan!N22+Feb!N22+Mar!N22+Apr!N22+May!N22+June!N22+July!N22+Aug!N22+Sep!N22+Oct!N22+Nov!N22+Dec!N22</f>
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="O22" s="82">
         <f>Jan!O22+Feb!O22+Mar!O22+Apr!O22+May!O22+June!O22+July!O22+Aug!O22+Sep!O22+Oct!O22+Nov!O22+Dec!O22</f>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P22" s="82">
         <f>Jan!P22+Feb!P22+Mar!P22+Apr!P22+May!P22+June!P22+July!P22+Aug!P22+Sep!P22+Oct!P22+Nov!P22+Dec!P22</f>
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q22" s="82">
         <f>Jan!Q22+Feb!Q22+Mar!Q22+Apr!Q22+May!Q22+June!Q22+July!Q22+Aug!Q22+Sep!Q22+Oct!Q22+Nov!Q22+Dec!Q22</f>
-        <v>159</v>
+        <v>225</v>
       </c>
       <c r="R22" s="82">
         <f>Jan!R22+Feb!R22+Mar!R22+Apr!R22+May!R22+June!R22+July!R22+Aug!R22+Sep!R22+Oct!R22+Nov!R22+Dec!R22</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S22" s="83">
         <f>Jan!S22+Feb!S22+Mar!S22+Apr!S22+May!S22+June!S22+July!S22+Aug!S22+Sep!S22+Oct!S22+Nov!S22+Dec!S22</f>
@@ -3290,23 +3290,23 @@
       <c r="F23" s="19"/>
       <c r="G23" s="79">
         <f>Jan!G23+Feb!G23+Mar!G23+Apr!G23+May!G23+June!G23+July!G23+Aug!G23+Sep!G23+Oct!G23+Nov!G23+Dec!G23</f>
-        <v>120124</v>
+        <v>142192</v>
       </c>
       <c r="H23" s="80">
         <f>Jan!H23+Feb!H23+Mar!H23+Apr!H23+May!H23+June!H23+July!H23+Aug!H23+Sep!H23+Oct!H23+Nov!H23+Dec!H23</f>
-        <v>31263</v>
+        <v>36644</v>
       </c>
       <c r="I23" s="81">
         <f>Jan!I23+Feb!I23+Mar!I23+Apr!I23+May!I23+June!I23+July!I23+Aug!I23+Sep!I23+Oct!I23+Nov!I23+Dec!I23</f>
-        <v>44912</v>
+        <v>52510</v>
       </c>
       <c r="J23" s="82">
         <f>Jan!J23+Feb!J23+Mar!J23+Apr!J23+May!J23+June!J23+July!J23+Aug!J23+Sep!J23+Oct!J23+Nov!J23+Dec!J23</f>
-        <v>16328</v>
+        <v>19410</v>
       </c>
       <c r="K23" s="82">
         <f>Jan!K23+Feb!K23+Mar!K23+Apr!K23+May!K23+June!K23+July!K23+Aug!K23+Sep!K23+Oct!K23+Nov!K23+Dec!K23</f>
-        <v>4595</v>
+        <v>5535</v>
       </c>
       <c r="L23" s="82">
         <f>Jan!L23+Feb!L23+Mar!L23+Apr!L23+May!L23+June!L23+July!L23+Aug!L23+Sep!L23+Oct!L23+Nov!L23+Dec!L23</f>
@@ -3314,15 +3314,15 @@
       </c>
       <c r="M23" s="82">
         <f>Jan!M23+Feb!M23+Mar!M23+Apr!M23+May!M23+June!M23+July!M23+Aug!M23+Sep!M23+Oct!M23+Nov!M23+Dec!M23</f>
-        <v>1501</v>
+        <v>1688</v>
       </c>
       <c r="N23" s="82">
         <f>Jan!N23+Feb!N23+Mar!N23+Apr!N23+May!N23+June!N23+July!N23+Aug!N23+Sep!N23+Oct!N23+Nov!N23+Dec!N23</f>
-        <v>5887</v>
+        <v>7224</v>
       </c>
       <c r="O23" s="82">
         <f>Jan!O23+Feb!O23+Mar!O23+Apr!O23+May!O23+June!O23+July!O23+Aug!O23+Sep!O23+Oct!O23+Nov!O23+Dec!O23</f>
-        <v>1788</v>
+        <v>2469</v>
       </c>
       <c r="P23" s="82">
         <f>Jan!P23+Feb!P23+Mar!P23+Apr!P23+May!P23+June!P23+July!P23+Aug!P23+Sep!P23+Oct!P23+Nov!P23+Dec!P23</f>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="Q23" s="82">
         <f>Jan!Q23+Feb!Q23+Mar!Q23+Apr!Q23+May!Q23+June!Q23+July!Q23+Aug!Q23+Sep!Q23+Oct!Q23+Nov!Q23+Dec!Q23</f>
-        <v>13850</v>
+        <v>16712</v>
       </c>
       <c r="R23" s="82">
         <f>Jan!R23+Feb!R23+Mar!R23+Apr!R23+May!R23+June!R23+July!R23+Aug!R23+Sep!R23+Oct!R23+Nov!R23+Dec!R23</f>
@@ -3351,19 +3351,19 @@
       <c r="F24" s="19"/>
       <c r="G24" s="79">
         <f>Jan!G24+Feb!G24+Mar!G24+Apr!G24+May!G24+June!G24+July!G24+Aug!G24+Sep!G24+Oct!G24+Nov!G24+Dec!G24</f>
-        <v>88043</v>
+        <v>99509</v>
       </c>
       <c r="H24" s="80">
         <f>Jan!H24+Feb!H24+Mar!H24+Apr!H24+May!H24+June!H24+July!H24+Aug!H24+Sep!H24+Oct!H24+Nov!H24+Dec!H24</f>
-        <v>55426</v>
+        <v>61579</v>
       </c>
       <c r="I24" s="81">
         <f>Jan!I24+Feb!I24+Mar!I24+Apr!I24+May!I24+June!I24+July!I24+Aug!I24+Sep!I24+Oct!I24+Nov!I24+Dec!I24</f>
-        <v>12870</v>
+        <v>15421</v>
       </c>
       <c r="J24" s="82">
         <f>Jan!J24+Feb!J24+Mar!J24+Apr!J24+May!J24+June!J24+July!J24+Aug!J24+Sep!J24+Oct!J24+Nov!J24+Dec!J24</f>
-        <v>3062</v>
+        <v>3606</v>
       </c>
       <c r="K24" s="82">
         <f>Jan!K24+Feb!K24+Mar!K24+Apr!K24+May!K24+June!K24+July!K24+Aug!K24+Sep!K24+Oct!K24+Nov!K24+Dec!K24</f>
@@ -3371,27 +3371,27 @@
       </c>
       <c r="L24" s="82">
         <f>Jan!L24+Feb!L24+Mar!L24+Apr!L24+May!L24+June!L24+July!L24+Aug!L24+Sep!L24+Oct!L24+Nov!L24+Dec!L24</f>
-        <v>4634</v>
+        <v>5336</v>
       </c>
       <c r="M24" s="82">
         <f>Jan!M24+Feb!M24+Mar!M24+Apr!M24+May!M24+June!M24+July!M24+Aug!M24+Sep!M24+Oct!M24+Nov!M24+Dec!M24</f>
-        <v>936</v>
+        <v>1050</v>
       </c>
       <c r="N24" s="82">
         <f>Jan!N24+Feb!N24+Mar!N24+Apr!N24+May!N24+June!N24+July!N24+Aug!N24+Sep!N24+Oct!N24+Nov!N24+Dec!N24</f>
-        <v>933</v>
+        <v>1074</v>
       </c>
       <c r="O24" s="82">
         <f>Jan!O24+Feb!O24+Mar!O24+Apr!O24+May!O24+June!O24+July!O24+Aug!O24+Sep!O24+Oct!O24+Nov!O24+Dec!O24</f>
-        <v>5992</v>
+        <v>6679</v>
       </c>
       <c r="P24" s="82">
         <f>Jan!P24+Feb!P24+Mar!P24+Apr!P24+May!P24+June!P24+July!P24+Aug!P24+Sep!P24+Oct!P24+Nov!P24+Dec!P24</f>
-        <v>487</v>
+        <v>542</v>
       </c>
       <c r="Q24" s="82">
         <f>Jan!Q24+Feb!Q24+Mar!Q24+Apr!Q24+May!Q24+June!Q24+July!Q24+Aug!Q24+Sep!Q24+Oct!Q24+Nov!Q24+Dec!Q24</f>
-        <v>3703</v>
+        <v>4222</v>
       </c>
       <c r="R24" s="82">
         <f>Jan!R24+Feb!R24+Mar!R24+Apr!R24+May!R24+June!R24+July!R24+Aug!R24+Sep!R24+Oct!R24+Nov!R24+Dec!R24</f>
@@ -3412,19 +3412,19 @@
       <c r="F25" s="19"/>
       <c r="G25" s="79">
         <f>Jan!G25+Feb!G25+Mar!G25+Apr!G25+May!G25+June!G25+July!G25+Aug!G25+Sep!G25+Oct!G25+Nov!G25+Dec!G25</f>
-        <v>84412</v>
+        <v>100884</v>
       </c>
       <c r="H25" s="80">
         <f>Jan!H25+Feb!H25+Mar!H25+Apr!H25+May!H25+June!H25+July!H25+Aug!H25+Sep!H25+Oct!H25+Nov!H25+Dec!H25</f>
-        <v>30202</v>
+        <v>37119</v>
       </c>
       <c r="I25" s="81">
         <f>Jan!I25+Feb!I25+Mar!I25+Apr!I25+May!I25+June!I25+July!I25+Aug!I25+Sep!I25+Oct!I25+Nov!I25+Dec!I25</f>
-        <v>40068</v>
+        <v>47347</v>
       </c>
       <c r="J25" s="82">
         <f>Jan!J25+Feb!J25+Mar!J25+Apr!J25+May!J25+June!J25+July!J25+Aug!J25+Sep!J25+Oct!J25+Nov!J25+Dec!J25</f>
-        <v>4475</v>
+        <v>5258</v>
       </c>
       <c r="K25" s="82">
         <f>Jan!K25+Feb!K25+Mar!K25+Apr!K25+May!K25+June!K25+July!K25+Aug!K25+Sep!K25+Oct!K25+Nov!K25+Dec!K25</f>
@@ -3436,23 +3436,23 @@
       </c>
       <c r="M25" s="82">
         <f>Jan!M25+Feb!M25+Mar!M25+Apr!M25+May!M25+June!M25+July!M25+Aug!M25+Sep!M25+Oct!M25+Nov!M25+Dec!M25</f>
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="N25" s="82">
         <f>Jan!N25+Feb!N25+Mar!N25+Apr!N25+May!N25+June!N25+July!N25+Aug!N25+Sep!N25+Oct!N25+Nov!N25+Dec!N25</f>
-        <v>604</v>
+        <v>684</v>
       </c>
       <c r="O25" s="82">
         <f>Jan!O25+Feb!O25+Mar!O25+Apr!O25+May!O25+June!O25+July!O25+Aug!O25+Sep!O25+Oct!O25+Nov!O25+Dec!O25</f>
-        <v>1465</v>
+        <v>1752</v>
       </c>
       <c r="P25" s="82">
         <f>Jan!P25+Feb!P25+Mar!P25+Apr!P25+May!P25+June!P25+July!P25+Aug!P25+Sep!P25+Oct!P25+Nov!P25+Dec!P25</f>
-        <v>197</v>
+        <v>225</v>
       </c>
       <c r="Q25" s="82">
         <f>Jan!Q25+Feb!Q25+Mar!Q25+Apr!Q25+May!Q25+June!Q25+July!Q25+Aug!Q25+Sep!Q25+Oct!Q25+Nov!Q25+Dec!Q25</f>
-        <v>7279</v>
+        <v>8364</v>
       </c>
       <c r="R25" s="82">
         <f>Jan!R25+Feb!R25+Mar!R25+Apr!R25+May!R25+June!R25+July!R25+Aug!R25+Sep!R25+Oct!R25+Nov!R25+Dec!R25</f>
@@ -3473,11 +3473,11 @@
       <c r="F26" s="19"/>
       <c r="G26" s="79">
         <f>Jan!G26+Feb!G26+Mar!G26+Apr!G26+May!G26+June!G26+July!G26+Aug!G26+Sep!G26+Oct!G26+Nov!G26+Dec!G26</f>
-        <v>6666</v>
+        <v>7750</v>
       </c>
       <c r="H26" s="80">
         <f>Jan!H26+Feb!H26+Mar!H26+Apr!H26+May!H26+June!H26+July!H26+Aug!H26+Sep!H26+Oct!H26+Nov!H26+Dec!H26</f>
-        <v>1976</v>
+        <v>2418</v>
       </c>
       <c r="I26" s="81">
         <f>Jan!I26+Feb!I26+Mar!I26+Apr!I26+May!I26+June!I26+July!I26+Aug!I26+Sep!I26+Oct!I26+Nov!I26+Dec!I26</f>
@@ -3501,19 +3501,19 @@
       </c>
       <c r="N26" s="82">
         <f>Jan!N26+Feb!N26+Mar!N26+Apr!N26+May!N26+June!N26+July!N26+Aug!N26+Sep!N26+Oct!N26+Nov!N26+Dec!N26</f>
-        <v>903</v>
+        <v>1016</v>
       </c>
       <c r="O26" s="82">
         <f>Jan!O26+Feb!O26+Mar!O26+Apr!O26+May!O26+June!O26+July!O26+Aug!O26+Sep!O26+Oct!O26+Nov!O26+Dec!O26</f>
-        <v>331</v>
+        <v>368</v>
       </c>
       <c r="P26" s="82">
         <f>Jan!P26+Feb!P26+Mar!P26+Apr!P26+May!P26+June!P26+July!P26+Aug!P26+Sep!P26+Oct!P26+Nov!P26+Dec!P26</f>
-        <v>444</v>
+        <v>502</v>
       </c>
       <c r="Q26" s="82">
         <f>Jan!Q26+Feb!Q26+Mar!Q26+Apr!Q26+May!Q26+June!Q26+July!Q26+Aug!Q26+Sep!Q26+Oct!Q26+Nov!Q26+Dec!Q26</f>
-        <v>3012</v>
+        <v>3446</v>
       </c>
       <c r="R26" s="82">
         <f>Jan!R26+Feb!R26+Mar!R26+Apr!R26+May!R26+June!R26+July!R26+Aug!R26+Sep!R26+Oct!R26+Nov!R26+Dec!R26</f>
@@ -3534,11 +3534,11 @@
       <c r="F27" s="19"/>
       <c r="G27" s="79">
         <f>Jan!G27+Feb!G27+Mar!G27+Apr!G27+May!G27+June!G27+July!G27+Aug!G27+Sep!G27+Oct!G27+Nov!G27+Dec!G27</f>
-        <v>31896</v>
+        <v>39065</v>
       </c>
       <c r="H27" s="80">
         <f>Jan!H27+Feb!H27+Mar!H27+Apr!H27+May!H27+June!H27+July!H27+Aug!H27+Sep!H27+Oct!H27+Nov!H27+Dec!H27</f>
-        <v>14037</v>
+        <v>16585</v>
       </c>
       <c r="I27" s="81">
         <f>Jan!I27+Feb!I27+Mar!I27+Apr!I27+May!I27+June!I27+July!I27+Aug!I27+Sep!I27+Oct!I27+Nov!I27+Dec!I27</f>
@@ -3558,23 +3558,23 @@
       </c>
       <c r="M27" s="82">
         <f>Jan!M27+Feb!M27+Mar!M27+Apr!M27+May!M27+June!M27+July!M27+Aug!M27+Sep!M27+Oct!M27+Nov!M27+Dec!M27</f>
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="N27" s="82">
         <f>Jan!N27+Feb!N27+Mar!N27+Apr!N27+May!N27+June!N27+July!N27+Aug!N27+Sep!N27+Oct!N27+Nov!N27+Dec!N27</f>
-        <v>7350</v>
+        <v>8490</v>
       </c>
       <c r="O27" s="82">
         <f>Jan!O27+Feb!O27+Mar!O27+Apr!O27+May!O27+June!O27+July!O27+Aug!O27+Sep!O27+Oct!O27+Nov!O27+Dec!O27</f>
-        <v>7226</v>
+        <v>10136</v>
       </c>
       <c r="P27" s="82">
         <f>Jan!P27+Feb!P27+Mar!P27+Apr!P27+May!P27+June!P27+July!P27+Aug!P27+Sep!P27+Oct!P27+Nov!P27+Dec!P27</f>
-        <v>1586</v>
+        <v>1848</v>
       </c>
       <c r="Q27" s="82">
         <f>Jan!Q27+Feb!Q27+Mar!Q27+Apr!Q27+May!Q27+June!Q27+July!Q27+Aug!Q27+Sep!Q27+Oct!Q27+Nov!Q27+Dec!Q27</f>
-        <v>1445</v>
+        <v>1724</v>
       </c>
       <c r="R27" s="82">
         <f>Jan!R27+Feb!R27+Mar!R27+Apr!R27+May!R27+June!R27+July!R27+Aug!R27+Sep!R27+Oct!R27+Nov!R27+Dec!R27</f>
@@ -3595,11 +3595,11 @@
       <c r="F28" s="19"/>
       <c r="G28" s="79">
         <f>Jan!G28+Feb!G28+Mar!G28+Apr!G28+May!G28+June!G28+July!G28+Aug!G28+Sep!G28+Oct!G28+Nov!G28+Dec!G28</f>
-        <v>2378</v>
+        <v>2676</v>
       </c>
       <c r="H28" s="80">
         <f>Jan!H28+Feb!H28+Mar!H28+Apr!H28+May!H28+June!H28+July!H28+Aug!H28+Sep!H28+Oct!H28+Nov!H28+Dec!H28</f>
-        <v>2378</v>
+        <v>2676</v>
       </c>
       <c r="I28" s="81">
         <f>Jan!I28+Feb!I28+Mar!I28+Apr!I28+May!I28+June!I28+July!I28+Aug!I28+Sep!I28+Oct!I28+Nov!I28+Dec!I28</f>
@@ -3656,11 +3656,11 @@
       <c r="F29" s="19"/>
       <c r="G29" s="79">
         <f>Jan!G29+Feb!G29+Mar!G29+Apr!G29+May!G29+June!G29+July!G29+Aug!G29+Sep!G29+Oct!G29+Nov!G29+Dec!G29</f>
-        <v>699</v>
+        <v>832</v>
       </c>
       <c r="H29" s="80">
         <f>Jan!H29+Feb!H29+Mar!H29+Apr!H29+May!H29+June!H29+July!H29+Aug!H29+Sep!H29+Oct!H29+Nov!H29+Dec!H29</f>
-        <v>699</v>
+        <v>832</v>
       </c>
       <c r="I29" s="81">
         <f>Jan!I29+Feb!I29+Mar!I29+Apr!I29+May!I29+June!I29+July!I29+Aug!I29+Sep!I29+Oct!I29+Nov!I29+Dec!I29</f>
@@ -3717,11 +3717,11 @@
       <c r="F30" s="19"/>
       <c r="G30" s="86">
         <f>Jan!G30+Feb!G30+Mar!G30+Apr!G30+May!G30+June!G30+July!G30+Aug!G30+Sep!G30+Oct!G30+Nov!G30+Dec!G30</f>
-        <v>29293</v>
+        <v>34582</v>
       </c>
       <c r="H30" s="87">
         <f>Jan!H30+Feb!H30+Mar!H30+Apr!H30+May!H30+June!H30+July!H30+Aug!H30+Sep!H30+Oct!H30+Nov!H30+Dec!H30</f>
-        <v>15000</v>
+        <v>17472</v>
       </c>
       <c r="I30" s="88">
         <f>Jan!I30+Feb!I30+Mar!I30+Apr!I30+May!I30+June!I30+July!I30+Aug!I30+Sep!I30+Oct!I30+Nov!I30+Dec!I30</f>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="L30" s="89">
         <f>Jan!L30+Feb!L30+Mar!L30+Apr!L30+May!L30+June!L30+July!L30+Aug!L30+Sep!L30+Oct!L30+Nov!L30+Dec!L30</f>
-        <v>14013</v>
+        <v>16654</v>
       </c>
       <c r="M30" s="89">
         <f>Jan!M30+Feb!M30+Mar!M30+Apr!M30+May!M30+June!M30+July!M30+Aug!M30+Sep!M30+Oct!M30+Nov!M30+Dec!M30</f>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="N30" s="89">
         <f>Jan!N30+Feb!N30+Mar!N30+Apr!N30+May!N30+June!N30+July!N30+Aug!N30+Sep!N30+Oct!N30+Nov!N30+Dec!N30</f>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O30" s="89">
         <f>Jan!O30+Feb!O30+Mar!O30+Apr!O30+May!O30+June!O30+July!O30+Aug!O30+Sep!O30+Oct!O30+Nov!O30+Dec!O30</f>
@@ -3753,11 +3753,11 @@
       </c>
       <c r="P30" s="89">
         <f>Jan!P30+Feb!P30+Mar!P30+Apr!P30+May!P30+June!P30+July!P30+Aug!P30+Sep!P30+Oct!P30+Nov!P30+Dec!P30</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q30" s="89">
         <f>Jan!Q30+Feb!Q30+Mar!Q30+Apr!Q30+May!Q30+June!Q30+July!Q30+Aug!Q30+Sep!Q30+Oct!Q30+Nov!Q30+Dec!Q30</f>
-        <v>255</v>
+        <v>419</v>
       </c>
       <c r="R30" s="89">
         <f>Jan!R30+Feb!R30+Mar!R30+Apr!R30+May!R30+June!R30+July!R30+Aug!R30+Sep!R30+Oct!R30+Nov!R30+Dec!R30</f>
@@ -3778,51 +3778,51 @@
       <c r="F31" s="35"/>
       <c r="G31" s="91">
         <f>Jan!G31+Feb!G31+Mar!G31+Apr!G31+May!G31+June!G31+July!G31+Aug!G31+Sep!G31+Oct!G31+Nov!G31+Dec!G31</f>
-        <v>807239</v>
+        <v>956207</v>
       </c>
       <c r="H31" s="103">
         <f>Jan!H31+Feb!H31+Mar!H31+Apr!H31+May!H31+June!H31+July!H31+Aug!H31+Sep!H31+Oct!H31+Nov!H31+Dec!H31</f>
-        <v>295779</v>
+        <v>350383</v>
       </c>
       <c r="I31" s="104">
         <f>Jan!I31+Feb!I31+Mar!I31+Apr!I31+May!I31+June!I31+July!I31+Aug!I31+Sep!I31+Oct!I31+Nov!I31+Dec!I31</f>
-        <v>186007</v>
+        <v>220658</v>
       </c>
       <c r="J31" s="94">
         <f>Jan!J31+Feb!J31+Mar!J31+Apr!J31+May!J31+June!J31+July!J31+Aug!J31+Sep!J31+Oct!J31+Nov!J31+Dec!J31</f>
-        <v>41264</v>
+        <v>49071</v>
       </c>
       <c r="K31" s="94">
         <f>Jan!K31+Feb!K31+Mar!K31+Apr!K31+May!K31+June!K31+July!K31+Aug!K31+Sep!K31+Oct!K31+Nov!K31+Dec!K31</f>
-        <v>4998</v>
+        <v>5989</v>
       </c>
       <c r="L31" s="94">
         <f>Jan!L31+Feb!L31+Mar!L31+Apr!L31+May!L31+June!L31+July!L31+Aug!L31+Sep!L31+Oct!L31+Nov!L31+Dec!L31</f>
-        <v>154901</v>
+        <v>181393</v>
       </c>
       <c r="M31" s="94">
         <f>Jan!M31+Feb!M31+Mar!M31+Apr!M31+May!M31+June!M31+July!M31+Aug!M31+Sep!M31+Oct!M31+Nov!M31+Dec!M31</f>
-        <v>6083</v>
+        <v>7679</v>
       </c>
       <c r="N31" s="94">
         <f>Jan!N31+Feb!N31+Mar!N31+Apr!N31+May!N31+June!N31+July!N31+Aug!N31+Sep!N31+Oct!N31+Nov!N31+Dec!N31</f>
-        <v>32883</v>
+        <v>39224</v>
       </c>
       <c r="O31" s="94">
         <f>Jan!O31+Feb!O31+Mar!O31+Apr!O31+May!O31+June!O31+July!O31+Aug!O31+Sep!O31+Oct!O31+Nov!O31+Dec!O31</f>
-        <v>27149</v>
+        <v>33707</v>
       </c>
       <c r="P31" s="94">
         <f>Jan!P31+Feb!P31+Mar!P31+Apr!P31+May!P31+June!P31+July!P31+Aug!P31+Sep!P31+Oct!P31+Nov!P31+Dec!P31</f>
-        <v>10409</v>
+        <v>12092</v>
       </c>
       <c r="Q31" s="94">
         <f>Jan!Q31+Feb!Q31+Mar!Q31+Apr!Q31+May!Q31+June!Q31+July!Q31+Aug!Q31+Sep!Q31+Oct!Q31+Nov!Q31+Dec!Q31</f>
-        <v>47653</v>
+        <v>55897</v>
       </c>
       <c r="R31" s="94">
         <f>Jan!R31+Feb!R31+Mar!R31+Apr!R31+May!R31+June!R31+July!R31+Aug!R31+Sep!R31+Oct!R31+Nov!R31+Dec!R31</f>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S31" s="95">
         <f>Jan!S31+Feb!S31+Mar!S31+Apr!S31+May!S31+June!S31+July!S31+Aug!S31+Sep!S31+Oct!S31+Nov!S31+Dec!S31</f>
@@ -3839,7 +3839,7 @@
       <c r="F32" s="20"/>
       <c r="G32" s="79">
         <f>Jan!G32+Feb!G32+Mar!G32+Apr!G32+May!G32+June!G32+July!G32+Aug!G32+Sep!G32+Oct!G32+Nov!G32+Dec!G32</f>
-        <v>51186</v>
+        <v>59823</v>
       </c>
       <c r="H32" s="80">
         <f>Jan!H32+Feb!H32+Mar!H32+Apr!H32+May!H32+June!H32+July!H32+Aug!H32+Sep!H32+Oct!H32+Nov!H32+Dec!H32</f>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="I32" s="81">
         <f>Jan!I32+Feb!I32+Mar!I32+Apr!I32+May!I32+June!I32+July!I32+Aug!I32+Sep!I32+Oct!I32+Nov!I32+Dec!I32</f>
-        <v>49995</v>
+        <v>58480</v>
       </c>
       <c r="J32" s="82">
         <f>Jan!J32+Feb!J32+Mar!J32+Apr!J32+May!J32+June!J32+July!J32+Aug!J32+Sep!J32+Oct!J32+Nov!J32+Dec!J32</f>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="N32" s="82">
         <f>Jan!N32+Feb!N32+Mar!N32+Apr!N32+May!N32+June!N32+July!N32+Aug!N32+Sep!N32+Oct!N32+Nov!N32+Dec!N32</f>
-        <v>1191</v>
+        <v>1343</v>
       </c>
       <c r="O32" s="82">
         <f>Jan!O32+Feb!O32+Mar!O32+Apr!O32+May!O32+June!O32+July!O32+Aug!O32+Sep!O32+Oct!O32+Nov!O32+Dec!O32</f>
@@ -3900,7 +3900,7 @@
       <c r="F33" s="20"/>
       <c r="G33" s="79">
         <f>Jan!G33+Feb!G33+Mar!G33+Apr!G33+May!G33+June!G33+July!G33+Aug!G33+Sep!G33+Oct!G33+Nov!G33+Dec!G33</f>
-        <v>37730</v>
+        <v>44443</v>
       </c>
       <c r="H33" s="80">
         <f>Jan!H33+Feb!H33+Mar!H33+Apr!H33+May!H33+June!H33+July!H33+Aug!H33+Sep!H33+Oct!H33+Nov!H33+Dec!H33</f>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="I33" s="81">
         <f>Jan!I33+Feb!I33+Mar!I33+Apr!I33+May!I33+June!I33+July!I33+Aug!I33+Sep!I33+Oct!I33+Nov!I33+Dec!I33</f>
-        <v>36478</v>
+        <v>42965</v>
       </c>
       <c r="J33" s="82">
         <f>Jan!J33+Feb!J33+Mar!J33+Apr!J33+May!J33+June!J33+July!J33+Aug!J33+Sep!J33+Oct!J33+Nov!J33+Dec!J33</f>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="K33" s="82">
         <f>Jan!K33+Feb!K33+Mar!K33+Apr!K33+May!K33+June!K33+July!K33+Aug!K33+Sep!K33+Oct!K33+Nov!K33+Dec!K33</f>
-        <v>757</v>
+        <v>919</v>
       </c>
       <c r="L33" s="82">
         <f>Jan!L33+Feb!L33+Mar!L33+Apr!L33+May!L33+June!L33+July!L33+Aug!L33+Sep!L33+Oct!L33+Nov!L33+Dec!L33</f>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="N33" s="82">
         <f>Jan!N33+Feb!N33+Mar!N33+Apr!N33+May!N33+June!N33+July!N33+Aug!N33+Sep!N33+Oct!N33+Nov!N33+Dec!N33</f>
-        <v>468</v>
+        <v>532</v>
       </c>
       <c r="O33" s="82">
         <f>Jan!O33+Feb!O33+Mar!O33+Apr!O33+May!O33+June!O33+July!O33+Aug!O33+Sep!O33+Oct!O33+Nov!O33+Dec!O33</f>
@@ -3961,7 +3961,7 @@
       <c r="F34" s="20"/>
       <c r="G34" s="79">
         <f>Jan!G34+Feb!G34+Mar!G34+Apr!G34+May!G34+June!G34+July!G34+Aug!G34+Sep!G34+Oct!G34+Nov!G34+Dec!G34</f>
-        <v>73973</v>
+        <v>85842</v>
       </c>
       <c r="H34" s="80">
         <f>Jan!H34+Feb!H34+Mar!H34+Apr!H34+May!H34+June!H34+July!H34+Aug!H34+Sep!H34+Oct!H34+Nov!H34+Dec!H34</f>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="I34" s="81">
         <f>Jan!I34+Feb!I34+Mar!I34+Apr!I34+May!I34+June!I34+July!I34+Aug!I34+Sep!I34+Oct!I34+Nov!I34+Dec!I34</f>
-        <v>73602</v>
+        <v>85417</v>
       </c>
       <c r="J34" s="82">
         <f>Jan!J34+Feb!J34+Mar!J34+Apr!J34+May!J34+June!J34+July!J34+Aug!J34+Sep!J34+Oct!J34+Nov!J34+Dec!J34</f>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="K34" s="82">
         <f>Jan!K34+Feb!K34+Mar!K34+Apr!K34+May!K34+June!K34+July!K34+Aug!K34+Sep!K34+Oct!K34+Nov!K34+Dec!K34</f>
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="L34" s="82">
         <f>Jan!L34+Feb!L34+Mar!L34+Apr!L34+May!L34+June!L34+July!L34+Aug!L34+Sep!L34+Oct!L34+Nov!L34+Dec!L34</f>
@@ -3989,11 +3989,11 @@
       </c>
       <c r="N34" s="82">
         <f>Jan!N34+Feb!N34+Mar!N34+Apr!N34+May!N34+June!N34+July!N34+Aug!N34+Sep!N34+Oct!N34+Nov!N34+Dec!N34</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O34" s="82">
         <f>Jan!O34+Feb!O34+Mar!O34+Apr!O34+May!O34+June!O34+July!O34+Aug!O34+Sep!O34+Oct!O34+Nov!O34+Dec!O34</f>
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="P34" s="82">
         <f>Jan!P34+Feb!P34+Mar!P34+Apr!P34+May!P34+June!P34+July!P34+Aug!P34+Sep!P34+Oct!P34+Nov!P34+Dec!P34</f>
@@ -4022,7 +4022,7 @@
       <c r="F35" s="20"/>
       <c r="G35" s="79">
         <f>Jan!G35+Feb!G35+Mar!G35+Apr!G35+May!G35+June!G35+July!G35+Aug!G35+Sep!G35+Oct!G35+Nov!G35+Dec!G35</f>
-        <v>4288</v>
+        <v>4978</v>
       </c>
       <c r="H35" s="80">
         <f>Jan!H35+Feb!H35+Mar!H35+Apr!H35+May!H35+June!H35+July!H35+Aug!H35+Sep!H35+Oct!H35+Nov!H35+Dec!H35</f>
@@ -4030,11 +4030,11 @@
       </c>
       <c r="I35" s="81">
         <f>Jan!I35+Feb!I35+Mar!I35+Apr!I35+May!I35+June!I35+July!I35+Aug!I35+Sep!I35+Oct!I35+Nov!I35+Dec!I35</f>
-        <v>4032</v>
+        <v>4706</v>
       </c>
       <c r="J35" s="82">
         <f>Jan!J35+Feb!J35+Mar!J35+Apr!J35+May!J35+June!J35+July!J35+Aug!J35+Sep!J35+Oct!J35+Nov!J35+Dec!J35</f>
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="K35" s="82">
         <f>Jan!K35+Feb!K35+Mar!K35+Apr!K35+May!K35+June!K35+July!K35+Aug!K35+Sep!K35+Oct!K35+Nov!K35+Dec!K35</f>
@@ -4083,7 +4083,7 @@
       <c r="F36" s="20"/>
       <c r="G36" s="86">
         <f>Jan!G36+Feb!G36+Mar!G36+Apr!G36+May!G36+June!G36+July!G36+Aug!G36+Sep!G36+Oct!G36+Nov!G36+Dec!G36</f>
-        <v>7041</v>
+        <v>8693</v>
       </c>
       <c r="H36" s="87">
         <f>Jan!H36+Feb!H36+Mar!H36+Apr!H36+May!H36+June!H36+July!H36+Aug!H36+Sep!H36+Oct!H36+Nov!H36+Dec!H36</f>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="I36" s="88">
         <f>Jan!I36+Feb!I36+Mar!I36+Apr!I36+May!I36+June!I36+July!I36+Aug!I36+Sep!I36+Oct!I36+Nov!I36+Dec!I36</f>
-        <v>7034</v>
+        <v>8684</v>
       </c>
       <c r="J36" s="89">
         <f>Jan!J36+Feb!J36+Mar!J36+Apr!J36+May!J36+June!J36+July!J36+Aug!J36+Sep!J36+Oct!J36+Nov!J36+Dec!J36</f>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="N36" s="89">
         <f>Jan!N36+Feb!N36+Mar!N36+Apr!N36+May!N36+June!N36+July!N36+Aug!N36+Sep!N36+Oct!N36+Nov!N36+Dec!N36</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O36" s="89">
         <f>Jan!O36+Feb!O36+Mar!O36+Apr!O36+May!O36+June!O36+July!O36+Aug!O36+Sep!O36+Oct!O36+Nov!O36+Dec!O36</f>
@@ -4144,7 +4144,7 @@
       <c r="F37" s="68"/>
       <c r="G37" s="91">
         <f>Jan!G37+Feb!G37+Mar!G37+Apr!G37+May!G37+June!G37+July!G37+Aug!G37+Sep!G37+Oct!G37+Nov!G37+Dec!G37</f>
-        <v>174218</v>
+        <v>203779</v>
       </c>
       <c r="H37" s="92">
         <f>Jan!H37+Feb!H37+Mar!H37+Apr!H37+May!H37+June!H37+July!H37+Aug!H37+Sep!H37+Oct!H37+Nov!H37+Dec!H37</f>
@@ -4152,15 +4152,15 @@
       </c>
       <c r="I37" s="104">
         <f>Jan!I37+Feb!I37+Mar!I37+Apr!I37+May!I37+June!I37+July!I37+Aug!I37+Sep!I37+Oct!I37+Nov!I37+Dec!I37</f>
-        <v>171141</v>
+        <v>200252</v>
       </c>
       <c r="J37" s="94">
         <f>Jan!J37+Feb!J37+Mar!J37+Apr!J37+May!J37+June!J37+July!J37+Aug!J37+Sep!J37+Oct!J37+Nov!J37+Dec!J37</f>
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="K37" s="94">
         <f>Jan!K37+Feb!K37+Mar!K37+Apr!K37+May!K37+June!K37+July!K37+Aug!K37+Sep!K37+Oct!K37+Nov!K37+Dec!K37</f>
-        <v>827</v>
+        <v>1014</v>
       </c>
       <c r="L37" s="94">
         <f>Jan!L37+Feb!L37+Mar!L37+Apr!L37+May!L37+June!L37+July!L37+Aug!L37+Sep!L37+Oct!L37+Nov!L37+Dec!L37</f>
@@ -4172,11 +4172,11 @@
       </c>
       <c r="N37" s="94">
         <f>Jan!N37+Feb!N37+Mar!N37+Apr!N37+May!N37+June!N37+July!N37+Aug!N37+Sep!N37+Oct!N37+Nov!N37+Dec!N37</f>
-        <v>1700</v>
+        <v>1919</v>
       </c>
       <c r="O37" s="94">
         <f>Jan!O37+Feb!O37+Mar!O37+Apr!O37+May!O37+June!O37+July!O37+Aug!O37+Sep!O37+Oct!O37+Nov!O37+Dec!O37</f>
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="P37" s="94">
         <f>Jan!P37+Feb!P37+Mar!P37+Apr!P37+May!P37+June!P37+July!P37+Aug!P37+Sep!P37+Oct!P37+Nov!P37+Dec!P37</f>
@@ -4205,7 +4205,7 @@
       <c r="F38" s="19"/>
       <c r="G38" s="79">
         <f>Jan!G38+Feb!G38+Mar!G38+Apr!G38+May!G38+June!G38+July!G38+Aug!G38+Sep!G38+Oct!G38+Nov!G38+Dec!G38</f>
-        <v>8673</v>
+        <v>13567</v>
       </c>
       <c r="H38" s="80">
         <f>Jan!H38+Feb!H38+Mar!H38+Apr!H38+May!H38+June!H38+July!H38+Aug!H38+Sep!H38+Oct!H38+Nov!H38+Dec!H38</f>
@@ -4225,15 +4225,15 @@
       </c>
       <c r="L38" s="82">
         <f>Jan!L38+Feb!L38+Mar!L38+Apr!L38+May!L38+June!L38+July!L38+Aug!L38+Sep!L38+Oct!L38+Nov!L38+Dec!L38</f>
-        <v>8567</v>
+        <v>13238</v>
       </c>
       <c r="M38" s="82">
         <f>Jan!M38+Feb!M38+Mar!M38+Apr!M38+May!M38+June!M38+July!M38+Aug!M38+Sep!M38+Oct!M38+Nov!M38+Dec!M38</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N38" s="82">
         <f>Jan!N38+Feb!N38+Mar!N38+Apr!N38+May!N38+June!N38+July!N38+Aug!N38+Sep!N38+Oct!N38+Nov!N38+Dec!N38</f>
-        <v>104</v>
+        <v>326</v>
       </c>
       <c r="O38" s="82">
         <f>Jan!O38+Feb!O38+Mar!O38+Apr!O38+May!O38+June!O38+July!O38+Aug!O38+Sep!O38+Oct!O38+Nov!O38+Dec!O38</f>
@@ -4266,7 +4266,7 @@
       <c r="F39" s="19"/>
       <c r="G39" s="79">
         <f>Jan!G39+Feb!G39+Mar!G39+Apr!G39+May!G39+June!G39+July!G39+Aug!G39+Sep!G39+Oct!G39+Nov!G39+Dec!G39</f>
-        <v>13779</v>
+        <v>16119</v>
       </c>
       <c r="H39" s="80">
         <f>Jan!H39+Feb!H39+Mar!H39+Apr!H39+May!H39+June!H39+July!H39+Aug!H39+Sep!H39+Oct!H39+Nov!H39+Dec!H39</f>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="L39" s="82">
         <f>Jan!L39+Feb!L39+Mar!L39+Apr!L39+May!L39+June!L39+July!L39+Aug!L39+Sep!L39+Oct!L39+Nov!L39+Dec!L39</f>
-        <v>13776</v>
+        <v>16116</v>
       </c>
       <c r="M39" s="82">
         <f>Jan!M39+Feb!M39+Mar!M39+Apr!M39+May!M39+June!M39+July!M39+Aug!M39+Sep!M39+Oct!M39+Nov!M39+Dec!M39</f>
@@ -4327,7 +4327,7 @@
       <c r="F40" s="19"/>
       <c r="G40" s="79">
         <f>Jan!G40+Feb!G40+Mar!G40+Apr!G40+May!G40+June!G40+July!G40+Aug!G40+Sep!G40+Oct!G40+Nov!G40+Dec!G40</f>
-        <v>7326</v>
+        <v>7544</v>
       </c>
       <c r="H40" s="80">
         <f>Jan!H40+Feb!H40+Mar!H40+Apr!H40+May!H40+June!H40+July!H40+Aug!H40+Sep!H40+Oct!H40+Nov!H40+Dec!H40</f>
@@ -4347,11 +4347,11 @@
       </c>
       <c r="L40" s="82">
         <f>Jan!L40+Feb!L40+Mar!L40+Apr!L40+May!L40+June!L40+July!L40+Aug!L40+Sep!L40+Oct!L40+Nov!L40+Dec!L40</f>
-        <v>6886</v>
+        <v>7073</v>
       </c>
       <c r="M40" s="82">
         <f>Jan!M40+Feb!M40+Mar!M40+Apr!M40+May!M40+June!M40+July!M40+Aug!M40+Sep!M40+Oct!M40+Nov!M40+Dec!M40</f>
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="N40" s="82">
         <f>Jan!N40+Feb!N40+Mar!N40+Apr!N40+May!N40+June!N40+July!N40+Aug!N40+Sep!N40+Oct!N40+Nov!N40+Dec!N40</f>
@@ -4367,7 +4367,7 @@
       </c>
       <c r="Q40" s="82">
         <f>Jan!Q40+Feb!Q40+Mar!Q40+Apr!Q40+May!Q40+June!Q40+July!Q40+Aug!Q40+Sep!Q40+Oct!Q40+Nov!Q40+Dec!Q40</f>
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="R40" s="82">
         <f>Jan!R40+Feb!R40+Mar!R40+Apr!R40+May!R40+June!R40+July!R40+Aug!R40+Sep!R40+Oct!R40+Nov!R40+Dec!R40</f>
@@ -4388,7 +4388,7 @@
       <c r="F41" s="20"/>
       <c r="G41" s="79">
         <f>Jan!G41+Feb!G41+Mar!G41+Apr!G41+May!G41+June!G41+July!G41+Aug!G41+Sep!G41+Oct!G41+Nov!G41+Dec!G41</f>
-        <v>15407</v>
+        <v>17587</v>
       </c>
       <c r="H41" s="80">
         <f>Jan!H41+Feb!H41+Mar!H41+Apr!H41+May!H41+June!H41+July!H41+Aug!H41+Sep!H41+Oct!H41+Nov!H41+Dec!H41</f>
@@ -4408,15 +4408,15 @@
       </c>
       <c r="L41" s="82">
         <f>Jan!L41+Feb!L41+Mar!L41+Apr!L41+May!L41+June!L41+July!L41+Aug!L41+Sep!L41+Oct!L41+Nov!L41+Dec!L41</f>
-        <v>13939</v>
+        <v>15834</v>
       </c>
       <c r="M41" s="82">
         <f>Jan!M41+Feb!M41+Mar!M41+Apr!M41+May!M41+June!M41+July!M41+Aug!M41+Sep!M41+Oct!M41+Nov!M41+Dec!M41</f>
-        <v>1383</v>
+        <v>1647</v>
       </c>
       <c r="N41" s="82">
         <f>Jan!N41+Feb!N41+Mar!N41+Apr!N41+May!N41+June!N41+July!N41+Aug!N41+Sep!N41+Oct!N41+Nov!N41+Dec!N41</f>
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="O41" s="82">
         <f>Jan!O41+Feb!O41+Mar!O41+Apr!O41+May!O41+June!O41+July!O41+Aug!O41+Sep!O41+Oct!O41+Nov!O41+Dec!O41</f>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="P41" s="82">
         <f>Jan!P41+Feb!P41+Mar!P41+Apr!P41+May!P41+June!P41+July!P41+Aug!P41+Sep!P41+Oct!P41+Nov!P41+Dec!P41</f>
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="Q41" s="82">
         <f>Jan!Q41+Feb!Q41+Mar!Q41+Apr!Q41+May!Q41+June!Q41+July!Q41+Aug!Q41+Sep!Q41+Oct!Q41+Nov!Q41+Dec!Q41</f>
@@ -4449,7 +4449,7 @@
       <c r="F42" s="20"/>
       <c r="G42" s="86">
         <f>Jan!G42+Feb!G42+Mar!G42+Apr!G42+May!G42+June!G42+July!G42+Aug!G42+Sep!G42+Oct!G42+Nov!G42+Dec!G42</f>
-        <v>110584</v>
+        <v>126707</v>
       </c>
       <c r="H42" s="87">
         <f>Jan!H42+Feb!H42+Mar!H42+Apr!H42+May!H42+June!H42+July!H42+Aug!H42+Sep!H42+Oct!H42+Nov!H42+Dec!H42</f>
@@ -4469,23 +4469,23 @@
       </c>
       <c r="L42" s="89">
         <f>Jan!L42+Feb!L42+Mar!L42+Apr!L42+May!L42+June!L42+July!L42+Aug!L42+Sep!L42+Oct!L42+Nov!L42+Dec!L42</f>
-        <v>85683</v>
+        <v>98238</v>
       </c>
       <c r="M42" s="89">
         <f>Jan!M42+Feb!M42+Mar!M42+Apr!M42+May!M42+June!M42+July!M42+Aug!M42+Sep!M42+Oct!M42+Nov!M42+Dec!M42</f>
-        <v>9538</v>
+        <v>10868</v>
       </c>
       <c r="N42" s="89">
         <f>Jan!N42+Feb!N42+Mar!N42+Apr!N42+May!N42+June!N42+July!N42+Aug!N42+Sep!N42+Oct!N42+Nov!N42+Dec!N42</f>
-        <v>1835</v>
+        <v>2134</v>
       </c>
       <c r="O42" s="89">
         <f>Jan!O42+Feb!O42+Mar!O42+Apr!O42+May!O42+June!O42+July!O42+Aug!O42+Sep!O42+Oct!O42+Nov!O42+Dec!O42</f>
-        <v>9248</v>
+        <v>10378</v>
       </c>
       <c r="P42" s="89">
         <f>Jan!P42+Feb!P42+Mar!P42+Apr!P42+May!P42+June!P42+July!P42+Aug!P42+Sep!P42+Oct!P42+Nov!P42+Dec!P42</f>
-        <v>4280</v>
+        <v>5089</v>
       </c>
       <c r="Q42" s="89">
         <f>Jan!Q42+Feb!Q42+Mar!Q42+Apr!Q42+May!Q42+June!Q42+July!Q42+Aug!Q42+Sep!Q42+Oct!Q42+Nov!Q42+Dec!Q42</f>
@@ -4510,7 +4510,7 @@
       <c r="F43" s="22"/>
       <c r="G43" s="91">
         <f>Jan!G43+Feb!G43+Mar!G43+Apr!G43+May!G43+June!G43+July!G43+Aug!G43+Sep!G43+Oct!G43+Nov!G43+Dec!G43</f>
-        <v>155769</v>
+        <v>181524</v>
       </c>
       <c r="H43" s="92">
         <f>Jan!H43+Feb!H43+Mar!H43+Apr!H43+May!H43+June!H43+July!H43+Aug!H43+Sep!H43+Oct!H43+Nov!H43+Dec!H43</f>
@@ -4530,27 +4530,27 @@
       </c>
       <c r="L43" s="94">
         <f>Jan!L43+Feb!L43+Mar!L43+Apr!L43+May!L43+June!L43+July!L43+Aug!L43+Sep!L43+Oct!L43+Nov!L43+Dec!L43</f>
-        <v>128851</v>
+        <v>150499</v>
       </c>
       <c r="M43" s="94">
         <f>Jan!M43+Feb!M43+Mar!M43+Apr!M43+May!M43+June!M43+July!M43+Aug!M43+Sep!M43+Oct!M43+Nov!M43+Dec!M43</f>
-        <v>11218</v>
+        <v>12825</v>
       </c>
       <c r="N43" s="94">
         <f>Jan!N43+Feb!N43+Mar!N43+Apr!N43+May!N43+June!N43+July!N43+Aug!N43+Sep!N43+Oct!N43+Nov!N43+Dec!N43</f>
-        <v>1975</v>
+        <v>2507</v>
       </c>
       <c r="O43" s="94">
         <f>Jan!O43+Feb!O43+Mar!O43+Apr!O43+May!O43+June!O43+July!O43+Aug!O43+Sep!O43+Oct!O43+Nov!O43+Dec!O43</f>
-        <v>9248</v>
+        <v>10378</v>
       </c>
       <c r="P43" s="94">
         <f>Jan!P43+Feb!P43+Mar!P43+Apr!P43+May!P43+June!P43+July!P43+Aug!P43+Sep!P43+Oct!P43+Nov!P43+Dec!P43</f>
-        <v>4349</v>
+        <v>5168</v>
       </c>
       <c r="Q43" s="94">
         <f>Jan!Q43+Feb!Q43+Mar!Q43+Apr!Q43+May!Q43+June!Q43+July!Q43+Aug!Q43+Sep!Q43+Oct!Q43+Nov!Q43+Dec!Q43</f>
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="R43" s="94">
         <f>Jan!R43+Feb!R43+Mar!R43+Apr!R43+May!R43+June!R43+July!R43+Aug!R43+Sep!R43+Oct!R43+Nov!R43+Dec!R43</f>
@@ -4571,7 +4571,7 @@
       <c r="F44" s="19"/>
       <c r="G44" s="79">
         <f>Jan!G44+Feb!G44+Mar!G44+Apr!G44+May!G44+June!G44+July!G44+Aug!G44+Sep!G44+Oct!G44+Nov!G44+Dec!G44</f>
-        <v>40060</v>
+        <v>46905</v>
       </c>
       <c r="H44" s="80">
         <f>Jan!H44+Feb!H44+Mar!H44+Apr!H44+May!H44+June!H44+July!H44+Aug!H44+Sep!H44+Oct!H44+Nov!H44+Dec!H44</f>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="K44" s="82">
         <f>Jan!K44+Feb!K44+Mar!K44+Apr!K44+May!K44+June!K44+July!K44+Aug!K44+Sep!K44+Oct!K44+Nov!K44+Dec!K44</f>
-        <v>29118</v>
+        <v>34444</v>
       </c>
       <c r="L44" s="82">
         <f>Jan!L44+Feb!L44+Mar!L44+Apr!L44+May!L44+June!L44+July!L44+Aug!L44+Sep!L44+Oct!L44+Nov!L44+Dec!L44</f>
@@ -4599,11 +4599,11 @@
       </c>
       <c r="N44" s="82">
         <f>Jan!N44+Feb!N44+Mar!N44+Apr!N44+May!N44+June!N44+July!N44+Aug!N44+Sep!N44+Oct!N44+Nov!N44+Dec!N44</f>
-        <v>9757</v>
+        <v>11112</v>
       </c>
       <c r="O44" s="82">
         <f>Jan!O44+Feb!O44+Mar!O44+Apr!O44+May!O44+June!O44+July!O44+Aug!O44+Sep!O44+Oct!O44+Nov!O44+Dec!O44</f>
-        <v>1185</v>
+        <v>1349</v>
       </c>
       <c r="P44" s="82">
         <f>Jan!P44+Feb!P44+Mar!P44+Apr!P44+May!P44+June!P44+July!P44+Aug!P44+Sep!P44+Oct!P44+Nov!P44+Dec!P44</f>
@@ -4632,7 +4632,7 @@
       <c r="F45" s="19"/>
       <c r="G45" s="86">
         <f>Jan!G45+Feb!G45+Mar!G45+Apr!G45+May!G45+June!G45+July!G45+Aug!G45+Sep!G45+Oct!G45+Nov!G45+Dec!G45</f>
-        <v>102601</v>
+        <v>119402</v>
       </c>
       <c r="H45" s="87">
         <f>Jan!H45+Feb!H45+Mar!H45+Apr!H45+May!H45+June!H45+July!H45+Aug!H45+Sep!H45+Oct!H45+Nov!H45+Dec!H45</f>
@@ -4640,19 +4640,19 @@
       </c>
       <c r="I45" s="88">
         <f>Jan!I45+Feb!I45+Mar!I45+Apr!I45+May!I45+June!I45+July!I45+Aug!I45+Sep!I45+Oct!I45+Nov!I45+Dec!I45</f>
-        <v>73579</v>
+        <v>85674</v>
       </c>
       <c r="J45" s="89">
         <f>Jan!J45+Feb!J45+Mar!J45+Apr!J45+May!J45+June!J45+July!J45+Aug!J45+Sep!J45+Oct!J45+Nov!J45+Dec!J45</f>
-        <v>6756</v>
+        <v>7575</v>
       </c>
       <c r="K45" s="89">
         <f>Jan!K45+Feb!K45+Mar!K45+Apr!K45+May!K45+June!K45+July!K45+Aug!K45+Sep!K45+Oct!K45+Nov!K45+Dec!K45</f>
-        <v>6458</v>
+        <v>7427</v>
       </c>
       <c r="L45" s="89">
         <f>Jan!L45+Feb!L45+Mar!L45+Apr!L45+May!L45+June!L45+July!L45+Aug!L45+Sep!L45+Oct!L45+Nov!L45+Dec!L45</f>
-        <v>7049</v>
+        <v>8914</v>
       </c>
       <c r="M45" s="89">
         <f>Jan!M45+Feb!M45+Mar!M45+Apr!M45+May!M45+June!M45+July!M45+Aug!M45+Sep!M45+Oct!M45+Nov!M45+Dec!M45</f>
@@ -4660,19 +4660,19 @@
       </c>
       <c r="N45" s="89">
         <f>Jan!N45+Feb!N45+Mar!N45+Apr!N45+May!N45+June!N45+July!N45+Aug!N45+Sep!N45+Oct!N45+Nov!N45+Dec!N45</f>
-        <v>230</v>
+        <v>273</v>
       </c>
       <c r="O45" s="89">
         <f>Jan!O45+Feb!O45+Mar!O45+Apr!O45+May!O45+June!O45+July!O45+Aug!O45+Sep!O45+Oct!O45+Nov!O45+Dec!O45</f>
-        <v>3602</v>
+        <v>4031</v>
       </c>
       <c r="P45" s="89">
         <f>Jan!P45+Feb!P45+Mar!P45+Apr!P45+May!P45+June!P45+July!P45+Aug!P45+Sep!P45+Oct!P45+Nov!P45+Dec!P45</f>
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="Q45" s="89">
         <f>Jan!Q45+Feb!Q45+Mar!Q45+Apr!Q45+May!Q45+June!Q45+July!Q45+Aug!Q45+Sep!Q45+Oct!Q45+Nov!Q45+Dec!Q45</f>
-        <v>4621</v>
+        <v>5180</v>
       </c>
       <c r="R45" s="89">
         <f>Jan!R45+Feb!R45+Mar!R45+Apr!R45+May!R45+June!R45+July!R45+Aug!R45+Sep!R45+Oct!R45+Nov!R45+Dec!R45</f>
@@ -4693,7 +4693,7 @@
       <c r="F46" s="22"/>
       <c r="G46" s="91">
         <f>Jan!G46+Feb!G46+Mar!G46+Apr!G46+May!G46+June!G46+July!G46+Aug!G46+Sep!G46+Oct!G46+Nov!G46+Dec!G46</f>
-        <v>142661</v>
+        <v>166307</v>
       </c>
       <c r="H46" s="92">
         <f>Jan!H46+Feb!H46+Mar!H46+Apr!H46+May!H46+June!H46+July!H46+Aug!H46+Sep!H46+Oct!H46+Nov!H46+Dec!H46</f>
@@ -4701,19 +4701,19 @@
       </c>
       <c r="I46" s="93">
         <f>Jan!I46+Feb!I46+Mar!I46+Apr!I46+May!I46+June!I46+July!I46+Aug!I46+Sep!I46+Oct!I46+Nov!I46+Dec!I46</f>
-        <v>73579</v>
+        <v>85674</v>
       </c>
       <c r="J46" s="94">
         <f>Jan!J46+Feb!J46+Mar!J46+Apr!J46+May!J46+June!J46+July!J46+Aug!J46+Sep!J46+Oct!J46+Nov!J46+Dec!J46</f>
-        <v>6756</v>
+        <v>7575</v>
       </c>
       <c r="K46" s="94">
         <f>Jan!K46+Feb!K46+Mar!K46+Apr!K46+May!K46+June!K46+July!K46+Aug!K46+Sep!K46+Oct!K46+Nov!K46+Dec!K46</f>
-        <v>35576</v>
+        <v>41871</v>
       </c>
       <c r="L46" s="94">
         <f>Jan!L46+Feb!L46+Mar!L46+Apr!L46+May!L46+June!L46+July!L46+Aug!L46+Sep!L46+Oct!L46+Nov!L46+Dec!L46</f>
-        <v>7049</v>
+        <v>8914</v>
       </c>
       <c r="M46" s="94">
         <f>Jan!M46+Feb!M46+Mar!M46+Apr!M46+May!M46+June!M46+July!M46+Aug!M46+Sep!M46+Oct!M46+Nov!M46+Dec!M46</f>
@@ -4721,19 +4721,19 @@
       </c>
       <c r="N46" s="94">
         <f>Jan!N46+Feb!N46+Mar!N46+Apr!N46+May!N46+June!N46+July!N46+Aug!N46+Sep!N46+Oct!N46+Nov!N46+Dec!N46</f>
-        <v>9987</v>
+        <v>11385</v>
       </c>
       <c r="O46" s="94">
         <f>Jan!O46+Feb!O46+Mar!O46+Apr!O46+May!O46+June!O46+July!O46+Aug!O46+Sep!O46+Oct!O46+Nov!O46+Dec!O46</f>
-        <v>4787</v>
+        <v>5380</v>
       </c>
       <c r="P46" s="94">
         <f>Jan!P46+Feb!P46+Mar!P46+Apr!P46+May!P46+June!P46+July!P46+Aug!P46+Sep!P46+Oct!P46+Nov!P46+Dec!P46</f>
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="Q46" s="94">
         <f>Jan!Q46+Feb!Q46+Mar!Q46+Apr!Q46+May!Q46+June!Q46+July!Q46+Aug!Q46+Sep!Q46+Oct!Q46+Nov!Q46+Dec!Q46</f>
-        <v>4621</v>
+        <v>5180</v>
       </c>
       <c r="R46" s="94">
         <f>Jan!R46+Feb!R46+Mar!R46+Apr!R46+May!R46+June!R46+July!R46+Aug!R46+Sep!R46+Oct!R46+Nov!R46+Dec!R46</f>
@@ -4876,7 +4876,7 @@
       <c r="F49" s="20"/>
       <c r="G49" s="79">
         <f>Jan!G49+Feb!G49+Mar!G49+Apr!G49+May!G49+June!G49+July!G49+Aug!G49+Sep!G49+Oct!G49+Nov!G49+Dec!G49</f>
-        <v>30136</v>
+        <v>34801</v>
       </c>
       <c r="H49" s="80">
         <f>Jan!H49+Feb!H49+Mar!H49+Apr!H49+May!H49+June!H49+July!H49+Aug!H49+Sep!H49+Oct!H49+Nov!H49+Dec!H49</f>
@@ -4900,23 +4900,23 @@
       </c>
       <c r="M49" s="82">
         <f>Jan!M49+Feb!M49+Mar!M49+Apr!M49+May!M49+June!M49+July!M49+Aug!M49+Sep!M49+Oct!M49+Nov!M49+Dec!M49</f>
-        <v>1441</v>
+        <v>1734</v>
       </c>
       <c r="N49" s="82">
         <f>Jan!N49+Feb!N49+Mar!N49+Apr!N49+May!N49+June!N49+July!N49+Aug!N49+Sep!N49+Oct!N49+Nov!N49+Dec!N49</f>
-        <v>15864</v>
+        <v>18538</v>
       </c>
       <c r="O49" s="82">
         <f>Jan!O49+Feb!O49+Mar!O49+Apr!O49+May!O49+June!O49+July!O49+Aug!O49+Sep!O49+Oct!O49+Nov!O49+Dec!O49</f>
-        <v>10955</v>
+        <v>12253</v>
       </c>
       <c r="P49" s="82">
         <f>Jan!P49+Feb!P49+Mar!P49+Apr!P49+May!P49+June!P49+July!P49+Aug!P49+Sep!P49+Oct!P49+Nov!P49+Dec!P49</f>
-        <v>1008</v>
+        <v>1297</v>
       </c>
       <c r="Q49" s="82">
         <f>Jan!Q49+Feb!Q49+Mar!Q49+Apr!Q49+May!Q49+June!Q49+July!Q49+Aug!Q49+Sep!Q49+Oct!Q49+Nov!Q49+Dec!Q49</f>
-        <v>858</v>
+        <v>969</v>
       </c>
       <c r="R49" s="82">
         <f>Jan!R49+Feb!R49+Mar!R49+Apr!R49+May!R49+June!R49+July!R49+Aug!R49+Sep!R49+Oct!R49+Nov!R49+Dec!R49</f>
@@ -4937,7 +4937,7 @@
       <c r="F50" s="20"/>
       <c r="G50" s="79">
         <f>Jan!G50+Feb!G50+Mar!G50+Apr!G50+May!G50+June!G50+July!G50+Aug!G50+Sep!G50+Oct!G50+Nov!G50+Dec!G50</f>
-        <v>3753</v>
+        <v>4143</v>
       </c>
       <c r="H50" s="80">
         <f>Jan!H50+Feb!H50+Mar!H50+Apr!H50+May!H50+June!H50+July!H50+Aug!H50+Sep!H50+Oct!H50+Nov!H50+Dec!H50</f>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="S50" s="84">
         <f>Jan!S50+Feb!S50+Mar!S50+Apr!S50+May!S50+June!S50+July!S50+Aug!S50+Sep!S50+Oct!S50+Nov!S50+Dec!S50</f>
-        <v>3753</v>
+        <v>4143</v>
       </c>
     </row>
     <row r="51" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -4998,7 +4998,7 @@
       <c r="F51" s="20"/>
       <c r="G51" s="79">
         <f>Jan!G51+Feb!G51+Mar!G51+Apr!G51+May!G51+June!G51+July!G51+Aug!G51+Sep!G51+Oct!G51+Nov!G51+Dec!G51</f>
-        <v>5736</v>
+        <v>7037</v>
       </c>
       <c r="H51" s="80">
         <f>Jan!H51+Feb!H51+Mar!H51+Apr!H51+May!H51+June!H51+July!H51+Aug!H51+Sep!H51+Oct!H51+Nov!H51+Dec!H51</f>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="S51" s="84">
         <f>Jan!S51+Feb!S51+Mar!S51+Apr!S51+May!S51+June!S51+July!S51+Aug!S51+Sep!S51+Oct!S51+Nov!S51+Dec!S51</f>
-        <v>5736</v>
+        <v>7037</v>
       </c>
     </row>
     <row r="52" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -5059,7 +5059,7 @@
       <c r="F52" s="19"/>
       <c r="G52" s="79">
         <f>Jan!G52+Feb!G52+Mar!G52+Apr!G52+May!G52+June!G52+July!G52+Aug!G52+Sep!G52+Oct!G52+Nov!G52+Dec!G52</f>
-        <v>2105</v>
+        <v>2529</v>
       </c>
       <c r="H52" s="80">
         <f>Jan!H52+Feb!H52+Mar!H52+Apr!H52+May!H52+June!H52+July!H52+Aug!H52+Sep!H52+Oct!H52+Nov!H52+Dec!H52</f>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="M52" s="82">
         <f>Jan!M52+Feb!M52+Mar!M52+Apr!M52+May!M52+June!M52+July!M52+Aug!M52+Sep!M52+Oct!M52+Nov!M52+Dec!M52</f>
-        <v>1907</v>
+        <v>2161</v>
       </c>
       <c r="N52" s="82">
         <f>Jan!N52+Feb!N52+Mar!N52+Apr!N52+May!N52+June!N52+July!N52+Aug!N52+Sep!N52+Oct!N52+Nov!N52+Dec!N52</f>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="S52" s="84">
         <f>Jan!S52+Feb!S52+Mar!S52+Apr!S52+May!S52+June!S52+July!S52+Aug!S52+Sep!S52+Oct!S52+Nov!S52+Dec!S52</f>
-        <v>198</v>
+        <v>368</v>
       </c>
     </row>
     <row r="53" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -5120,7 +5120,7 @@
       <c r="F53" s="19"/>
       <c r="G53" s="79">
         <f>Jan!G53+Feb!G53+Mar!G53+Apr!G53+May!G53+June!G53+July!G53+Aug!G53+Sep!G53+Oct!G53+Nov!G53+Dec!G53</f>
-        <v>11439</v>
+        <v>13017</v>
       </c>
       <c r="H53" s="80">
         <f>Jan!H53+Feb!H53+Mar!H53+Apr!H53+May!H53+June!H53+July!H53+Aug!H53+Sep!H53+Oct!H53+Nov!H53+Dec!H53</f>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="S53" s="84">
         <f>Jan!S53+Feb!S53+Mar!S53+Apr!S53+May!S53+June!S53+July!S53+Aug!S53+Sep!S53+Oct!S53+Nov!S53+Dec!S53</f>
-        <v>11439</v>
+        <v>13017</v>
       </c>
     </row>
     <row r="54" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -5181,7 +5181,7 @@
       <c r="F54" s="20"/>
       <c r="G54" s="79">
         <f>Jan!G54+Feb!G54+Mar!G54+Apr!G54+May!G54+June!G54+July!G54+Aug!G54+Sep!G54+Oct!G54+Nov!G54+Dec!G54</f>
-        <v>20289</v>
+        <v>23008</v>
       </c>
       <c r="H54" s="80">
         <f>Jan!H54+Feb!H54+Mar!H54+Apr!H54+May!H54+June!H54+July!H54+Aug!H54+Sep!H54+Oct!H54+Nov!H54+Dec!H54</f>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="K54" s="82">
         <f>Jan!K54+Feb!K54+Mar!K54+Apr!K54+May!K54+June!K54+July!K54+Aug!K54+Sep!K54+Oct!K54+Nov!K54+Dec!K54</f>
-        <v>6056</v>
+        <v>6770</v>
       </c>
       <c r="L54" s="82">
         <f>Jan!L54+Feb!L54+Mar!L54+Apr!L54+May!L54+June!L54+July!L54+Aug!L54+Sep!L54+Oct!L54+Nov!L54+Dec!L54</f>
@@ -5205,23 +5205,23 @@
       </c>
       <c r="M54" s="82">
         <f>Jan!M54+Feb!M54+Mar!M54+Apr!M54+May!M54+June!M54+July!M54+Aug!M54+Sep!M54+Oct!M54+Nov!M54+Dec!M54</f>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N54" s="82">
         <f>Jan!N54+Feb!N54+Mar!N54+Apr!N54+May!N54+June!N54+July!N54+Aug!N54+Sep!N54+Oct!N54+Nov!N54+Dec!N54</f>
-        <v>8214</v>
+        <v>9432</v>
       </c>
       <c r="O54" s="82">
         <f>Jan!O54+Feb!O54+Mar!O54+Apr!O54+May!O54+June!O54+July!O54+Aug!O54+Sep!O54+Oct!O54+Nov!O54+Dec!O54</f>
-        <v>2598</v>
+        <v>2996</v>
       </c>
       <c r="P54" s="82">
         <f>Jan!P54+Feb!P54+Mar!P54+Apr!P54+May!P54+June!P54+July!P54+Aug!P54+Sep!P54+Oct!P54+Nov!P54+Dec!P54</f>
-        <v>623</v>
+        <v>715</v>
       </c>
       <c r="Q54" s="82">
         <f>Jan!Q54+Feb!Q54+Mar!Q54+Apr!Q54+May!Q54+June!Q54+July!Q54+Aug!Q54+Sep!Q54+Oct!Q54+Nov!Q54+Dec!Q54</f>
-        <v>2745</v>
+        <v>3033</v>
       </c>
       <c r="R54" s="82">
         <f>Jan!R54+Feb!R54+Mar!R54+Apr!R54+May!R54+June!R54+July!R54+Aug!R54+Sep!R54+Oct!R54+Nov!R54+Dec!R54</f>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="S54" s="84">
         <f>Jan!S54+Feb!S54+Mar!S54+Apr!S54+May!S54+June!S54+July!S54+Aug!S54+Sep!S54+Oct!S54+Nov!S54+Dec!S54</f>
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -5242,7 +5242,7 @@
       <c r="F55" s="59"/>
       <c r="G55" s="79">
         <f>Jan!G55+Feb!G55+Mar!G55+Apr!G55+May!G55+June!G55+July!G55+Aug!G55+Sep!G55+Oct!G55+Nov!G55+Dec!G55</f>
-        <v>27167</v>
+        <v>32124</v>
       </c>
       <c r="H55" s="80">
         <f>Jan!H55+Feb!H55+Mar!H55+Apr!H55+May!H55+June!H55+July!H55+Aug!H55+Sep!H55+Oct!H55+Nov!H55+Dec!H55</f>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="K55" s="82">
         <f>Jan!K55+Feb!K55+Mar!K55+Apr!K55+May!K55+June!K55+July!K55+Aug!K55+Sep!K55+Oct!K55+Nov!K55+Dec!K55</f>
-        <v>7395</v>
+        <v>8515</v>
       </c>
       <c r="L55" s="82">
         <f>Jan!L55+Feb!L55+Mar!L55+Apr!L55+May!L55+June!L55+July!L55+Aug!L55+Sep!L55+Oct!L55+Nov!L55+Dec!L55</f>
@@ -5270,19 +5270,19 @@
       </c>
       <c r="N55" s="82">
         <f>Jan!N55+Feb!N55+Mar!N55+Apr!N55+May!N55+June!N55+July!N55+Aug!N55+Sep!N55+Oct!N55+Nov!N55+Dec!N55</f>
-        <v>5764</v>
+        <v>6633</v>
       </c>
       <c r="O55" s="82">
         <f>Jan!O55+Feb!O55+Mar!O55+Apr!O55+May!O55+June!O55+July!O55+Aug!O55+Sep!O55+Oct!O55+Nov!O55+Dec!O55</f>
-        <v>3683</v>
+        <v>4118</v>
       </c>
       <c r="P55" s="82">
         <f>Jan!P55+Feb!P55+Mar!P55+Apr!P55+May!P55+June!P55+July!P55+Aug!P55+Sep!P55+Oct!P55+Nov!P55+Dec!P55</f>
-        <v>864</v>
+        <v>971</v>
       </c>
       <c r="Q55" s="82">
         <f>Jan!Q55+Feb!Q55+Mar!Q55+Apr!Q55+May!Q55+June!Q55+July!Q55+Aug!Q55+Sep!Q55+Oct!Q55+Nov!Q55+Dec!Q55</f>
-        <v>684</v>
+        <v>773</v>
       </c>
       <c r="R55" s="82">
         <f>Jan!R55+Feb!R55+Mar!R55+Apr!R55+May!R55+June!R55+July!R55+Aug!R55+Sep!R55+Oct!R55+Nov!R55+Dec!R55</f>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="S55" s="84">
         <f>Jan!S55+Feb!S55+Mar!S55+Apr!S55+May!S55+June!S55+July!S55+Aug!S55+Sep!S55+Oct!S55+Nov!S55+Dec!S55</f>
-        <v>8777</v>
+        <v>11114</v>
       </c>
     </row>
     <row r="56" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -5303,7 +5303,7 @@
       <c r="F56" s="19"/>
       <c r="G56" s="79">
         <f>Jan!G56+Feb!G56+Mar!G56+Apr!G56+May!G56+June!G56+July!G56+Aug!G56+Sep!G56+Oct!G56+Nov!G56+Dec!G56</f>
-        <v>223</v>
+        <v>279</v>
       </c>
       <c r="H56" s="80">
         <f>Jan!H56+Feb!H56+Mar!H56+Apr!H56+May!H56+June!H56+July!H56+Aug!H56+Sep!H56+Oct!H56+Nov!H56+Dec!H56</f>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="S56" s="84">
         <f>Jan!S56+Feb!S56+Mar!S56+Apr!S56+May!S56+June!S56+July!S56+Aug!S56+Sep!S56+Oct!S56+Nov!S56+Dec!S56</f>
-        <v>223</v>
+        <v>279</v>
       </c>
     </row>
     <row r="57" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -5364,7 +5364,7 @@
       <c r="F57" s="19"/>
       <c r="G57" s="79">
         <f>Jan!G57+Feb!G57+Mar!G57+Apr!G57+May!G57+June!G57+July!G57+Aug!G57+Sep!G57+Oct!G57+Nov!G57+Dec!G57</f>
-        <v>12247</v>
+        <v>13625</v>
       </c>
       <c r="H57" s="80">
         <f>Jan!H57+Feb!H57+Mar!H57+Apr!H57+May!H57+June!H57+July!H57+Aug!H57+Sep!H57+Oct!H57+Nov!H57+Dec!H57</f>
@@ -5392,11 +5392,11 @@
       </c>
       <c r="N57" s="82">
         <f>Jan!N57+Feb!N57+Mar!N57+Apr!N57+May!N57+June!N57+July!N57+Aug!N57+Sep!N57+Oct!N57+Nov!N57+Dec!N57</f>
-        <v>263</v>
+        <v>636</v>
       </c>
       <c r="O57" s="82">
         <f>Jan!O57+Feb!O57+Mar!O57+Apr!O57+May!O57+June!O57+July!O57+Aug!O57+Sep!O57+Oct!O57+Nov!O57+Dec!O57</f>
-        <v>6833</v>
+        <v>7230</v>
       </c>
       <c r="P57" s="82">
         <f>Jan!P57+Feb!P57+Mar!P57+Apr!P57+May!P57+June!P57+July!P57+Aug!P57+Sep!P57+Oct!P57+Nov!P57+Dec!P57</f>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="S57" s="84">
         <f>Jan!S57+Feb!S57+Mar!S57+Apr!S57+May!S57+June!S57+July!S57+Aug!S57+Sep!S57+Oct!S57+Nov!S57+Dec!S57</f>
-        <v>5151</v>
+        <v>5759</v>
       </c>
     </row>
     <row r="58" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -5425,7 +5425,7 @@
       <c r="F58" s="20"/>
       <c r="G58" s="79">
         <f>Jan!G58+Feb!G58+Mar!G58+Apr!G58+May!G58+June!G58+July!G58+Aug!G58+Sep!G58+Oct!G58+Nov!G58+Dec!G58</f>
-        <v>439</v>
+        <v>482</v>
       </c>
       <c r="H58" s="80">
         <f>Jan!H58+Feb!H58+Mar!H58+Apr!H58+May!H58+June!H58+July!H58+Aug!H58+Sep!H58+Oct!H58+Nov!H58+Dec!H58</f>
@@ -5473,7 +5473,7 @@
       </c>
       <c r="S58" s="84">
         <f>Jan!S58+Feb!S58+Mar!S58+Apr!S58+May!S58+June!S58+July!S58+Aug!S58+Sep!S58+Oct!S58+Nov!S58+Dec!S58</f>
-        <v>439</v>
+        <v>482</v>
       </c>
     </row>
     <row r="59" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -5486,7 +5486,7 @@
       <c r="F59" s="20"/>
       <c r="G59" s="86">
         <f>Jan!G59+Feb!G59+Mar!G59+Apr!G59+May!G59+June!G59+July!G59+Aug!G59+Sep!G59+Oct!G59+Nov!G59+Dec!G59</f>
-        <v>4479</v>
+        <v>5389</v>
       </c>
       <c r="H59" s="87">
         <f>Jan!H59+Feb!H59+Mar!H59+Apr!H59+May!H59+June!H59+July!H59+Aug!H59+Sep!H59+Oct!H59+Nov!H59+Dec!H59</f>
@@ -5514,19 +5514,19 @@
       </c>
       <c r="N59" s="89">
         <f>Jan!N59+Feb!N59+Mar!N59+Apr!N59+May!N59+June!N59+July!N59+Aug!N59+Sep!N59+Oct!N59+Nov!N59+Dec!N59</f>
-        <v>522</v>
+        <v>688</v>
       </c>
       <c r="O59" s="89">
         <f>Jan!O59+Feb!O59+Mar!O59+Apr!O59+May!O59+June!O59+July!O59+Aug!O59+Sep!O59+Oct!O59+Nov!O59+Dec!O59</f>
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P59" s="89">
         <f>Jan!P59+Feb!P59+Mar!P59+Apr!P59+May!P59+June!P59+July!P59+Aug!P59+Sep!P59+Oct!P59+Nov!P59+Dec!P59</f>
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Q59" s="89">
         <f>Jan!Q59+Feb!Q59+Mar!Q59+Apr!Q59+May!Q59+June!Q59+July!Q59+Aug!Q59+Sep!Q59+Oct!Q59+Nov!Q59+Dec!Q59</f>
-        <v>3506</v>
+        <v>4213</v>
       </c>
       <c r="R59" s="89">
         <f>Jan!R59+Feb!R59+Mar!R59+Apr!R59+May!R59+June!R59+July!R59+Aug!R59+Sep!R59+Oct!R59+Nov!R59+Dec!R59</f>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="S59" s="101">
         <f>Jan!S59+Feb!S59+Mar!S59+Apr!S59+May!S59+June!S59+July!S59+Aug!S59+Sep!S59+Oct!S59+Nov!S59+Dec!S59</f>
-        <v>242</v>
+        <v>275</v>
       </c>
     </row>
     <row r="60" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -5547,7 +5547,7 @@
       <c r="F60" s="22"/>
       <c r="G60" s="102">
         <f>Jan!G60+Feb!G60+Mar!G60+Apr!G60+May!G60+June!G60+July!G60+Aug!G60+Sep!G60+Oct!G60+Nov!G60+Dec!G60</f>
-        <v>118013</v>
+        <v>136434</v>
       </c>
       <c r="H60" s="103">
         <f>Jan!H60+Feb!H60+Mar!H60+Apr!H60+May!H60+June!H60+July!H60+Aug!H60+Sep!H60+Oct!H60+Nov!H60+Dec!H60</f>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="K60" s="105">
         <f>Jan!K60+Feb!K60+Mar!K60+Apr!K60+May!K60+June!K60+July!K60+Aug!K60+Sep!K60+Oct!K60+Nov!K60+Dec!K60</f>
-        <v>13451</v>
+        <v>15285</v>
       </c>
       <c r="L60" s="105">
         <f>Jan!L60+Feb!L60+Mar!L60+Apr!L60+May!L60+June!L60+July!L60+Aug!L60+Sep!L60+Oct!L60+Nov!L60+Dec!L60</f>
@@ -5571,23 +5571,23 @@
       </c>
       <c r="M60" s="105">
         <f>Jan!M60+Feb!M60+Mar!M60+Apr!M60+May!M60+June!M60+July!M60+Aug!M60+Sep!M60+Oct!M60+Nov!M60+Dec!M60</f>
-        <v>3369</v>
+        <v>3921</v>
       </c>
       <c r="N60" s="105">
         <f>Jan!N60+Feb!N60+Mar!N60+Apr!N60+May!N60+June!N60+July!N60+Aug!N60+Sep!N60+Oct!N60+Nov!N60+Dec!N60</f>
-        <v>30627</v>
+        <v>35927</v>
       </c>
       <c r="O60" s="105">
         <f>Jan!O60+Feb!O60+Mar!O60+Apr!O60+May!O60+June!O60+July!O60+Aug!O60+Sep!O60+Oct!O60+Nov!O60+Dec!O60</f>
-        <v>24228</v>
+        <v>26757</v>
       </c>
       <c r="P60" s="105">
         <f>Jan!P60+Feb!P60+Mar!P60+Apr!P60+May!P60+June!P60+July!P60+Aug!P60+Sep!P60+Oct!P60+Nov!P60+Dec!P60</f>
-        <v>2545</v>
+        <v>3036</v>
       </c>
       <c r="Q60" s="105">
         <f>Jan!Q60+Feb!Q60+Mar!Q60+Apr!Q60+May!Q60+June!Q60+July!Q60+Aug!Q60+Sep!Q60+Oct!Q60+Nov!Q60+Dec!Q60</f>
-        <v>7793</v>
+        <v>8988</v>
       </c>
       <c r="R60" s="105">
         <f>Jan!R60+Feb!R60+Mar!R60+Apr!R60+May!R60+June!R60+July!R60+Aug!R60+Sep!R60+Oct!R60+Nov!R60+Dec!R60</f>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="S60" s="106">
         <f>Jan!S60+Feb!S60+Mar!S60+Apr!S60+May!S60+June!S60+July!S60+Aug!S60+Sep!S60+Oct!S60+Nov!S60+Dec!S60</f>
-        <v>36000</v>
+        <v>42520</v>
       </c>
     </row>
     <row r="61" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -5608,7 +5608,7 @@
       <c r="F61" s="20"/>
       <c r="G61" s="79">
         <f>Jan!G61+Feb!G61+Mar!G61+Apr!G61+May!G61+June!G61+July!G61+Aug!G61+Sep!G61+Oct!G61+Nov!G61+Dec!G61</f>
-        <v>3971</v>
+        <v>4952</v>
       </c>
       <c r="H61" s="80">
         <f>Jan!H61+Feb!H61+Mar!H61+Apr!H61+May!H61+June!H61+July!H61+Aug!H61+Sep!H61+Oct!H61+Nov!H61+Dec!H61</f>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="R61" s="82">
         <f>Jan!R61+Feb!R61+Mar!R61+Apr!R61+May!R61+June!R61+July!R61+Aug!R61+Sep!R61+Oct!R61+Nov!R61+Dec!R61</f>
-        <v>3971</v>
+        <v>4952</v>
       </c>
       <c r="S61" s="84">
         <f>Jan!S61+Feb!S61+Mar!S61+Apr!S61+May!S61+June!S61+July!S61+Aug!S61+Sep!S61+Oct!S61+Nov!S61+Dec!S61</f>
@@ -5669,7 +5669,7 @@
       <c r="F62" s="20"/>
       <c r="G62" s="79">
         <f>Jan!G62+Feb!G62+Mar!G62+Apr!G62+May!G62+June!G62+July!G62+Aug!G62+Sep!G62+Oct!G62+Nov!G62+Dec!G62</f>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="H62" s="80">
         <f>Jan!H62+Feb!H62+Mar!H62+Apr!H62+May!H62+June!H62+July!H62+Aug!H62+Sep!H62+Oct!H62+Nov!H62+Dec!H62</f>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="R62" s="82">
         <f>Jan!R62+Feb!R62+Mar!R62+Apr!R62+May!R62+June!R62+July!R62+Aug!R62+Sep!R62+Oct!R62+Nov!R62+Dec!R62</f>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="S62" s="84">
         <f>Jan!S62+Feb!S62+Mar!S62+Apr!S62+May!S62+June!S62+July!S62+Aug!S62+Sep!S62+Oct!S62+Nov!S62+Dec!S62</f>
@@ -5730,7 +5730,7 @@
       <c r="F63" s="20"/>
       <c r="G63" s="79">
         <f>Jan!G63+Feb!G63+Mar!G63+Apr!G63+May!G63+June!G63+July!G63+Aug!G63+Sep!G63+Oct!G63+Nov!G63+Dec!G63</f>
-        <v>63301</v>
+        <v>73950</v>
       </c>
       <c r="H63" s="80">
         <f>Jan!H63+Feb!H63+Mar!H63+Apr!H63+May!H63+June!H63+July!H63+Aug!H63+Sep!H63+Oct!H63+Nov!H63+Dec!H63</f>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="N63" s="82">
         <f>Jan!N63+Feb!N63+Mar!N63+Apr!N63+May!N63+June!N63+July!N63+Aug!N63+Sep!N63+Oct!N63+Nov!N63+Dec!N63</f>
-        <v>318</v>
+        <v>356</v>
       </c>
       <c r="O63" s="82">
         <f>Jan!O63+Feb!O63+Mar!O63+Apr!O63+May!O63+June!O63+July!O63+Aug!O63+Sep!O63+Oct!O63+Nov!O63+Dec!O63</f>
@@ -5766,15 +5766,15 @@
       </c>
       <c r="P63" s="82">
         <f>Jan!P63+Feb!P63+Mar!P63+Apr!P63+May!P63+June!P63+July!P63+Aug!P63+Sep!P63+Oct!P63+Nov!P63+Dec!P63</f>
-        <v>6112</v>
+        <v>7370</v>
       </c>
       <c r="Q63" s="82">
         <f>Jan!Q63+Feb!Q63+Mar!Q63+Apr!Q63+May!Q63+June!Q63+July!Q63+Aug!Q63+Sep!Q63+Oct!Q63+Nov!Q63+Dec!Q63</f>
-        <v>778</v>
+        <v>998</v>
       </c>
       <c r="R63" s="82">
         <f>Jan!R63+Feb!R63+Mar!R63+Apr!R63+May!R63+June!R63+July!R63+Aug!R63+Sep!R63+Oct!R63+Nov!R63+Dec!R63</f>
-        <v>56091</v>
+        <v>65224</v>
       </c>
       <c r="S63" s="84">
         <f>Jan!S63+Feb!S63+Mar!S63+Apr!S63+May!S63+June!S63+July!S63+Aug!S63+Sep!S63+Oct!S63+Nov!S63+Dec!S63</f>
@@ -5791,7 +5791,7 @@
       <c r="F64" s="20"/>
       <c r="G64" s="79">
         <f>Jan!G64+Feb!G64+Mar!G64+Apr!G64+May!G64+June!G64+July!G64+Aug!G64+Sep!G64+Oct!G64+Nov!G64+Dec!G64</f>
-        <v>65049</v>
+        <v>76546</v>
       </c>
       <c r="H64" s="80">
         <f>Jan!H64+Feb!H64+Mar!H64+Apr!H64+May!H64+June!H64+July!H64+Aug!H64+Sep!H64+Oct!H64+Nov!H64+Dec!H64</f>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="N64" s="82">
         <f>Jan!N64+Feb!N64+Mar!N64+Apr!N64+May!N64+June!N64+July!N64+Aug!N64+Sep!N64+Oct!N64+Nov!N64+Dec!N64</f>
-        <v>814</v>
+        <v>890</v>
       </c>
       <c r="O64" s="82">
         <f>Jan!O64+Feb!O64+Mar!O64+Apr!O64+May!O64+June!O64+July!O64+Aug!O64+Sep!O64+Oct!O64+Nov!O64+Dec!O64</f>
@@ -5827,15 +5827,15 @@
       </c>
       <c r="P64" s="82">
         <f>Jan!P64+Feb!P64+Mar!P64+Apr!P64+May!P64+June!P64+July!P64+Aug!P64+Sep!P64+Oct!P64+Nov!P64+Dec!P64</f>
-        <v>1766</v>
+        <v>2216</v>
       </c>
       <c r="Q64" s="82">
         <f>Jan!Q64+Feb!Q64+Mar!Q64+Apr!Q64+May!Q64+June!Q64+July!Q64+Aug!Q64+Sep!Q64+Oct!Q64+Nov!Q64+Dec!Q64</f>
-        <v>519</v>
+        <v>618</v>
       </c>
       <c r="R64" s="82">
         <f>Jan!R64+Feb!R64+Mar!R64+Apr!R64+May!R64+June!R64+July!R64+Aug!R64+Sep!R64+Oct!R64+Nov!R64+Dec!R64</f>
-        <v>61950</v>
+        <v>72822</v>
       </c>
       <c r="S64" s="84">
         <f>Jan!S64+Feb!S64+Mar!S64+Apr!S64+May!S64+June!S64+July!S64+Aug!S64+Sep!S64+Oct!S64+Nov!S64+Dec!S64</f>
@@ -5852,7 +5852,7 @@
       <c r="F65" s="20"/>
       <c r="G65" s="79">
         <f>Jan!G65+Feb!G65+Mar!G65+Apr!G65+May!G65+June!G65+July!G65+Aug!G65+Sep!G65+Oct!G65+Nov!G65+Dec!G65</f>
-        <v>35233</v>
+        <v>40661</v>
       </c>
       <c r="H65" s="80">
         <f>Jan!H65+Feb!H65+Mar!H65+Apr!H65+May!H65+June!H65+July!H65+Aug!H65+Sep!H65+Oct!H65+Nov!H65+Dec!H65</f>
@@ -5876,27 +5876,27 @@
       </c>
       <c r="M65" s="82">
         <f>Jan!M65+Feb!M65+Mar!M65+Apr!M65+May!M65+June!M65+July!M65+Aug!M65+Sep!M65+Oct!M65+Nov!M65+Dec!M65</f>
-        <v>197</v>
+        <v>283</v>
       </c>
       <c r="N65" s="82">
         <f>Jan!N65+Feb!N65+Mar!N65+Apr!N65+May!N65+June!N65+July!N65+Aug!N65+Sep!N65+Oct!N65+Nov!N65+Dec!N65</f>
-        <v>1278</v>
+        <v>1481</v>
       </c>
       <c r="O65" s="82">
         <f>Jan!O65+Feb!O65+Mar!O65+Apr!O65+May!O65+June!O65+July!O65+Aug!O65+Sep!O65+Oct!O65+Nov!O65+Dec!O65</f>
-        <v>1505</v>
+        <v>1618</v>
       </c>
       <c r="P65" s="82">
         <f>Jan!P65+Feb!P65+Mar!P65+Apr!P65+May!P65+June!P65+July!P65+Aug!P65+Sep!P65+Oct!P65+Nov!P65+Dec!P65</f>
-        <v>327</v>
+        <v>385</v>
       </c>
       <c r="Q65" s="82">
         <f>Jan!Q65+Feb!Q65+Mar!Q65+Apr!Q65+May!Q65+June!Q65+July!Q65+Aug!Q65+Sep!Q65+Oct!Q65+Nov!Q65+Dec!Q65</f>
-        <v>466</v>
+        <v>544</v>
       </c>
       <c r="R65" s="82">
         <f>Jan!R65+Feb!R65+Mar!R65+Apr!R65+May!R65+June!R65+July!R65+Aug!R65+Sep!R65+Oct!R65+Nov!R65+Dec!R65</f>
-        <v>31460</v>
+        <v>36350</v>
       </c>
       <c r="S65" s="84">
         <f>Jan!S65+Feb!S65+Mar!S65+Apr!S65+May!S65+June!S65+July!S65+Aug!S65+Sep!S65+Oct!S65+Nov!S65+Dec!S65</f>
@@ -5913,7 +5913,7 @@
       <c r="F66" s="20"/>
       <c r="G66" s="79">
         <f>Jan!G66+Feb!G66+Mar!G66+Apr!G66+May!G66+June!G66+July!G66+Aug!G66+Sep!G66+Oct!G66+Nov!G66+Dec!G66</f>
-        <v>2519</v>
+        <v>3181</v>
       </c>
       <c r="H66" s="80">
         <f>Jan!H66+Feb!H66+Mar!H66+Apr!H66+May!H66+June!H66+July!H66+Aug!H66+Sep!H66+Oct!H66+Nov!H66+Dec!H66</f>
@@ -5953,11 +5953,11 @@
       </c>
       <c r="Q66" s="82">
         <f>Jan!Q66+Feb!Q66+Mar!Q66+Apr!Q66+May!Q66+June!Q66+July!Q66+Aug!Q66+Sep!Q66+Oct!Q66+Nov!Q66+Dec!Q66</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R66" s="82">
         <f>Jan!R66+Feb!R66+Mar!R66+Apr!R66+May!R66+June!R66+July!R66+Aug!R66+Sep!R66+Oct!R66+Nov!R66+Dec!R66</f>
-        <v>2513</v>
+        <v>3169</v>
       </c>
       <c r="S66" s="84">
         <f>Jan!S66+Feb!S66+Mar!S66+Apr!S66+May!S66+June!S66+July!S66+Aug!S66+Sep!S66+Oct!S66+Nov!S66+Dec!S66</f>
@@ -6035,7 +6035,7 @@
       <c r="F68" s="20"/>
       <c r="G68" s="86">
         <f>Jan!G68+Feb!G68+Mar!G68+Apr!G68+May!G68+June!G68+July!G68+Aug!G68+Sep!G68+Oct!G68+Nov!G68+Dec!G68</f>
-        <v>425</v>
+        <v>496</v>
       </c>
       <c r="H68" s="87">
         <f>Jan!H68+Feb!H68+Mar!H68+Apr!H68+May!H68+June!H68+July!H68+Aug!H68+Sep!H68+Oct!H68+Nov!H68+Dec!H68</f>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="R68" s="89">
         <f>Jan!R68+Feb!R68+Mar!R68+Apr!R68+May!R68+June!R68+July!R68+Aug!R68+Sep!R68+Oct!R68+Nov!R68+Dec!R68</f>
-        <v>425</v>
+        <v>496</v>
       </c>
       <c r="S68" s="101">
         <f>Jan!S68+Feb!S68+Mar!S68+Apr!S68+May!S68+June!S68+July!S68+Aug!S68+Sep!S68+Oct!S68+Nov!S68+Dec!S68</f>
@@ -6096,7 +6096,7 @@
       <c r="F69" s="22"/>
       <c r="G69" s="102">
         <f>Jan!G69+Feb!G69+Mar!G69+Apr!G69+May!G69+June!G69+July!G69+Aug!G69+Sep!G69+Oct!G69+Nov!G69+Dec!G69</f>
-        <v>170498</v>
+        <v>199864</v>
       </c>
       <c r="H69" s="103">
         <f>Jan!H69+Feb!H69+Mar!H69+Apr!H69+May!H69+June!H69+July!H69+Aug!H69+Sep!H69+Oct!H69+Nov!H69+Dec!H69</f>
@@ -6120,27 +6120,27 @@
       </c>
       <c r="M69" s="105">
         <f>Jan!M69+Feb!M69+Mar!M69+Apr!M69+May!M69+June!M69+July!M69+Aug!M69+Sep!M69+Oct!M69+Nov!M69+Dec!M69</f>
-        <v>199</v>
+        <v>285</v>
       </c>
       <c r="N69" s="105">
         <f>Jan!N69+Feb!N69+Mar!N69+Apr!N69+May!N69+June!N69+July!N69+Aug!N69+Sep!N69+Oct!N69+Nov!N69+Dec!N69</f>
-        <v>2410</v>
+        <v>2727</v>
       </c>
       <c r="O69" s="105">
         <f>Jan!O69+Feb!O69+Mar!O69+Apr!O69+May!O69+June!O69+July!O69+Aug!O69+Sep!O69+Oct!O69+Nov!O69+Dec!O69</f>
-        <v>1505</v>
+        <v>1618</v>
       </c>
       <c r="P69" s="105">
         <f>Jan!P69+Feb!P69+Mar!P69+Apr!P69+May!P69+June!P69+July!P69+Aug!P69+Sep!P69+Oct!P69+Nov!P69+Dec!P69</f>
-        <v>8205</v>
+        <v>9971</v>
       </c>
       <c r="Q69" s="105">
         <f>Jan!Q69+Feb!Q69+Mar!Q69+Apr!Q69+May!Q69+June!Q69+July!Q69+Aug!Q69+Sep!Q69+Oct!Q69+Nov!Q69+Dec!Q69</f>
-        <v>1769</v>
+        <v>2172</v>
       </c>
       <c r="R69" s="105">
         <f>Jan!R69+Feb!R69+Mar!R69+Apr!R69+May!R69+June!R69+July!R69+Aug!R69+Sep!R69+Oct!R69+Nov!R69+Dec!R69</f>
-        <v>156410</v>
+        <v>183091</v>
       </c>
       <c r="S69" s="106">
         <f>Jan!S69+Feb!S69+Mar!S69+Apr!S69+May!S69+June!S69+July!S69+Aug!S69+Sep!S69+Oct!S69+Nov!S69+Dec!S69</f>
@@ -6157,7 +6157,7 @@
       <c r="F70" s="19"/>
       <c r="G70" s="96">
         <f>Jan!G70+Feb!G70+Mar!G70+Apr!G70+May!G70+June!G70+July!G70+Aug!G70+Sep!G70+Oct!G70+Nov!G70+Dec!G70</f>
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="H70" s="97">
         <f>Jan!H70+Feb!H70+Mar!H70+Apr!H70+May!H70+June!H70+July!H70+Aug!H70+Sep!H70+Oct!H70+Nov!H70+Dec!H70</f>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="Q70" s="99">
         <f>Jan!Q70+Feb!Q70+Mar!Q70+Apr!Q70+May!Q70+June!Q70+July!Q70+Aug!Q70+Sep!Q70+Oct!Q70+Nov!Q70+Dec!Q70</f>
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="R70" s="99">
         <f>Jan!R70+Feb!R70+Mar!R70+Apr!R70+May!R70+June!R70+July!R70+Aug!R70+Sep!R70+Oct!R70+Nov!R70+Dec!R70</f>
@@ -6218,7 +6218,7 @@
       <c r="F71" s="22"/>
       <c r="G71" s="91">
         <f>Jan!G71+Feb!G71+Mar!G71+Apr!G71+May!G71+June!G71+July!G71+Aug!G71+Sep!G71+Oct!G71+Nov!G71+Dec!G71</f>
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="H71" s="92">
         <f>Jan!H71+Feb!H71+Mar!H71+Apr!H71+May!H71+June!H71+July!H71+Aug!H71+Sep!H71+Oct!H71+Nov!H71+Dec!H71</f>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="Q71" s="94">
         <f>Jan!Q71+Feb!Q71+Mar!Q71+Apr!Q71+May!Q71+June!Q71+July!Q71+Aug!Q71+Sep!Q71+Oct!Q71+Nov!Q71+Dec!Q71</f>
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="R71" s="94">
         <f>Jan!R71+Feb!R71+Mar!R71+Apr!R71+May!R71+June!R71+July!R71+Aug!R71+Sep!R71+Oct!R71+Nov!R71+Dec!R71</f>
@@ -6299,7 +6299,7 @@
       <c r="F73" s="19"/>
       <c r="G73" s="74">
         <f>Jan!G73+Feb!G73+Mar!G73+Apr!G73+May!G73+June!G73+July!G73+Aug!G73+Sep!G73+Oct!G73+Nov!G73+Dec!G73</f>
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="H73" s="75">
         <f>Jan!H73+Feb!H73+Mar!H73+Apr!H73+May!H73+June!H73+July!H73+Aug!H73+Sep!H73+Oct!H73+Nov!H73+Dec!H73</f>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="Q73" s="77">
         <f>Jan!Q73+Feb!Q73+Mar!Q73+Apr!Q73+May!Q73+June!Q73+July!Q73+Aug!Q73+Sep!Q73+Oct!Q73+Nov!Q73+Dec!Q73</f>
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="R73" s="77">
         <f>Jan!R73+Feb!R73+Mar!R73+Apr!R73+May!R73+June!R73+July!R73+Aug!R73+Sep!R73+Oct!R73+Nov!R73+Dec!R73</f>
@@ -6360,7 +6360,7 @@
       <c r="F74" s="19"/>
       <c r="G74" s="79">
         <f>Jan!G74+Feb!G74+Mar!G74+Apr!G74+May!G74+June!G74+July!G74+Aug!G74+Sep!G74+Oct!G74+Nov!G74+Dec!G74</f>
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="H74" s="80">
         <f>Jan!H74+Feb!H74+Mar!H74+Apr!H74+May!H74+June!H74+July!H74+Aug!H74+Sep!H74+Oct!H74+Nov!H74+Dec!H74</f>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="Q74" s="82">
         <f>Jan!Q74+Feb!Q74+Mar!Q74+Apr!Q74+May!Q74+June!Q74+July!Q74+Aug!Q74+Sep!Q74+Oct!Q74+Nov!Q74+Dec!Q74</f>
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="R74" s="82">
         <f>Jan!R74+Feb!R74+Mar!R74+Apr!R74+May!R74+June!R74+July!R74+Aug!R74+Sep!R74+Oct!R74+Nov!R74+Dec!R74</f>
@@ -6421,7 +6421,7 @@
       <c r="F75" s="19"/>
       <c r="G75" s="79">
         <f>Jan!G75+Feb!G75+Mar!G75+Apr!G75+May!G75+June!G75+July!G75+Aug!G75+Sep!G75+Oct!G75+Nov!G75+Dec!G75</f>
-        <v>2186</v>
+        <v>3269</v>
       </c>
       <c r="H75" s="80">
         <f>Jan!H75+Feb!H75+Mar!H75+Apr!H75+May!H75+June!H75+July!H75+Aug!H75+Sep!H75+Oct!H75+Nov!H75+Dec!H75</f>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="M75" s="82">
         <f>Jan!M75+Feb!M75+Mar!M75+Apr!M75+May!M75+June!M75+July!M75+Aug!M75+Sep!M75+Oct!M75+Nov!M75+Dec!M75</f>
-        <v>1642</v>
+        <v>2686</v>
       </c>
       <c r="N75" s="82">
         <f>Jan!N75+Feb!N75+Mar!N75+Apr!N75+May!N75+June!N75+July!N75+Aug!N75+Sep!N75+Oct!N75+Nov!N75+Dec!N75</f>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="Q75" s="82">
         <f>Jan!Q75+Feb!Q75+Mar!Q75+Apr!Q75+May!Q75+June!Q75+July!Q75+Aug!Q75+Sep!Q75+Oct!Q75+Nov!Q75+Dec!Q75</f>
-        <v>544</v>
+        <v>583</v>
       </c>
       <c r="R75" s="82">
         <f>Jan!R75+Feb!R75+Mar!R75+Apr!R75+May!R75+June!R75+July!R75+Aug!R75+Sep!R75+Oct!R75+Nov!R75+Dec!R75</f>
@@ -6543,7 +6543,7 @@
       <c r="F77" s="19"/>
       <c r="G77" s="79">
         <f>Jan!G77+Feb!G77+Mar!G77+Apr!G77+May!G77+June!G77+July!G77+Aug!G77+Sep!G77+Oct!G77+Nov!G77+Dec!G77</f>
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="H77" s="80">
         <f>Jan!H77+Feb!H77+Mar!H77+Apr!H77+May!H77+June!H77+July!H77+Aug!H77+Sep!H77+Oct!H77+Nov!H77+Dec!H77</f>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="Q77" s="82">
         <f>Jan!Q77+Feb!Q77+Mar!Q77+Apr!Q77+May!Q77+June!Q77+July!Q77+Aug!Q77+Sep!Q77+Oct!Q77+Nov!Q77+Dec!Q77</f>
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="R77" s="82">
         <f>Jan!R77+Feb!R77+Mar!R77+Apr!R77+May!R77+June!R77+July!R77+Aug!R77+Sep!R77+Oct!R77+Nov!R77+Dec!R77</f>
@@ -6665,7 +6665,7 @@
       <c r="F79" s="19"/>
       <c r="G79" s="79">
         <f>Jan!G79+Feb!G79+Mar!G79+Apr!G79+May!G79+June!G79+July!G79+Aug!G79+Sep!G79+Oct!G79+Nov!G79+Dec!G79</f>
-        <v>16575</v>
+        <v>20186</v>
       </c>
       <c r="H79" s="80">
         <f>Jan!H79+Feb!H79+Mar!H79+Apr!H79+May!H79+June!H79+July!H79+Aug!H79+Sep!H79+Oct!H79+Nov!H79+Dec!H79</f>
@@ -6689,11 +6689,11 @@
       </c>
       <c r="M79" s="82">
         <f>Jan!M79+Feb!M79+Mar!M79+Apr!M79+May!M79+June!M79+July!M79+Aug!M79+Sep!M79+Oct!M79+Nov!M79+Dec!M79</f>
-        <v>10328</v>
+        <v>12618</v>
       </c>
       <c r="N79" s="82">
         <f>Jan!N79+Feb!N79+Mar!N79+Apr!N79+May!N79+June!N79+July!N79+Aug!N79+Sep!N79+Oct!N79+Nov!N79+Dec!N79</f>
-        <v>2260</v>
+        <v>2845</v>
       </c>
       <c r="O79" s="82">
         <f>Jan!O79+Feb!O79+Mar!O79+Apr!O79+May!O79+June!O79+July!O79+Aug!O79+Sep!O79+Oct!O79+Nov!O79+Dec!O79</f>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Q79" s="82">
         <f>Jan!Q79+Feb!Q79+Mar!Q79+Apr!Q79+May!Q79+June!Q79+July!Q79+Aug!Q79+Sep!Q79+Oct!Q79+Nov!Q79+Dec!Q79</f>
-        <v>3987</v>
+        <v>4723</v>
       </c>
       <c r="R79" s="82">
         <f>Jan!R79+Feb!R79+Mar!R79+Apr!R79+May!R79+June!R79+July!R79+Aug!R79+Sep!R79+Oct!R79+Nov!R79+Dec!R79</f>
@@ -6726,7 +6726,7 @@
       <c r="F80" s="19"/>
       <c r="G80" s="79">
         <f>Jan!G80+Feb!G80+Mar!G80+Apr!G80+May!G80+June!G80+July!G80+Aug!G80+Sep!G80+Oct!G80+Nov!G80+Dec!G80</f>
-        <v>923</v>
+        <v>1050</v>
       </c>
       <c r="H80" s="80">
         <f>Jan!H80+Feb!H80+Mar!H80+Apr!H80+May!H80+June!H80+July!H80+Aug!H80+Sep!H80+Oct!H80+Nov!H80+Dec!H80</f>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="O80" s="82">
         <f>Jan!O80+Feb!O80+Mar!O80+Apr!O80+May!O80+June!O80+July!O80+Aug!O80+Sep!O80+Oct!O80+Nov!O80+Dec!O80</f>
-        <v>923</v>
+        <v>1050</v>
       </c>
       <c r="P80" s="82">
         <f>Jan!P80+Feb!P80+Mar!P80+Apr!P80+May!P80+June!P80+July!P80+Aug!P80+Sep!P80+Oct!P80+Nov!P80+Dec!P80</f>
@@ -6787,7 +6787,7 @@
       <c r="F81" s="19"/>
       <c r="G81" s="79">
         <f>Jan!G81+Feb!G81+Mar!G81+Apr!G81+May!G81+June!G81+July!G81+Aug!G81+Sep!G81+Oct!G81+Nov!G81+Dec!G81</f>
-        <v>4779</v>
+        <v>5675</v>
       </c>
       <c r="H81" s="80">
         <f>Jan!H81+Feb!H81+Mar!H81+Apr!H81+May!H81+June!H81+July!H81+Aug!H81+Sep!H81+Oct!H81+Nov!H81+Dec!H81</f>
@@ -6827,7 +6827,7 @@
       </c>
       <c r="Q81" s="82">
         <f>Jan!Q81+Feb!Q81+Mar!Q81+Apr!Q81+May!Q81+June!Q81+July!Q81+Aug!Q81+Sep!Q81+Oct!Q81+Nov!Q81+Dec!Q81</f>
-        <v>4729</v>
+        <v>5625</v>
       </c>
       <c r="R81" s="82">
         <f>Jan!R81+Feb!R81+Mar!R81+Apr!R81+May!R81+June!R81+July!R81+Aug!R81+Sep!R81+Oct!R81+Nov!R81+Dec!R81</f>
@@ -7092,7 +7092,7 @@
       <c r="F86" s="19"/>
       <c r="G86" s="79">
         <f>Jan!G86+Feb!G86+Mar!G86+Apr!G86+May!G86+June!G86+July!G86+Aug!G86+Sep!G86+Oct!G86+Nov!G86+Dec!G86</f>
-        <v>7284</v>
+        <v>8349</v>
       </c>
       <c r="H86" s="80">
         <f>Jan!H86+Feb!H86+Mar!H86+Apr!H86+May!H86+June!H86+July!H86+Aug!H86+Sep!H86+Oct!H86+Nov!H86+Dec!H86</f>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="M86" s="82">
         <f>Jan!M86+Feb!M86+Mar!M86+Apr!M86+May!M86+June!M86+July!M86+Aug!M86+Sep!M86+Oct!M86+Nov!M86+Dec!M86</f>
-        <v>4157</v>
+        <v>4731</v>
       </c>
       <c r="N86" s="82">
         <f>Jan!N86+Feb!N86+Mar!N86+Apr!N86+May!N86+June!N86+July!N86+Aug!N86+Sep!N86+Oct!N86+Nov!N86+Dec!N86</f>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="O86" s="82">
         <f>Jan!O86+Feb!O86+Mar!O86+Apr!O86+May!O86+June!O86+July!O86+Aug!O86+Sep!O86+Oct!O86+Nov!O86+Dec!O86</f>
-        <v>2154</v>
+        <v>2293</v>
       </c>
       <c r="P86" s="82">
         <f>Jan!P86+Feb!P86+Mar!P86+Apr!P86+May!P86+June!P86+July!P86+Aug!P86+Sep!P86+Oct!P86+Nov!P86+Dec!P86</f>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="Q86" s="82">
         <f>Jan!Q86+Feb!Q86+Mar!Q86+Apr!Q86+May!Q86+June!Q86+July!Q86+Aug!Q86+Sep!Q86+Oct!Q86+Nov!Q86+Dec!Q86</f>
-        <v>973</v>
+        <v>1325</v>
       </c>
       <c r="R86" s="82">
         <f>Jan!R86+Feb!R86+Mar!R86+Apr!R86+May!R86+June!R86+July!R86+Aug!R86+Sep!R86+Oct!R86+Nov!R86+Dec!R86</f>
@@ -7153,7 +7153,7 @@
       <c r="F87" s="19"/>
       <c r="G87" s="79">
         <f>Jan!G87+Feb!G87+Mar!G87+Apr!G87+May!G87+June!G87+July!G87+Aug!G87+Sep!G87+Oct!G87+Nov!G87+Dec!G87</f>
-        <v>2135</v>
+        <v>2276</v>
       </c>
       <c r="H87" s="80">
         <f>Jan!H87+Feb!H87+Mar!H87+Apr!H87+May!H87+June!H87+July!H87+Aug!H87+Sep!H87+Oct!H87+Nov!H87+Dec!H87</f>
@@ -7177,7 +7177,7 @@
       </c>
       <c r="M87" s="82">
         <f>Jan!M87+Feb!M87+Mar!M87+Apr!M87+May!M87+June!M87+July!M87+Aug!M87+Sep!M87+Oct!M87+Nov!M87+Dec!M87</f>
-        <v>1116</v>
+        <v>1216</v>
       </c>
       <c r="N87" s="82">
         <f>Jan!N87+Feb!N87+Mar!N87+Apr!N87+May!N87+June!N87+July!N87+Aug!N87+Sep!N87+Oct!N87+Nov!N87+Dec!N87</f>
@@ -7185,7 +7185,7 @@
       </c>
       <c r="O87" s="82">
         <f>Jan!O87+Feb!O87+Mar!O87+Apr!O87+May!O87+June!O87+July!O87+Aug!O87+Sep!O87+Oct!O87+Nov!O87+Dec!O87</f>
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="P87" s="82">
         <f>Jan!P87+Feb!P87+Mar!P87+Apr!P87+May!P87+June!P87+July!P87+Aug!P87+Sep!P87+Oct!P87+Nov!P87+Dec!P87</f>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="Q87" s="82">
         <f>Jan!Q87+Feb!Q87+Mar!Q87+Apr!Q87+May!Q87+June!Q87+July!Q87+Aug!Q87+Sep!Q87+Oct!Q87+Nov!Q87+Dec!Q87</f>
-        <v>381</v>
+        <v>420</v>
       </c>
       <c r="R87" s="82">
         <f>Jan!R87+Feb!R87+Mar!R87+Apr!R87+May!R87+June!R87+July!R87+Aug!R87+Sep!R87+Oct!R87+Nov!R87+Dec!R87</f>
@@ -7214,7 +7214,7 @@
       <c r="F88" s="19"/>
       <c r="G88" s="79">
         <f>Jan!G88+Feb!G88+Mar!G88+Apr!G88+May!G88+June!G88+July!G88+Aug!G88+Sep!G88+Oct!G88+Nov!G88+Dec!G88</f>
-        <v>2462</v>
+        <v>2911</v>
       </c>
       <c r="H88" s="80">
         <f>Jan!H88+Feb!H88+Mar!H88+Apr!H88+May!H88+June!H88+July!H88+Aug!H88+Sep!H88+Oct!H88+Nov!H88+Dec!H88</f>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="Q88" s="82">
         <f>Jan!Q88+Feb!Q88+Mar!Q88+Apr!Q88+May!Q88+June!Q88+July!Q88+Aug!Q88+Sep!Q88+Oct!Q88+Nov!Q88+Dec!Q88</f>
-        <v>2462</v>
+        <v>2911</v>
       </c>
       <c r="R88" s="82">
         <f>Jan!R88+Feb!R88+Mar!R88+Apr!R88+May!R88+June!R88+July!R88+Aug!R88+Sep!R88+Oct!R88+Nov!R88+Dec!R88</f>
@@ -7275,7 +7275,7 @@
       <c r="F89" s="19"/>
       <c r="G89" s="79">
         <f>Jan!G89+Feb!G89+Mar!G89+Apr!G89+May!G89+June!G89+July!G89+Aug!G89+Sep!G89+Oct!G89+Nov!G89+Dec!G89</f>
-        <v>2743</v>
+        <v>3138</v>
       </c>
       <c r="H89" s="80">
         <f>Jan!H89+Feb!H89+Mar!H89+Apr!H89+May!H89+June!H89+July!H89+Aug!H89+Sep!H89+Oct!H89+Nov!H89+Dec!H89</f>
@@ -7315,7 +7315,7 @@
       </c>
       <c r="Q89" s="82">
         <f>Jan!Q89+Feb!Q89+Mar!Q89+Apr!Q89+May!Q89+June!Q89+July!Q89+Aug!Q89+Sep!Q89+Oct!Q89+Nov!Q89+Dec!Q89</f>
-        <v>2743</v>
+        <v>3138</v>
       </c>
       <c r="R89" s="82">
         <f>Jan!R89+Feb!R89+Mar!R89+Apr!R89+May!R89+June!R89+July!R89+Aug!R89+Sep!R89+Oct!R89+Nov!R89+Dec!R89</f>
@@ -7397,7 +7397,7 @@
       <c r="F91" s="19"/>
       <c r="G91" s="86">
         <f>Jan!G91+Feb!G91+Mar!G91+Apr!G91+May!G91+June!G91+July!G91+Aug!G91+Sep!G91+Oct!G91+Nov!G91+Dec!G91</f>
-        <v>7990</v>
+        <v>9446</v>
       </c>
       <c r="H91" s="87">
         <f>Jan!H91+Feb!H91+Mar!H91+Apr!H91+May!H91+June!H91+July!H91+Aug!H91+Sep!H91+Oct!H91+Nov!H91+Dec!H91</f>
@@ -7425,7 +7425,7 @@
       </c>
       <c r="N91" s="89">
         <f>Jan!N91+Feb!N91+Mar!N91+Apr!N91+May!N91+June!N91+July!N91+Aug!N91+Sep!N91+Oct!N91+Nov!N91+Dec!N91</f>
-        <v>2109</v>
+        <v>2509</v>
       </c>
       <c r="O91" s="89">
         <f>Jan!O91+Feb!O91+Mar!O91+Apr!O91+May!O91+June!O91+July!O91+Aug!O91+Sep!O91+Oct!O91+Nov!O91+Dec!O91</f>
@@ -7437,7 +7437,7 @@
       </c>
       <c r="Q91" s="89">
         <f>Jan!Q91+Feb!Q91+Mar!Q91+Apr!Q91+May!Q91+June!Q91+July!Q91+Aug!Q91+Sep!Q91+Oct!Q91+Nov!Q91+Dec!Q91</f>
-        <v>5881</v>
+        <v>6937</v>
       </c>
       <c r="R91" s="89">
         <f>Jan!R91+Feb!R91+Mar!R91+Apr!R91+May!R91+June!R91+July!R91+Aug!R91+Sep!R91+Oct!R91+Nov!R91+Dec!R91</f>
@@ -7458,7 +7458,7 @@
       <c r="F92" s="22"/>
       <c r="G92" s="102">
         <f>Jan!G92+Feb!G92+Mar!G92+Apr!G92+May!G92+June!G92+July!G92+Aug!G92+Sep!G92+Oct!G92+Nov!G92+Dec!G92</f>
-        <v>47509</v>
+        <v>56770</v>
       </c>
       <c r="H92" s="103">
         <f>Jan!H92+Feb!H92+Mar!H92+Apr!H92+May!H92+June!H92+July!H92+Aug!H92+Sep!H92+Oct!H92+Nov!H92+Dec!H92</f>
@@ -7482,15 +7482,15 @@
       </c>
       <c r="M92" s="105">
         <f>Jan!M92+Feb!M92+Mar!M92+Apr!M92+May!M92+June!M92+July!M92+Aug!M92+Sep!M92+Oct!M92+Nov!M92+Dec!M92</f>
-        <v>17294</v>
+        <v>21302</v>
       </c>
       <c r="N92" s="105">
         <f>Jan!N92+Feb!N92+Mar!N92+Apr!N92+May!N92+June!N92+July!N92+Aug!N92+Sep!N92+Oct!N92+Nov!N92+Dec!N92</f>
-        <v>4369</v>
+        <v>5354</v>
       </c>
       <c r="O92" s="105">
         <f>Jan!O92+Feb!O92+Mar!O92+Apr!O92+May!O92+June!O92+July!O92+Aug!O92+Sep!O92+Oct!O92+Nov!O92+Dec!O92</f>
-        <v>3716</v>
+        <v>3984</v>
       </c>
       <c r="P92" s="105">
         <f>Jan!P92+Feb!P92+Mar!P92+Apr!P92+May!P92+June!P92+July!P92+Aug!P92+Sep!P92+Oct!P92+Nov!P92+Dec!P92</f>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="Q92" s="105">
         <f>Jan!Q92+Feb!Q92+Mar!Q92+Apr!Q92+May!Q92+June!Q92+July!Q92+Aug!Q92+Sep!Q92+Oct!Q92+Nov!Q92+Dec!Q92</f>
-        <v>22130</v>
+        <v>26130</v>
       </c>
       <c r="R92" s="105">
         <f>Jan!R92+Feb!R92+Mar!R92+Apr!R92+May!R92+June!R92+July!R92+Aug!R92+Sep!R92+Oct!R92+Nov!R92+Dec!R92</f>
@@ -7539,7 +7539,7 @@
       <c r="F94" s="19"/>
       <c r="G94" s="74">
         <f>Jan!G94+Feb!G94+Mar!G94+Apr!G94+May!G94+June!G94+July!G94+Aug!G94+Sep!G94+Oct!G94+Nov!G94+Dec!G94</f>
-        <v>542</v>
+        <v>1142</v>
       </c>
       <c r="H94" s="75">
         <f>Jan!H94+Feb!H94+Mar!H94+Apr!H94+May!H94+June!H94+July!H94+Aug!H94+Sep!H94+Oct!H94+Nov!H94+Dec!H94</f>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="M94" s="77">
         <f>Jan!M94+Feb!M94+Mar!M94+Apr!M94+May!M94+June!M94+July!M94+Aug!M94+Sep!M94+Oct!M94+Nov!M94+Dec!M94</f>
-        <v>320</v>
+        <v>920</v>
       </c>
       <c r="N94" s="77">
         <f>Jan!N94+Feb!N94+Mar!N94+Apr!N94+May!N94+June!N94+July!N94+Aug!N94+Sep!N94+Oct!N94+Nov!N94+Dec!N94</f>
@@ -7600,7 +7600,7 @@
       <c r="F95" s="19"/>
       <c r="G95" s="79">
         <f>Jan!G95+Feb!G95+Mar!G95+Apr!G95+May!G95+June!G95+July!G95+Aug!G95+Sep!G95+Oct!G95+Nov!G95+Dec!G95</f>
-        <v>631</v>
+        <v>741</v>
       </c>
       <c r="H95" s="80">
         <f>Jan!H95+Feb!H95+Mar!H95+Apr!H95+May!H95+June!H95+July!H95+Aug!H95+Sep!H95+Oct!H95+Nov!H95+Dec!H95</f>
@@ -7624,11 +7624,11 @@
       </c>
       <c r="M95" s="82">
         <f>Jan!M95+Feb!M95+Mar!M95+Apr!M95+May!M95+June!M95+July!M95+Aug!M95+Sep!M95+Oct!M95+Nov!M95+Dec!M95</f>
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="N95" s="82">
         <f>Jan!N95+Feb!N95+Mar!N95+Apr!N95+May!N95+June!N95+July!N95+Aug!N95+Sep!N95+Oct!N95+Nov!N95+Dec!N95</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O95" s="82">
         <f>Jan!O95+Feb!O95+Mar!O95+Apr!O95+May!O95+June!O95+July!O95+Aug!O95+Sep!O95+Oct!O95+Nov!O95+Dec!O95</f>
@@ -7636,11 +7636,11 @@
       </c>
       <c r="P95" s="82">
         <f>Jan!P95+Feb!P95+Mar!P95+Apr!P95+May!P95+June!P95+July!P95+Aug!P95+Sep!P95+Oct!P95+Nov!P95+Dec!P95</f>
-        <v>549</v>
+        <v>568</v>
       </c>
       <c r="Q95" s="82">
         <f>Jan!Q95+Feb!Q95+Mar!Q95+Apr!Q95+May!Q95+June!Q95+July!Q95+Aug!Q95+Sep!Q95+Oct!Q95+Nov!Q95+Dec!Q95</f>
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="R95" s="82">
         <f>Jan!R95+Feb!R95+Mar!R95+Apr!R95+May!R95+June!R95+July!R95+Aug!R95+Sep!R95+Oct!R95+Nov!R95+Dec!R95</f>
@@ -7661,11 +7661,11 @@
       <c r="F96" s="19"/>
       <c r="G96" s="79">
         <f>Jan!G96+Feb!G96+Mar!G96+Apr!G96+May!G96+June!G96+July!G96+Aug!G96+Sep!G96+Oct!G96+Nov!G96+Dec!G96</f>
-        <v>1145</v>
+        <v>1276</v>
       </c>
       <c r="H96" s="80">
         <f>Jan!H96+Feb!H96+Mar!H96+Apr!H96+May!H96+June!H96+July!H96+Aug!H96+Sep!H96+Oct!H96+Nov!H96+Dec!H96</f>
-        <v>700</v>
+        <v>781</v>
       </c>
       <c r="I96" s="81">
         <f>Jan!I96+Feb!I96+Mar!I96+Apr!I96+May!I96+June!I96+July!I96+Aug!I96+Sep!I96+Oct!I96+Nov!I96+Dec!I96</f>
@@ -7697,7 +7697,7 @@
       </c>
       <c r="P96" s="82">
         <f>Jan!P96+Feb!P96+Mar!P96+Apr!P96+May!P96+June!P96+July!P96+Aug!P96+Sep!P96+Oct!P96+Nov!P96+Dec!P96</f>
-        <v>351</v>
+        <v>401</v>
       </c>
       <c r="Q96" s="82">
         <f>Jan!Q96+Feb!Q96+Mar!Q96+Apr!Q96+May!Q96+June!Q96+July!Q96+Aug!Q96+Sep!Q96+Oct!Q96+Nov!Q96+Dec!Q96</f>
@@ -7905,7 +7905,7 @@
       <c r="F100" s="19"/>
       <c r="G100" s="79">
         <f>Jan!G100+Feb!G100+Mar!G100+Apr!G100+May!G100+June!G100+July!G100+Aug!G100+Sep!G100+Oct!G100+Nov!G100+Dec!G100</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H100" s="80">
         <f>Jan!H100+Feb!H100+Mar!H100+Apr!H100+May!H100+June!H100+July!H100+Aug!H100+Sep!H100+Oct!H100+Nov!H100+Dec!H100</f>
@@ -7941,7 +7941,7 @@
       </c>
       <c r="P100" s="82">
         <f>Jan!P100+Feb!P100+Mar!P100+Apr!P100+May!P100+June!P100+July!P100+Aug!P100+Sep!P100+Oct!P100+Nov!P100+Dec!P100</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q100" s="82">
         <f>Jan!Q100+Feb!Q100+Mar!Q100+Apr!Q100+May!Q100+June!Q100+July!Q100+Aug!Q100+Sep!Q100+Oct!Q100+Nov!Q100+Dec!Q100</f>
@@ -8027,11 +8027,11 @@
       <c r="F102" s="22"/>
       <c r="G102" s="91">
         <f>Jan!G102+Feb!G102+Mar!G102+Apr!G102+May!G102+June!G102+July!G102+Aug!G102+Sep!G102+Oct!G102+Nov!G102+Dec!G102</f>
-        <v>3076</v>
+        <v>3918</v>
       </c>
       <c r="H102" s="92">
         <f>Jan!H102+Feb!H102+Mar!H102+Apr!H102+May!H102+June!H102+July!H102+Aug!H102+Sep!H102+Oct!H102+Nov!H102+Dec!H102</f>
-        <v>700</v>
+        <v>781</v>
       </c>
       <c r="I102" s="93">
         <f>Jan!I102+Feb!I102+Mar!I102+Apr!I102+May!I102+June!I102+July!I102+Aug!I102+Sep!I102+Oct!I102+Nov!I102+Dec!I102</f>
@@ -8051,11 +8051,11 @@
       </c>
       <c r="M102" s="94">
         <f>Jan!M102+Feb!M102+Mar!M102+Apr!M102+May!M102+June!M102+July!M102+Aug!M102+Sep!M102+Oct!M102+Nov!M102+Dec!M102</f>
-        <v>381</v>
+        <v>1061</v>
       </c>
       <c r="N102" s="94">
         <f>Jan!N102+Feb!N102+Mar!N102+Apr!N102+May!N102+June!N102+July!N102+Aug!N102+Sep!N102+Oct!N102+Nov!N102+Dec!N102</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O102" s="94">
         <f>Jan!O102+Feb!O102+Mar!O102+Apr!O102+May!O102+June!O102+July!O102+Aug!O102+Sep!O102+Oct!O102+Nov!O102+Dec!O102</f>
@@ -8063,11 +8063,11 @@
       </c>
       <c r="P102" s="94">
         <f>Jan!P102+Feb!P102+Mar!P102+Apr!P102+May!P102+June!P102+July!P102+Aug!P102+Sep!P102+Oct!P102+Nov!P102+Dec!P102</f>
-        <v>1016</v>
+        <v>1086</v>
       </c>
       <c r="Q102" s="94">
         <f>Jan!Q102+Feb!Q102+Mar!Q102+Apr!Q102+May!Q102+June!Q102+July!Q102+Aug!Q102+Sep!Q102+Oct!Q102+Nov!Q102+Dec!Q102</f>
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="R102" s="94">
         <f>Jan!R102+Feb!R102+Mar!R102+Apr!R102+May!R102+June!R102+July!R102+Aug!R102+Sep!R102+Oct!R102+Nov!R102+Dec!R102</f>
@@ -8108,55 +8108,55 @@
       <c r="F104" s="22"/>
       <c r="G104" s="112">
         <f>Jan!G104+Feb!G104+Mar!G104+Apr!G104+May!G104+June!G104+July!G104+Aug!G104+Sep!G104+Oct!G104+Nov!G104+Dec!G104</f>
-        <v>1619037</v>
+        <v>1904864</v>
       </c>
       <c r="H104" s="113">
         <f>Jan!H104+Feb!H104+Mar!H104+Apr!H104+May!H104+June!H104+July!H104+Aug!H104+Sep!H104+Oct!H104+Nov!H104+Dec!H104</f>
-        <v>296479</v>
+        <v>351164</v>
       </c>
       <c r="I104" s="114">
         <f>Jan!I104+Feb!I104+Mar!I104+Apr!I104+May!I104+June!I104+July!I104+Aug!I104+Sep!I104+Oct!I104+Nov!I104+Dec!I104</f>
-        <v>430727</v>
+        <v>506584</v>
       </c>
       <c r="J104" s="115">
         <f>Jan!J104+Feb!J104+Mar!J104+Apr!J104+May!J104+June!J104+July!J104+Aug!J104+Sep!J104+Oct!J104+Nov!J104+Dec!J104</f>
-        <v>48336</v>
+        <v>56978</v>
       </c>
       <c r="K104" s="115">
         <f>Jan!K104+Feb!K104+Mar!K104+Apr!K104+May!K104+June!K104+July!K104+Aug!K104+Sep!K104+Oct!K104+Nov!K104+Dec!K104</f>
-        <v>54852</v>
+        <v>64159</v>
       </c>
       <c r="L104" s="115">
         <f>Jan!L104+Feb!L104+Mar!L104+Apr!L104+May!L104+June!L104+July!L104+Aug!L104+Sep!L104+Oct!L104+Nov!L104+Dec!L104</f>
-        <v>290820</v>
+        <v>340825</v>
       </c>
       <c r="M104" s="115">
         <f>Jan!M104+Feb!M104+Mar!M104+Apr!M104+May!M104+June!M104+July!M104+Aug!M104+Sep!M104+Oct!M104+Nov!M104+Dec!M104</f>
-        <v>38572</v>
+        <v>47101</v>
       </c>
       <c r="N104" s="115">
         <f>Jan!N104+Feb!N104+Mar!N104+Apr!N104+May!N104+June!N104+July!N104+Aug!N104+Sep!N104+Oct!N104+Nov!N104+Dec!N104</f>
-        <v>83951</v>
+        <v>99049</v>
       </c>
       <c r="O104" s="115">
         <f>Jan!O104+Feb!O104+Mar!O104+Apr!O104+May!O104+June!O104+July!O104+Aug!O104+Sep!O104+Oct!O104+Nov!O104+Dec!O104</f>
-        <v>71125</v>
+        <v>82344</v>
       </c>
       <c r="P104" s="115">
         <f>Jan!P104+Feb!P104+Mar!P104+Apr!P104+May!P104+June!P104+July!P104+Aug!P104+Sep!P104+Oct!P104+Nov!P104+Dec!P104</f>
-        <v>26802</v>
+        <v>31653</v>
       </c>
       <c r="Q104" s="115">
         <f>Jan!Q104+Feb!Q104+Mar!Q104+Apr!Q104+May!Q104+June!Q104+July!Q104+Aug!Q104+Sep!Q104+Oct!Q104+Nov!Q104+Dec!Q104</f>
-        <v>84850</v>
+        <v>99282</v>
       </c>
       <c r="R104" s="115">
         <f>Jan!R104+Feb!R104+Mar!R104+Apr!R104+May!R104+June!R104+July!R104+Aug!R104+Sep!R104+Oct!R104+Nov!R104+Dec!R104</f>
-        <v>156523</v>
+        <v>183205</v>
       </c>
       <c r="S104" s="116">
         <f>Jan!S104+Feb!S104+Mar!S104+Apr!S104+May!S104+June!S104+July!S104+Aug!S104+Sep!S104+Oct!S104+Nov!S104+Dec!S104</f>
-        <v>36000</v>
+        <v>42520</v>
       </c>
     </row>
     <row r="105" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8169,19 +8169,19 @@
       <c r="F105" s="22"/>
       <c r="G105" s="117">
         <f>Jan!G105+Feb!G105+Mar!G105+Apr!G105+May!G105+June!G105+July!G105+Aug!G105+Sep!G105+Oct!G105+Nov!G105+Dec!G105</f>
-        <v>196443</v>
+        <v>237582</v>
       </c>
       <c r="H105" s="118">
         <f>Jan!H105+Feb!H105+Mar!H105+Apr!H105+May!H105+June!H105+July!H105+Aug!H105+Sep!H105+Oct!H105+Nov!H105+Dec!H105</f>
-        <v>72078</v>
+        <v>85444</v>
       </c>
       <c r="I105" s="119">
         <f>Jan!I105+Feb!I105+Mar!I105+Apr!I105+May!I105+June!I105+July!I105+Aug!I105+Sep!I105+Oct!I105+Nov!I105+Dec!I105</f>
-        <v>12731</v>
+        <v>15396</v>
       </c>
       <c r="J105" s="120">
         <f>Jan!J105+Feb!J105+Mar!J105+Apr!J105+May!J105+June!J105+July!J105+Aug!J105+Sep!J105+Oct!J105+Nov!J105+Dec!J105</f>
-        <v>7111</v>
+        <v>8457</v>
       </c>
       <c r="K105" s="120">
         <f>Jan!K105+Feb!K105+Mar!K105+Apr!K105+May!K105+June!K105+July!K105+Aug!K105+Sep!K105+Oct!K105+Nov!K105+Dec!K105</f>
@@ -8189,35 +8189,35 @@
       </c>
       <c r="L105" s="120">
         <f>Jan!L105+Feb!L105+Mar!L105+Apr!L105+May!L105+June!L105+July!L105+Aug!L105+Sep!L105+Oct!L105+Nov!L105+Dec!L105</f>
-        <v>90201</v>
+        <v>110063</v>
       </c>
       <c r="M105" s="120">
         <f>Jan!M105+Feb!M105+Mar!M105+Apr!M105+May!M105+June!M105+July!M105+Aug!M105+Sep!M105+Oct!M105+Nov!M105+Dec!M105</f>
-        <v>1369</v>
+        <v>1955</v>
       </c>
       <c r="N105" s="120">
         <f>Jan!N105+Feb!N105+Mar!N105+Apr!N105+May!N105+June!N105+July!N105+Aug!N105+Sep!N105+Oct!N105+Nov!N105+Dec!N105</f>
-        <v>935</v>
+        <v>1402</v>
       </c>
       <c r="O105" s="120">
         <f>Jan!O105+Feb!O105+Mar!O105+Apr!O105+May!O105+June!O105+July!O105+Aug!O105+Sep!O105+Oct!O105+Nov!O105+Dec!O105</f>
-        <v>934</v>
+        <v>1111</v>
       </c>
       <c r="P105" s="120">
         <f>Jan!P105+Feb!P105+Mar!P105+Apr!P105+May!P105+June!P105+July!P105+Aug!P105+Sep!P105+Oct!P105+Nov!P105+Dec!P105</f>
-        <v>440</v>
+        <v>503</v>
       </c>
       <c r="Q105" s="120">
         <f>Jan!Q105+Feb!Q105+Mar!Q105+Apr!Q105+May!Q105+June!Q105+July!Q105+Aug!Q105+Sep!Q105+Oct!Q105+Nov!Q105+Dec!Q105</f>
-        <v>7757</v>
+        <v>9596</v>
       </c>
       <c r="R105" s="120">
         <f>Jan!R105+Feb!R105+Mar!R105+Apr!R105+May!R105+June!R105+July!R105+Aug!R105+Sep!R105+Oct!R105+Nov!R105+Dec!R105</f>
-        <v>2626</v>
+        <v>3361</v>
       </c>
       <c r="S105" s="121">
         <f>Jan!S105+Feb!S105+Mar!S105+Apr!S105+May!S105+June!S105+July!S105+Aug!S105+Sep!S105+Oct!S105+Nov!S105+Dec!S105</f>
-        <v>242</v>
+        <v>275</v>
       </c>
     </row>
     <row r="106" spans="2:19" ht="12.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -51577,20 +51577,40 @@
       <c r="F6" s="19"/>
       <c r="G6" s="74">
         <f>SUM(H6:S6)</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="76"/>
+        <v>13731</v>
+      </c>
+      <c r="H6" s="75">
+        <v>3408</v>
+      </c>
+      <c r="I6" s="76">
+        <v>0</v>
+      </c>
       <c r="J6" s="77"/>
       <c r="K6" s="77"/>
-      <c r="L6" s="77"/>
-      <c r="M6" s="77"/>
-      <c r="N6" s="77"/>
-      <c r="O6" s="77"/>
-      <c r="P6" s="77"/>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="78"/>
+      <c r="L6" s="77">
+        <v>5287</v>
+      </c>
+      <c r="M6" s="77">
+        <v>509</v>
+      </c>
+      <c r="N6" s="77">
+        <v>2080</v>
+      </c>
+      <c r="O6" s="77">
+        <v>721</v>
+      </c>
+      <c r="P6" s="77">
+        <v>1116</v>
+      </c>
+      <c r="Q6" s="77">
+        <v>610</v>
+      </c>
+      <c r="R6" s="77">
+        <v>0</v>
+      </c>
+      <c r="S6" s="78">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="2:25" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="26"/>
@@ -51602,20 +51622,36 @@
       <c r="F7" s="19"/>
       <c r="G7" s="79">
         <f t="shared" ref="G7:G74" si="0">SUM(H7:S7)</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="80"/>
-      <c r="I7" s="81"/>
+        <v>3844</v>
+      </c>
+      <c r="H7" s="80">
+        <v>3844</v>
+      </c>
+      <c r="I7" s="81">
+        <v>0</v>
+      </c>
       <c r="J7" s="82"/>
       <c r="K7" s="82"/>
-      <c r="L7" s="82"/>
-      <c r="M7" s="82"/>
-      <c r="N7" s="82"/>
+      <c r="L7" s="82">
+        <v>0</v>
+      </c>
+      <c r="M7" s="82">
+        <v>0</v>
+      </c>
+      <c r="N7" s="82">
+        <v>0</v>
+      </c>
       <c r="O7" s="82"/>
       <c r="P7" s="82"/>
-      <c r="Q7" s="82"/>
-      <c r="R7" s="82"/>
-      <c r="S7" s="83"/>
+      <c r="Q7" s="82">
+        <v>0</v>
+      </c>
+      <c r="R7" s="82">
+        <v>0</v>
+      </c>
+      <c r="S7" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="2:25" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="26"/>
@@ -51627,20 +51663,36 @@
       <c r="F8" s="19"/>
       <c r="G8" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="80"/>
-      <c r="I8" s="81"/>
+        <v>1334</v>
+      </c>
+      <c r="H8" s="80">
+        <v>1334</v>
+      </c>
+      <c r="I8" s="81">
+        <v>0</v>
+      </c>
       <c r="J8" s="82"/>
       <c r="K8" s="82"/>
-      <c r="L8" s="82"/>
-      <c r="M8" s="82"/>
-      <c r="N8" s="82"/>
+      <c r="L8" s="82">
+        <v>0</v>
+      </c>
+      <c r="M8" s="82">
+        <v>0</v>
+      </c>
+      <c r="N8" s="82">
+        <v>0</v>
+      </c>
       <c r="O8" s="82"/>
       <c r="P8" s="82"/>
-      <c r="Q8" s="82"/>
-      <c r="R8" s="82"/>
-      <c r="S8" s="84"/>
+      <c r="Q8" s="82">
+        <v>0</v>
+      </c>
+      <c r="R8" s="82">
+        <v>0</v>
+      </c>
+      <c r="S8" s="84">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="2:25" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="26"/>
@@ -51652,20 +51704,44 @@
       <c r="F9" s="19"/>
       <c r="G9" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="80"/>
-      <c r="I9" s="81"/>
-      <c r="J9" s="82"/>
-      <c r="K9" s="82"/>
-      <c r="L9" s="82"/>
-      <c r="M9" s="82"/>
-      <c r="N9" s="82"/>
-      <c r="O9" s="82"/>
-      <c r="P9" s="82"/>
-      <c r="Q9" s="82"/>
-      <c r="R9" s="82"/>
-      <c r="S9" s="85"/>
+        <v>2</v>
+      </c>
+      <c r="H9" s="80">
+        <v>0</v>
+      </c>
+      <c r="I9" s="81">
+        <v>0</v>
+      </c>
+      <c r="J9" s="82">
+        <v>0</v>
+      </c>
+      <c r="K9" s="82">
+        <v>0</v>
+      </c>
+      <c r="L9" s="82">
+        <v>0</v>
+      </c>
+      <c r="M9" s="82">
+        <v>2</v>
+      </c>
+      <c r="N9" s="82">
+        <v>0</v>
+      </c>
+      <c r="O9" s="82">
+        <v>0</v>
+      </c>
+      <c r="P9" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="82">
+        <v>0</v>
+      </c>
+      <c r="R9" s="82">
+        <v>0</v>
+      </c>
+      <c r="S9" s="85">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="2:25" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="26"/>
@@ -51677,20 +51753,44 @@
       <c r="F10" s="19"/>
       <c r="G10" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="80"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="82"/>
-      <c r="K10" s="82"/>
-      <c r="L10" s="82"/>
-      <c r="M10" s="82"/>
-      <c r="N10" s="82"/>
-      <c r="O10" s="82"/>
-      <c r="P10" s="82"/>
-      <c r="Q10" s="82"/>
-      <c r="R10" s="82"/>
-      <c r="S10" s="85"/>
+        <v>9406</v>
+      </c>
+      <c r="H10" s="80">
+        <v>2362</v>
+      </c>
+      <c r="I10" s="81">
+        <v>6694</v>
+      </c>
+      <c r="J10" s="82">
+        <v>0</v>
+      </c>
+      <c r="K10" s="82">
+        <v>0</v>
+      </c>
+      <c r="L10" s="82">
+        <v>0</v>
+      </c>
+      <c r="M10" s="82">
+        <v>6</v>
+      </c>
+      <c r="N10" s="82">
+        <v>0</v>
+      </c>
+      <c r="O10" s="82">
+        <v>344</v>
+      </c>
+      <c r="P10" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="82">
+        <v>0</v>
+      </c>
+      <c r="R10" s="82">
+        <v>0</v>
+      </c>
+      <c r="S10" s="85">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="2:25" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="26"/>
@@ -51702,20 +51802,44 @@
       <c r="F11" s="19"/>
       <c r="G11" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="80"/>
-      <c r="I11" s="81"/>
-      <c r="J11" s="82"/>
-      <c r="K11" s="82"/>
-      <c r="L11" s="82"/>
-      <c r="M11" s="82"/>
-      <c r="N11" s="82"/>
-      <c r="O11" s="82"/>
-      <c r="P11" s="82"/>
-      <c r="Q11" s="82"/>
-      <c r="R11" s="82"/>
-      <c r="S11" s="83"/>
+        <v>1321</v>
+      </c>
+      <c r="H11" s="80">
+        <v>1259</v>
+      </c>
+      <c r="I11" s="81">
+        <v>0</v>
+      </c>
+      <c r="J11" s="82">
+        <v>0</v>
+      </c>
+      <c r="K11" s="82">
+        <v>0</v>
+      </c>
+      <c r="L11" s="82">
+        <v>0</v>
+      </c>
+      <c r="M11" s="82">
+        <v>10</v>
+      </c>
+      <c r="N11" s="82">
+        <v>0</v>
+      </c>
+      <c r="O11" s="82">
+        <v>52</v>
+      </c>
+      <c r="P11" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="82">
+        <v>0</v>
+      </c>
+      <c r="R11" s="82">
+        <v>0</v>
+      </c>
+      <c r="S11" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="2:25" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="26"/>
@@ -51727,20 +51851,44 @@
       <c r="F12" s="19"/>
       <c r="G12" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="80"/>
-      <c r="I12" s="81"/>
-      <c r="J12" s="82"/>
-      <c r="K12" s="82"/>
-      <c r="L12" s="82"/>
-      <c r="M12" s="82"/>
-      <c r="N12" s="82"/>
-      <c r="O12" s="82"/>
-      <c r="P12" s="82"/>
-      <c r="Q12" s="82"/>
-      <c r="R12" s="82"/>
-      <c r="S12" s="83"/>
+        <v>58</v>
+      </c>
+      <c r="H12" s="80">
+        <v>57</v>
+      </c>
+      <c r="I12" s="81">
+        <v>0</v>
+      </c>
+      <c r="J12" s="82">
+        <v>0</v>
+      </c>
+      <c r="K12" s="82">
+        <v>0</v>
+      </c>
+      <c r="L12" s="82">
+        <v>0</v>
+      </c>
+      <c r="M12" s="82">
+        <v>1</v>
+      </c>
+      <c r="N12" s="82">
+        <v>0</v>
+      </c>
+      <c r="O12" s="82">
+        <v>0</v>
+      </c>
+      <c r="P12" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="82">
+        <v>0</v>
+      </c>
+      <c r="R12" s="82">
+        <v>0</v>
+      </c>
+      <c r="S12" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="2:25" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="26"/>
@@ -51752,20 +51900,40 @@
       <c r="F13" s="19"/>
       <c r="G13" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="80"/>
-      <c r="I13" s="81"/>
+        <v>6311</v>
+      </c>
+      <c r="H13" s="80">
+        <v>0</v>
+      </c>
+      <c r="I13" s="81">
+        <v>0</v>
+      </c>
       <c r="J13" s="82"/>
       <c r="K13" s="82"/>
-      <c r="L13" s="82"/>
-      <c r="M13" s="82"/>
-      <c r="N13" s="82"/>
-      <c r="O13" s="82"/>
-      <c r="P13" s="82"/>
-      <c r="Q13" s="82"/>
-      <c r="R13" s="82"/>
-      <c r="S13" s="83"/>
+      <c r="L13" s="82">
+        <v>4515</v>
+      </c>
+      <c r="M13" s="82">
+        <v>85</v>
+      </c>
+      <c r="N13" s="82">
+        <v>418</v>
+      </c>
+      <c r="O13" s="82">
+        <v>395</v>
+      </c>
+      <c r="P13" s="82">
+        <v>68</v>
+      </c>
+      <c r="Q13" s="82">
+        <v>830</v>
+      </c>
+      <c r="R13" s="82">
+        <v>0</v>
+      </c>
+      <c r="S13" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="2:25" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="26"/>
@@ -51777,20 +51945,44 @@
       <c r="F14" s="19"/>
       <c r="G14" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="80"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="82"/>
-      <c r="K14" s="82"/>
-      <c r="L14" s="82"/>
-      <c r="M14" s="82"/>
-      <c r="N14" s="82"/>
-      <c r="O14" s="82"/>
-      <c r="P14" s="82"/>
-      <c r="Q14" s="82"/>
-      <c r="R14" s="82"/>
-      <c r="S14" s="83"/>
+        <v>19448</v>
+      </c>
+      <c r="H14" s="80">
+        <v>7427</v>
+      </c>
+      <c r="I14" s="81">
+        <v>8807</v>
+      </c>
+      <c r="J14" s="82">
+        <v>1713</v>
+      </c>
+      <c r="K14" s="82">
+        <v>0</v>
+      </c>
+      <c r="L14" s="82">
+        <v>629</v>
+      </c>
+      <c r="M14" s="82">
+        <v>36</v>
+      </c>
+      <c r="N14" s="82">
+        <v>394</v>
+      </c>
+      <c r="O14" s="82">
+        <v>4</v>
+      </c>
+      <c r="P14" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="82">
+        <v>438</v>
+      </c>
+      <c r="R14" s="82">
+        <v>0</v>
+      </c>
+      <c r="S14" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="2:25" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="26"/>
@@ -51802,20 +51994,44 @@
       <c r="F15" s="19"/>
       <c r="G15" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H15" s="80"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="82"/>
-      <c r="K15" s="82"/>
-      <c r="L15" s="82"/>
-      <c r="M15" s="82"/>
-      <c r="N15" s="82"/>
-      <c r="O15" s="82"/>
-      <c r="P15" s="82"/>
-      <c r="Q15" s="82"/>
-      <c r="R15" s="82"/>
-      <c r="S15" s="83"/>
+        <v>22</v>
+      </c>
+      <c r="H15" s="80">
+        <v>0</v>
+      </c>
+      <c r="I15" s="81">
+        <v>0</v>
+      </c>
+      <c r="J15" s="82">
+        <v>0</v>
+      </c>
+      <c r="K15" s="82">
+        <v>0</v>
+      </c>
+      <c r="L15" s="82">
+        <v>0</v>
+      </c>
+      <c r="M15" s="82">
+        <v>10</v>
+      </c>
+      <c r="N15" s="82">
+        <v>12</v>
+      </c>
+      <c r="O15" s="82">
+        <v>0</v>
+      </c>
+      <c r="P15" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="82">
+        <v>0</v>
+      </c>
+      <c r="R15" s="82">
+        <v>0</v>
+      </c>
+      <c r="S15" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="2:25" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="26"/>
@@ -51827,20 +52043,44 @@
       <c r="F16" s="19"/>
       <c r="G16" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="80"/>
-      <c r="I16" s="81"/>
-      <c r="J16" s="82"/>
-      <c r="K16" s="82"/>
-      <c r="L16" s="82"/>
-      <c r="M16" s="82"/>
-      <c r="N16" s="82"/>
-      <c r="O16" s="82"/>
-      <c r="P16" s="82"/>
-      <c r="Q16" s="82"/>
-      <c r="R16" s="82"/>
-      <c r="S16" s="83"/>
+        <v>6527</v>
+      </c>
+      <c r="H16" s="80">
+        <v>1307</v>
+      </c>
+      <c r="I16" s="81">
+        <v>1381</v>
+      </c>
+      <c r="J16" s="82">
+        <v>355</v>
+      </c>
+      <c r="K16" s="82">
+        <v>51</v>
+      </c>
+      <c r="L16" s="82">
+        <v>2508</v>
+      </c>
+      <c r="M16" s="82">
+        <v>8</v>
+      </c>
+      <c r="N16" s="82">
+        <v>549</v>
+      </c>
+      <c r="O16" s="82">
+        <v>264</v>
+      </c>
+      <c r="P16" s="82">
+        <v>36</v>
+      </c>
+      <c r="Q16" s="82">
+        <v>68</v>
+      </c>
+      <c r="R16" s="82">
+        <v>0</v>
+      </c>
+      <c r="S16" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="26"/>
@@ -51852,20 +52092,44 @@
       <c r="F17" s="19"/>
       <c r="G17" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="80"/>
-      <c r="I17" s="81"/>
-      <c r="J17" s="82"/>
-      <c r="K17" s="82"/>
-      <c r="L17" s="82"/>
-      <c r="M17" s="82"/>
-      <c r="N17" s="82"/>
-      <c r="O17" s="82"/>
-      <c r="P17" s="82"/>
-      <c r="Q17" s="82"/>
-      <c r="R17" s="82"/>
-      <c r="S17" s="83"/>
+        <v>1763</v>
+      </c>
+      <c r="H17" s="80">
+        <v>0</v>
+      </c>
+      <c r="I17" s="81">
+        <v>341</v>
+      </c>
+      <c r="J17" s="82">
+        <v>561</v>
+      </c>
+      <c r="K17" s="82">
+        <v>0</v>
+      </c>
+      <c r="L17" s="82">
+        <v>695</v>
+      </c>
+      <c r="M17" s="82">
+        <v>163</v>
+      </c>
+      <c r="N17" s="82">
+        <v>1</v>
+      </c>
+      <c r="O17" s="82">
+        <v>0</v>
+      </c>
+      <c r="P17" s="82">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="82">
+        <v>0</v>
+      </c>
+      <c r="R17" s="82">
+        <v>0</v>
+      </c>
+      <c r="S17" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="26"/>
@@ -51877,20 +52141,40 @@
       <c r="F18" s="19"/>
       <c r="G18" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H18" s="80"/>
-      <c r="I18" s="81"/>
+        <v>10410</v>
+      </c>
+      <c r="H18" s="80">
+        <v>3467</v>
+      </c>
+      <c r="I18" s="81">
+        <v>0</v>
+      </c>
       <c r="J18" s="82"/>
       <c r="K18" s="82"/>
-      <c r="L18" s="82"/>
-      <c r="M18" s="82"/>
-      <c r="N18" s="82"/>
-      <c r="O18" s="82"/>
-      <c r="P18" s="82"/>
-      <c r="Q18" s="82"/>
-      <c r="R18" s="82"/>
-      <c r="S18" s="83"/>
+      <c r="L18" s="82">
+        <v>5430</v>
+      </c>
+      <c r="M18" s="82">
+        <v>414</v>
+      </c>
+      <c r="N18" s="82">
+        <v>55</v>
+      </c>
+      <c r="O18" s="82">
+        <v>173</v>
+      </c>
+      <c r="P18" s="82">
+        <v>44</v>
+      </c>
+      <c r="Q18" s="82">
+        <v>827</v>
+      </c>
+      <c r="R18" s="82">
+        <v>0</v>
+      </c>
+      <c r="S18" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="26"/>
@@ -51902,20 +52186,44 @@
       <c r="F19" s="19"/>
       <c r="G19" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H19" s="80"/>
-      <c r="I19" s="81"/>
-      <c r="J19" s="82"/>
-      <c r="K19" s="82"/>
-      <c r="L19" s="82"/>
-      <c r="M19" s="82"/>
-      <c r="N19" s="82"/>
-      <c r="O19" s="82"/>
-      <c r="P19" s="82"/>
-      <c r="Q19" s="82"/>
-      <c r="R19" s="82"/>
-      <c r="S19" s="83"/>
+        <v>1339</v>
+      </c>
+      <c r="H19" s="80">
+        <v>849</v>
+      </c>
+      <c r="I19" s="81">
+        <v>0</v>
+      </c>
+      <c r="J19" s="82">
+        <v>164</v>
+      </c>
+      <c r="K19" s="82">
+        <v>0</v>
+      </c>
+      <c r="L19" s="82">
+        <v>293</v>
+      </c>
+      <c r="M19" s="82">
+        <v>0</v>
+      </c>
+      <c r="N19" s="82">
+        <v>0</v>
+      </c>
+      <c r="O19" s="82">
+        <v>0</v>
+      </c>
+      <c r="P19" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="82">
+        <v>33</v>
+      </c>
+      <c r="R19" s="82">
+        <v>0</v>
+      </c>
+      <c r="S19" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="26"/>
@@ -51927,20 +52235,44 @@
       <c r="F20" s="19"/>
       <c r="G20" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H20" s="80"/>
-      <c r="I20" s="81"/>
-      <c r="J20" s="82"/>
-      <c r="K20" s="82"/>
-      <c r="L20" s="82"/>
-      <c r="M20" s="82"/>
-      <c r="N20" s="82"/>
-      <c r="O20" s="82"/>
-      <c r="P20" s="82"/>
-      <c r="Q20" s="82"/>
-      <c r="R20" s="82"/>
-      <c r="S20" s="83"/>
+        <v>6160</v>
+      </c>
+      <c r="H20" s="80">
+        <v>3434</v>
+      </c>
+      <c r="I20" s="81">
+        <v>0</v>
+      </c>
+      <c r="J20" s="82">
+        <v>298</v>
+      </c>
+      <c r="K20" s="82">
+        <v>0</v>
+      </c>
+      <c r="L20" s="82">
+        <v>2425</v>
+      </c>
+      <c r="M20" s="82">
+        <v>0</v>
+      </c>
+      <c r="N20" s="82">
+        <v>0</v>
+      </c>
+      <c r="O20" s="82">
+        <v>0</v>
+      </c>
+      <c r="P20" s="82">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="82">
+        <v>0</v>
+      </c>
+      <c r="R20" s="82">
+        <v>0</v>
+      </c>
+      <c r="S20" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="26"/>
@@ -51952,20 +52284,44 @@
       <c r="F21" s="19"/>
       <c r="G21" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="80"/>
-      <c r="I21" s="81"/>
-      <c r="J21" s="82"/>
-      <c r="K21" s="82"/>
-      <c r="L21" s="82"/>
-      <c r="M21" s="82"/>
-      <c r="N21" s="82"/>
-      <c r="O21" s="82"/>
-      <c r="P21" s="82"/>
-      <c r="Q21" s="82"/>
-      <c r="R21" s="82"/>
-      <c r="S21" s="83"/>
+        <v>1805</v>
+      </c>
+      <c r="H21" s="80">
+        <v>1070</v>
+      </c>
+      <c r="I21" s="81">
+        <v>0</v>
+      </c>
+      <c r="J21" s="82">
+        <v>0</v>
+      </c>
+      <c r="K21" s="82">
+        <v>0</v>
+      </c>
+      <c r="L21" s="82">
+        <v>696</v>
+      </c>
+      <c r="M21" s="82">
+        <v>1</v>
+      </c>
+      <c r="N21" s="82">
+        <v>4</v>
+      </c>
+      <c r="O21" s="82">
+        <v>0</v>
+      </c>
+      <c r="P21" s="82">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="82">
+        <v>29</v>
+      </c>
+      <c r="R21" s="82">
+        <v>0</v>
+      </c>
+      <c r="S21" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="26"/>
@@ -51977,20 +52333,44 @@
       <c r="F22" s="19"/>
       <c r="G22" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H22" s="80"/>
-      <c r="I22" s="81"/>
-      <c r="J22" s="82"/>
-      <c r="K22" s="82"/>
-      <c r="L22" s="82"/>
-      <c r="M22" s="82"/>
-      <c r="N22" s="82"/>
-      <c r="O22" s="82"/>
-      <c r="P22" s="82"/>
-      <c r="Q22" s="82"/>
-      <c r="R22" s="82"/>
-      <c r="S22" s="83"/>
+        <v>1508</v>
+      </c>
+      <c r="H22" s="80">
+        <v>442</v>
+      </c>
+      <c r="I22" s="81">
+        <v>0</v>
+      </c>
+      <c r="J22" s="82">
+        <v>307</v>
+      </c>
+      <c r="K22" s="82">
+        <v>0</v>
+      </c>
+      <c r="L22" s="82">
+        <v>671</v>
+      </c>
+      <c r="M22" s="82">
+        <v>7</v>
+      </c>
+      <c r="N22" s="82">
+        <v>7</v>
+      </c>
+      <c r="O22" s="82">
+        <v>3</v>
+      </c>
+      <c r="P22" s="82">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="82">
+        <v>66</v>
+      </c>
+      <c r="R22" s="82">
+        <v>1</v>
+      </c>
+      <c r="S22" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="26"/>
@@ -52002,20 +52382,44 @@
       <c r="F23" s="19"/>
       <c r="G23" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H23" s="80"/>
-      <c r="I23" s="81"/>
-      <c r="J23" s="82"/>
-      <c r="K23" s="82"/>
-      <c r="L23" s="82"/>
-      <c r="M23" s="82"/>
-      <c r="N23" s="82"/>
-      <c r="O23" s="82"/>
-      <c r="P23" s="82"/>
-      <c r="Q23" s="82"/>
-      <c r="R23" s="82"/>
-      <c r="S23" s="83"/>
+        <v>22068</v>
+      </c>
+      <c r="H23" s="80">
+        <v>5381</v>
+      </c>
+      <c r="I23" s="81">
+        <v>7598</v>
+      </c>
+      <c r="J23" s="82">
+        <v>3082</v>
+      </c>
+      <c r="K23" s="82">
+        <v>940</v>
+      </c>
+      <c r="L23" s="82">
+        <v>0</v>
+      </c>
+      <c r="M23" s="82">
+        <v>187</v>
+      </c>
+      <c r="N23" s="82">
+        <v>1337</v>
+      </c>
+      <c r="O23" s="82">
+        <v>681</v>
+      </c>
+      <c r="P23" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="82">
+        <v>2862</v>
+      </c>
+      <c r="R23" s="82">
+        <v>0</v>
+      </c>
+      <c r="S23" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="26"/>
@@ -52027,20 +52431,44 @@
       <c r="F24" s="19"/>
       <c r="G24" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H24" s="80"/>
-      <c r="I24" s="81"/>
-      <c r="J24" s="82"/>
-      <c r="K24" s="82"/>
-      <c r="L24" s="82"/>
-      <c r="M24" s="82"/>
-      <c r="N24" s="82"/>
-      <c r="O24" s="82"/>
-      <c r="P24" s="82"/>
-      <c r="Q24" s="82"/>
-      <c r="R24" s="82"/>
-      <c r="S24" s="83"/>
+        <v>11466</v>
+      </c>
+      <c r="H24" s="80">
+        <v>6153</v>
+      </c>
+      <c r="I24" s="81">
+        <v>2551</v>
+      </c>
+      <c r="J24" s="82">
+        <v>544</v>
+      </c>
+      <c r="K24" s="82">
+        <v>0</v>
+      </c>
+      <c r="L24" s="82">
+        <v>702</v>
+      </c>
+      <c r="M24" s="82">
+        <v>114</v>
+      </c>
+      <c r="N24" s="82">
+        <v>141</v>
+      </c>
+      <c r="O24" s="82">
+        <v>687</v>
+      </c>
+      <c r="P24" s="82">
+        <v>55</v>
+      </c>
+      <c r="Q24" s="82">
+        <v>519</v>
+      </c>
+      <c r="R24" s="82">
+        <v>0</v>
+      </c>
+      <c r="S24" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="26"/>
@@ -52052,20 +52480,44 @@
       <c r="F25" s="19"/>
       <c r="G25" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H25" s="80"/>
-      <c r="I25" s="81"/>
-      <c r="J25" s="82"/>
-      <c r="K25" s="82"/>
-      <c r="L25" s="82"/>
-      <c r="M25" s="82"/>
-      <c r="N25" s="82"/>
-      <c r="O25" s="82"/>
-      <c r="P25" s="82"/>
-      <c r="Q25" s="82"/>
-      <c r="R25" s="82"/>
-      <c r="S25" s="83"/>
+        <v>16472</v>
+      </c>
+      <c r="H25" s="80">
+        <v>6917</v>
+      </c>
+      <c r="I25" s="81">
+        <v>7279</v>
+      </c>
+      <c r="J25" s="82">
+        <v>783</v>
+      </c>
+      <c r="K25" s="82">
+        <v>0</v>
+      </c>
+      <c r="L25" s="82">
+        <v>0</v>
+      </c>
+      <c r="M25" s="82">
+        <v>13</v>
+      </c>
+      <c r="N25" s="82">
+        <v>80</v>
+      </c>
+      <c r="O25" s="82">
+        <v>287</v>
+      </c>
+      <c r="P25" s="82">
+        <v>28</v>
+      </c>
+      <c r="Q25" s="82">
+        <v>1085</v>
+      </c>
+      <c r="R25" s="82">
+        <v>0</v>
+      </c>
+      <c r="S25" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="26"/>
@@ -52077,20 +52529,40 @@
       <c r="F26" s="19"/>
       <c r="G26" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H26" s="80"/>
-      <c r="I26" s="81"/>
+        <v>1084</v>
+      </c>
+      <c r="H26" s="80">
+        <v>442</v>
+      </c>
+      <c r="I26" s="81">
+        <v>0</v>
+      </c>
       <c r="J26" s="82"/>
       <c r="K26" s="82"/>
-      <c r="L26" s="82"/>
-      <c r="M26" s="82"/>
-      <c r="N26" s="82"/>
-      <c r="O26" s="82"/>
-      <c r="P26" s="82"/>
-      <c r="Q26" s="82"/>
-      <c r="R26" s="82"/>
-      <c r="S26" s="83"/>
+      <c r="L26" s="82">
+        <v>0</v>
+      </c>
+      <c r="M26" s="82">
+        <v>0</v>
+      </c>
+      <c r="N26" s="82">
+        <v>113</v>
+      </c>
+      <c r="O26" s="82">
+        <v>37</v>
+      </c>
+      <c r="P26" s="82">
+        <v>58</v>
+      </c>
+      <c r="Q26" s="82">
+        <v>434</v>
+      </c>
+      <c r="R26" s="82">
+        <v>0</v>
+      </c>
+      <c r="S26" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="26"/>
@@ -52102,20 +52574,40 @@
       <c r="F27" s="19"/>
       <c r="G27" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H27" s="80"/>
-      <c r="I27" s="81"/>
+        <v>7169</v>
+      </c>
+      <c r="H27" s="80">
+        <v>2548</v>
+      </c>
+      <c r="I27" s="81">
+        <v>0</v>
+      </c>
       <c r="J27" s="82"/>
       <c r="K27" s="82"/>
-      <c r="L27" s="82"/>
-      <c r="M27" s="82"/>
-      <c r="N27" s="82"/>
-      <c r="O27" s="82"/>
-      <c r="P27" s="82"/>
-      <c r="Q27" s="82"/>
-      <c r="R27" s="82"/>
-      <c r="S27" s="83"/>
+      <c r="L27" s="82">
+        <v>0</v>
+      </c>
+      <c r="M27" s="82">
+        <v>30</v>
+      </c>
+      <c r="N27" s="82">
+        <v>1140</v>
+      </c>
+      <c r="O27" s="82">
+        <v>2910</v>
+      </c>
+      <c r="P27" s="82">
+        <v>262</v>
+      </c>
+      <c r="Q27" s="82">
+        <v>279</v>
+      </c>
+      <c r="R27" s="82">
+        <v>0</v>
+      </c>
+      <c r="S27" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="26"/>
@@ -52127,20 +52619,40 @@
       <c r="F28" s="19"/>
       <c r="G28" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H28" s="80"/>
-      <c r="I28" s="81"/>
+        <v>298</v>
+      </c>
+      <c r="H28" s="80">
+        <v>298</v>
+      </c>
+      <c r="I28" s="81">
+        <v>0</v>
+      </c>
       <c r="J28" s="82"/>
       <c r="K28" s="82"/>
-      <c r="L28" s="82"/>
-      <c r="M28" s="82"/>
-      <c r="N28" s="82"/>
-      <c r="O28" s="82"/>
-      <c r="P28" s="82"/>
-      <c r="Q28" s="82"/>
-      <c r="R28" s="82"/>
-      <c r="S28" s="83"/>
+      <c r="L28" s="82">
+        <v>0</v>
+      </c>
+      <c r="M28" s="82">
+        <v>0</v>
+      </c>
+      <c r="N28" s="82">
+        <v>0</v>
+      </c>
+      <c r="O28" s="82">
+        <v>0</v>
+      </c>
+      <c r="P28" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="82">
+        <v>0</v>
+      </c>
+      <c r="R28" s="82">
+        <v>0</v>
+      </c>
+      <c r="S28" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="26"/>
@@ -52152,20 +52664,40 @@
       <c r="F29" s="19"/>
       <c r="G29" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H29" s="80"/>
-      <c r="I29" s="81"/>
+        <v>133</v>
+      </c>
+      <c r="H29" s="80">
+        <v>133</v>
+      </c>
+      <c r="I29" s="81">
+        <v>0</v>
+      </c>
       <c r="J29" s="82"/>
       <c r="K29" s="82"/>
-      <c r="L29" s="82"/>
-      <c r="M29" s="82"/>
-      <c r="N29" s="82"/>
-      <c r="O29" s="82"/>
-      <c r="P29" s="82"/>
-      <c r="Q29" s="82"/>
-      <c r="R29" s="82"/>
-      <c r="S29" s="83"/>
+      <c r="L29" s="82">
+        <v>0</v>
+      </c>
+      <c r="M29" s="82">
+        <v>0</v>
+      </c>
+      <c r="N29" s="82">
+        <v>0</v>
+      </c>
+      <c r="O29" s="82">
+        <v>0</v>
+      </c>
+      <c r="P29" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="82">
+        <v>0</v>
+      </c>
+      <c r="R29" s="82">
+        <v>0</v>
+      </c>
+      <c r="S29" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="26"/>
@@ -52177,20 +52709,44 @@
       <c r="F30" s="19"/>
       <c r="G30" s="86">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H30" s="87"/>
-      <c r="I30" s="88"/>
-      <c r="J30" s="89"/>
-      <c r="K30" s="89"/>
-      <c r="L30" s="89"/>
-      <c r="M30" s="89"/>
-      <c r="N30" s="89"/>
-      <c r="O30" s="89"/>
-      <c r="P30" s="89"/>
-      <c r="Q30" s="89"/>
-      <c r="R30" s="89"/>
-      <c r="S30" s="90"/>
+        <v>5289</v>
+      </c>
+      <c r="H30" s="87">
+        <v>2472</v>
+      </c>
+      <c r="I30" s="88">
+        <v>0</v>
+      </c>
+      <c r="J30" s="89">
+        <v>0</v>
+      </c>
+      <c r="K30" s="89">
+        <v>0</v>
+      </c>
+      <c r="L30" s="89">
+        <v>2641</v>
+      </c>
+      <c r="M30" s="89">
+        <v>0</v>
+      </c>
+      <c r="N30" s="89">
+        <v>10</v>
+      </c>
+      <c r="O30" s="89">
+        <v>0</v>
+      </c>
+      <c r="P30" s="89">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="89">
+        <v>164</v>
+      </c>
+      <c r="R30" s="89">
+        <v>0</v>
+      </c>
+      <c r="S30" s="90">
+        <v>0</v>
+      </c>
     </row>
     <row r="31" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="130" t="s">
@@ -52202,51 +52758,51 @@
       <c r="F31" s="35"/>
       <c r="G31" s="91">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>148968</v>
       </c>
       <c r="H31" s="92">
         <f t="shared" ref="H31:S31" si="1">SUM(H6:H30)</f>
-        <v>0</v>
+        <v>54604</v>
       </c>
       <c r="I31" s="93">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>34651</v>
       </c>
       <c r="J31" s="94">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7807</v>
       </c>
       <c r="K31" s="94">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>991</v>
       </c>
       <c r="L31" s="94">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>26492</v>
       </c>
       <c r="M31" s="94">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1596</v>
       </c>
       <c r="N31" s="94">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6341</v>
       </c>
       <c r="O31" s="94">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6558</v>
       </c>
       <c r="P31" s="94">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1683</v>
       </c>
       <c r="Q31" s="94">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8244</v>
       </c>
       <c r="R31" s="94">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" s="95">
         <f t="shared" si="1"/>
@@ -52263,20 +52819,40 @@
       <c r="F32" s="20"/>
       <c r="G32" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H32" s="80"/>
-      <c r="I32" s="81"/>
-      <c r="J32" s="82"/>
-      <c r="K32" s="82"/>
-      <c r="L32" s="82"/>
-      <c r="M32" s="82"/>
-      <c r="N32" s="82"/>
+        <v>8637</v>
+      </c>
+      <c r="H32" s="80">
+        <v>0</v>
+      </c>
+      <c r="I32" s="81">
+        <v>8485</v>
+      </c>
+      <c r="J32" s="82">
+        <v>0</v>
+      </c>
+      <c r="K32" s="82">
+        <v>0</v>
+      </c>
+      <c r="L32" s="82">
+        <v>0</v>
+      </c>
+      <c r="M32" s="82">
+        <v>0</v>
+      </c>
+      <c r="N32" s="82">
+        <v>152</v>
+      </c>
       <c r="O32" s="82"/>
       <c r="P32" s="82"/>
-      <c r="Q32" s="82"/>
-      <c r="R32" s="82"/>
-      <c r="S32" s="83"/>
+      <c r="Q32" s="82">
+        <v>0</v>
+      </c>
+      <c r="R32" s="82">
+        <v>0</v>
+      </c>
+      <c r="S32" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="33" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="26"/>
@@ -52288,20 +52864,44 @@
       <c r="F33" s="20"/>
       <c r="G33" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H33" s="80"/>
-      <c r="I33" s="81"/>
-      <c r="J33" s="82"/>
-      <c r="K33" s="82"/>
-      <c r="L33" s="82"/>
-      <c r="M33" s="82"/>
-      <c r="N33" s="82"/>
-      <c r="O33" s="82"/>
-      <c r="P33" s="82"/>
-      <c r="Q33" s="82"/>
-      <c r="R33" s="82"/>
-      <c r="S33" s="83"/>
+        <v>6713</v>
+      </c>
+      <c r="H33" s="80">
+        <v>0</v>
+      </c>
+      <c r="I33" s="81">
+        <v>6487</v>
+      </c>
+      <c r="J33" s="82">
+        <v>0</v>
+      </c>
+      <c r="K33" s="82">
+        <v>162</v>
+      </c>
+      <c r="L33" s="82">
+        <v>0</v>
+      </c>
+      <c r="M33" s="82">
+        <v>0</v>
+      </c>
+      <c r="N33" s="82">
+        <v>64</v>
+      </c>
+      <c r="O33" s="82">
+        <v>0</v>
+      </c>
+      <c r="P33" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="82">
+        <v>0</v>
+      </c>
+      <c r="R33" s="82">
+        <v>0</v>
+      </c>
+      <c r="S33" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="34" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="26"/>
@@ -52313,20 +52913,44 @@
       <c r="F34" s="20"/>
       <c r="G34" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H34" s="80"/>
-      <c r="I34" s="81"/>
-      <c r="J34" s="82"/>
-      <c r="K34" s="82"/>
-      <c r="L34" s="82"/>
-      <c r="M34" s="82"/>
-      <c r="N34" s="82"/>
-      <c r="O34" s="82"/>
-      <c r="P34" s="82"/>
-      <c r="Q34" s="82"/>
-      <c r="R34" s="82"/>
-      <c r="S34" s="83"/>
+        <v>11869</v>
+      </c>
+      <c r="H34" s="80">
+        <v>0</v>
+      </c>
+      <c r="I34" s="81">
+        <v>11815</v>
+      </c>
+      <c r="J34" s="82">
+        <v>0</v>
+      </c>
+      <c r="K34" s="82">
+        <v>25</v>
+      </c>
+      <c r="L34" s="82">
+        <v>0</v>
+      </c>
+      <c r="M34" s="82">
+        <v>0</v>
+      </c>
+      <c r="N34" s="82">
+        <v>1</v>
+      </c>
+      <c r="O34" s="82">
+        <v>28</v>
+      </c>
+      <c r="P34" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="82">
+        <v>0</v>
+      </c>
+      <c r="R34" s="82">
+        <v>0</v>
+      </c>
+      <c r="S34" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="35" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="26"/>
@@ -52338,20 +52962,40 @@
       <c r="F35" s="20"/>
       <c r="G35" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H35" s="80"/>
-      <c r="I35" s="81"/>
-      <c r="J35" s="82"/>
-      <c r="K35" s="82"/>
-      <c r="L35" s="82"/>
-      <c r="M35" s="82"/>
-      <c r="N35" s="82"/>
+        <v>690</v>
+      </c>
+      <c r="H35" s="80">
+        <v>0</v>
+      </c>
+      <c r="I35" s="81">
+        <v>674</v>
+      </c>
+      <c r="J35" s="82">
+        <v>16</v>
+      </c>
+      <c r="K35" s="82">
+        <v>0</v>
+      </c>
+      <c r="L35" s="82">
+        <v>0</v>
+      </c>
+      <c r="M35" s="82">
+        <v>0</v>
+      </c>
+      <c r="N35" s="82">
+        <v>0</v>
+      </c>
       <c r="O35" s="82"/>
       <c r="P35" s="82"/>
-      <c r="Q35" s="82"/>
-      <c r="R35" s="82"/>
-      <c r="S35" s="83"/>
+      <c r="Q35" s="82">
+        <v>0</v>
+      </c>
+      <c r="R35" s="82">
+        <v>0</v>
+      </c>
+      <c r="S35" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="36" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="26"/>
@@ -52363,20 +53007,44 @@
       <c r="F36" s="20"/>
       <c r="G36" s="86">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H36" s="87"/>
-      <c r="I36" s="88"/>
-      <c r="J36" s="89"/>
-      <c r="K36" s="89"/>
-      <c r="L36" s="89"/>
-      <c r="M36" s="89"/>
-      <c r="N36" s="89"/>
-      <c r="O36" s="89"/>
-      <c r="P36" s="89"/>
-      <c r="Q36" s="89"/>
-      <c r="R36" s="89"/>
-      <c r="S36" s="90"/>
+        <v>1652</v>
+      </c>
+      <c r="H36" s="87">
+        <v>0</v>
+      </c>
+      <c r="I36" s="88">
+        <v>1650</v>
+      </c>
+      <c r="J36" s="89">
+        <v>0</v>
+      </c>
+      <c r="K36" s="89">
+        <v>0</v>
+      </c>
+      <c r="L36" s="89">
+        <v>0</v>
+      </c>
+      <c r="M36" s="89">
+        <v>0</v>
+      </c>
+      <c r="N36" s="89">
+        <v>2</v>
+      </c>
+      <c r="O36" s="89">
+        <v>0</v>
+      </c>
+      <c r="P36" s="89">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="89">
+        <v>0</v>
+      </c>
+      <c r="R36" s="89">
+        <v>0</v>
+      </c>
+      <c r="S36" s="90">
+        <v>0</v>
+      </c>
     </row>
     <row r="37" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="133" t="s">
@@ -52388,7 +53056,7 @@
       <c r="F37" s="68"/>
       <c r="G37" s="91">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>29561</v>
       </c>
       <c r="H37" s="92">
         <f t="shared" ref="H37:S37" si="2">SUM(H32:H36)</f>
@@ -52396,15 +53064,15 @@
       </c>
       <c r="I37" s="93">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>29111</v>
       </c>
       <c r="J37" s="94">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K37" s="94">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="L37" s="94">
         <f t="shared" si="2"/>
@@ -52416,11 +53084,11 @@
       </c>
       <c r="N37" s="94">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="O37" s="94">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="P37" s="94">
         <f t="shared" si="2"/>
@@ -52449,20 +53117,40 @@
       <c r="F38" s="19"/>
       <c r="G38" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H38" s="80"/>
-      <c r="I38" s="81"/>
+        <v>4894</v>
+      </c>
+      <c r="H38" s="80">
+        <v>0</v>
+      </c>
+      <c r="I38" s="81">
+        <v>0</v>
+      </c>
       <c r="J38" s="82"/>
       <c r="K38" s="82"/>
-      <c r="L38" s="82"/>
-      <c r="M38" s="82"/>
-      <c r="N38" s="82"/>
-      <c r="O38" s="82"/>
-      <c r="P38" s="82"/>
-      <c r="Q38" s="82"/>
-      <c r="R38" s="82"/>
-      <c r="S38" s="83"/>
+      <c r="L38" s="82">
+        <v>4671</v>
+      </c>
+      <c r="M38" s="82">
+        <v>1</v>
+      </c>
+      <c r="N38" s="82">
+        <v>222</v>
+      </c>
+      <c r="O38" s="82">
+        <v>0</v>
+      </c>
+      <c r="P38" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="82">
+        <v>0</v>
+      </c>
+      <c r="R38" s="82">
+        <v>0</v>
+      </c>
+      <c r="S38" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="39" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="26"/>
@@ -52474,20 +53162,40 @@
       <c r="F39" s="19"/>
       <c r="G39" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H39" s="80"/>
-      <c r="I39" s="81"/>
+        <v>2340</v>
+      </c>
+      <c r="H39" s="80">
+        <v>0</v>
+      </c>
+      <c r="I39" s="81">
+        <v>0</v>
+      </c>
       <c r="J39" s="82"/>
       <c r="K39" s="82"/>
-      <c r="L39" s="82"/>
-      <c r="M39" s="82"/>
-      <c r="N39" s="82"/>
-      <c r="O39" s="82"/>
-      <c r="P39" s="82"/>
-      <c r="Q39" s="82"/>
-      <c r="R39" s="82"/>
-      <c r="S39" s="83"/>
+      <c r="L39" s="82">
+        <v>2340</v>
+      </c>
+      <c r="M39" s="82">
+        <v>0</v>
+      </c>
+      <c r="N39" s="82">
+        <v>0</v>
+      </c>
+      <c r="O39" s="82">
+        <v>0</v>
+      </c>
+      <c r="P39" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="82">
+        <v>0</v>
+      </c>
+      <c r="R39" s="82">
+        <v>0</v>
+      </c>
+      <c r="S39" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="40" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="26"/>
@@ -52499,20 +53207,40 @@
       <c r="F40" s="19"/>
       <c r="G40" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H40" s="80"/>
-      <c r="I40" s="81"/>
+        <v>218</v>
+      </c>
+      <c r="H40" s="80">
+        <v>0</v>
+      </c>
+      <c r="I40" s="81">
+        <v>0</v>
+      </c>
       <c r="J40" s="82"/>
       <c r="K40" s="82"/>
-      <c r="L40" s="82"/>
-      <c r="M40" s="82"/>
-      <c r="N40" s="82"/>
-      <c r="O40" s="82"/>
-      <c r="P40" s="82"/>
-      <c r="Q40" s="82"/>
-      <c r="R40" s="82"/>
-      <c r="S40" s="83"/>
+      <c r="L40" s="82">
+        <v>187</v>
+      </c>
+      <c r="M40" s="82">
+        <v>12</v>
+      </c>
+      <c r="N40" s="82">
+        <v>0</v>
+      </c>
+      <c r="O40" s="82">
+        <v>0</v>
+      </c>
+      <c r="P40" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="82">
+        <v>19</v>
+      </c>
+      <c r="R40" s="82">
+        <v>0</v>
+      </c>
+      <c r="S40" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="41" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="26"/>
@@ -52524,20 +53252,40 @@
       <c r="F41" s="20"/>
       <c r="G41" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H41" s="80"/>
-      <c r="I41" s="81"/>
+        <v>2180</v>
+      </c>
+      <c r="H41" s="80">
+        <v>0</v>
+      </c>
+      <c r="I41" s="81">
+        <v>0</v>
+      </c>
       <c r="J41" s="82"/>
       <c r="K41" s="82"/>
-      <c r="L41" s="82"/>
-      <c r="M41" s="82"/>
-      <c r="N41" s="82"/>
-      <c r="O41" s="82"/>
-      <c r="P41" s="82"/>
-      <c r="Q41" s="82"/>
-      <c r="R41" s="82"/>
-      <c r="S41" s="83"/>
+      <c r="L41" s="82">
+        <v>1895</v>
+      </c>
+      <c r="M41" s="82">
+        <v>264</v>
+      </c>
+      <c r="N41" s="82">
+        <v>11</v>
+      </c>
+      <c r="O41" s="82">
+        <v>0</v>
+      </c>
+      <c r="P41" s="82">
+        <v>10</v>
+      </c>
+      <c r="Q41" s="82">
+        <v>0</v>
+      </c>
+      <c r="R41" s="82">
+        <v>0</v>
+      </c>
+      <c r="S41" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="42" spans="2:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="26"/>
@@ -52549,20 +53297,40 @@
       <c r="F42" s="20"/>
       <c r="G42" s="86">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H42" s="87"/>
-      <c r="I42" s="88"/>
+        <v>16123</v>
+      </c>
+      <c r="H42" s="87">
+        <v>0</v>
+      </c>
+      <c r="I42" s="88">
+        <v>0</v>
+      </c>
       <c r="J42" s="89"/>
       <c r="K42" s="89"/>
-      <c r="L42" s="89"/>
-      <c r="M42" s="89"/>
-      <c r="N42" s="89"/>
-      <c r="O42" s="89"/>
-      <c r="P42" s="89"/>
-      <c r="Q42" s="89"/>
-      <c r="R42" s="89"/>
-      <c r="S42" s="90"/>
+      <c r="L42" s="89">
+        <v>12555</v>
+      </c>
+      <c r="M42" s="89">
+        <v>1330</v>
+      </c>
+      <c r="N42" s="89">
+        <v>299</v>
+      </c>
+      <c r="O42" s="89">
+        <v>1130</v>
+      </c>
+      <c r="P42" s="89">
+        <v>809</v>
+      </c>
+      <c r="Q42" s="89">
+        <v>0</v>
+      </c>
+      <c r="R42" s="89">
+        <v>0</v>
+      </c>
+      <c r="S42" s="90">
+        <v>0</v>
+      </c>
     </row>
     <row r="43" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="133" t="s">
@@ -52574,7 +53342,7 @@
       <c r="F43" s="22"/>
       <c r="G43" s="91">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>25755</v>
       </c>
       <c r="H43" s="92">
         <f t="shared" ref="H43:S43" si="3">SUM(H38:H42)</f>
@@ -52594,27 +53362,27 @@
       </c>
       <c r="L43" s="94">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>21648</v>
       </c>
       <c r="M43" s="94">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1607</v>
       </c>
       <c r="N43" s="94">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>532</v>
       </c>
       <c r="O43" s="94">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1130</v>
       </c>
       <c r="P43" s="94">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>819</v>
       </c>
       <c r="Q43" s="94">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R43" s="94">
         <f t="shared" si="3"/>
@@ -52635,20 +53403,44 @@
       <c r="F44" s="19"/>
       <c r="G44" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H44" s="80"/>
-      <c r="I44" s="81"/>
-      <c r="J44" s="82"/>
-      <c r="K44" s="82"/>
-      <c r="L44" s="82"/>
-      <c r="M44" s="82"/>
-      <c r="N44" s="82"/>
-      <c r="O44" s="82"/>
-      <c r="P44" s="82"/>
-      <c r="Q44" s="82"/>
-      <c r="R44" s="82"/>
-      <c r="S44" s="83"/>
+        <v>6845</v>
+      </c>
+      <c r="H44" s="80">
+        <v>0</v>
+      </c>
+      <c r="I44" s="81">
+        <v>0</v>
+      </c>
+      <c r="J44" s="82">
+        <v>0</v>
+      </c>
+      <c r="K44" s="82">
+        <v>5326</v>
+      </c>
+      <c r="L44" s="82">
+        <v>0</v>
+      </c>
+      <c r="M44" s="82">
+        <v>0</v>
+      </c>
+      <c r="N44" s="82">
+        <v>1355</v>
+      </c>
+      <c r="O44" s="82">
+        <v>164</v>
+      </c>
+      <c r="P44" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="82">
+        <v>0</v>
+      </c>
+      <c r="R44" s="82">
+        <v>0</v>
+      </c>
+      <c r="S44" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="45" spans="2:19" s="21" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="26"/>
@@ -52660,20 +53452,44 @@
       <c r="F45" s="19"/>
       <c r="G45" s="86">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H45" s="87"/>
-      <c r="I45" s="88"/>
-      <c r="J45" s="89"/>
-      <c r="K45" s="89"/>
-      <c r="L45" s="89"/>
-      <c r="M45" s="89"/>
-      <c r="N45" s="89"/>
-      <c r="O45" s="89"/>
-      <c r="P45" s="89"/>
-      <c r="Q45" s="89"/>
-      <c r="R45" s="89"/>
-      <c r="S45" s="90"/>
+        <v>16801</v>
+      </c>
+      <c r="H45" s="87">
+        <v>0</v>
+      </c>
+      <c r="I45" s="88">
+        <v>12095</v>
+      </c>
+      <c r="J45" s="89">
+        <v>819</v>
+      </c>
+      <c r="K45" s="89">
+        <v>969</v>
+      </c>
+      <c r="L45" s="89">
+        <v>1865</v>
+      </c>
+      <c r="M45" s="89">
+        <v>0</v>
+      </c>
+      <c r="N45" s="89">
+        <v>43</v>
+      </c>
+      <c r="O45" s="89">
+        <v>429</v>
+      </c>
+      <c r="P45" s="89">
+        <v>22</v>
+      </c>
+      <c r="Q45" s="89">
+        <v>559</v>
+      </c>
+      <c r="R45" s="89">
+        <v>0</v>
+      </c>
+      <c r="S45" s="90">
+        <v>0</v>
+      </c>
     </row>
     <row r="46" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="133" t="s">
@@ -52685,7 +53501,7 @@
       <c r="F46" s="22"/>
       <c r="G46" s="91">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>23646</v>
       </c>
       <c r="H46" s="92">
         <f t="shared" ref="H46:S46" si="4">SUM(H44:H45)</f>
@@ -52693,19 +53509,19 @@
       </c>
       <c r="I46" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>12095</v>
       </c>
       <c r="J46" s="94">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>819</v>
       </c>
       <c r="K46" s="94">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6295</v>
       </c>
       <c r="L46" s="94">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1865</v>
       </c>
       <c r="M46" s="94">
         <f t="shared" si="4"/>
@@ -52713,19 +53529,19 @@
       </c>
       <c r="N46" s="94">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1398</v>
       </c>
       <c r="O46" s="94">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>593</v>
       </c>
       <c r="P46" s="94">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q46" s="94">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="R46" s="94">
         <f t="shared" si="4"/>
@@ -52832,20 +53648,40 @@
       <c r="F49" s="20"/>
       <c r="G49" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H49" s="80"/>
-      <c r="I49" s="81"/>
+        <v>4665</v>
+      </c>
+      <c r="H49" s="80">
+        <v>0</v>
+      </c>
+      <c r="I49" s="81">
+        <v>0</v>
+      </c>
       <c r="J49" s="82"/>
       <c r="K49" s="82"/>
-      <c r="L49" s="82"/>
-      <c r="M49" s="82"/>
-      <c r="N49" s="82"/>
-      <c r="O49" s="82"/>
-      <c r="P49" s="82"/>
-      <c r="Q49" s="82"/>
-      <c r="R49" s="82"/>
-      <c r="S49" s="84"/>
+      <c r="L49" s="82">
+        <v>0</v>
+      </c>
+      <c r="M49" s="82">
+        <v>293</v>
+      </c>
+      <c r="N49" s="82">
+        <v>2674</v>
+      </c>
+      <c r="O49" s="82">
+        <v>1298</v>
+      </c>
+      <c r="P49" s="82">
+        <v>289</v>
+      </c>
+      <c r="Q49" s="82">
+        <v>111</v>
+      </c>
+      <c r="R49" s="82">
+        <v>0</v>
+      </c>
+      <c r="S49" s="84">
+        <v>0</v>
+      </c>
     </row>
     <row r="50" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="26"/>
@@ -52857,20 +53693,40 @@
       <c r="F50" s="20"/>
       <c r="G50" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H50" s="80"/>
-      <c r="I50" s="81"/>
+        <v>390</v>
+      </c>
+      <c r="H50" s="80">
+        <v>0</v>
+      </c>
+      <c r="I50" s="81">
+        <v>0</v>
+      </c>
       <c r="J50" s="82"/>
       <c r="K50" s="82"/>
-      <c r="L50" s="82"/>
-      <c r="M50" s="82"/>
-      <c r="N50" s="82"/>
-      <c r="O50" s="82"/>
-      <c r="P50" s="82"/>
-      <c r="Q50" s="82"/>
-      <c r="R50" s="82"/>
-      <c r="S50" s="84"/>
+      <c r="L50" s="82">
+        <v>0</v>
+      </c>
+      <c r="M50" s="82">
+        <v>0</v>
+      </c>
+      <c r="N50" s="82">
+        <v>0</v>
+      </c>
+      <c r="O50" s="82">
+        <v>0</v>
+      </c>
+      <c r="P50" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="82">
+        <v>0</v>
+      </c>
+      <c r="R50" s="82">
+        <v>0</v>
+      </c>
+      <c r="S50" s="84">
+        <v>390</v>
+      </c>
     </row>
     <row r="51" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="26"/>
@@ -52882,20 +53738,44 @@
       <c r="F51" s="20"/>
       <c r="G51" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H51" s="80"/>
-      <c r="I51" s="81"/>
-      <c r="J51" s="82"/>
-      <c r="K51" s="82"/>
-      <c r="L51" s="82"/>
-      <c r="M51" s="82"/>
-      <c r="N51" s="82"/>
-      <c r="O51" s="82"/>
-      <c r="P51" s="82"/>
-      <c r="Q51" s="82"/>
-      <c r="R51" s="82"/>
-      <c r="S51" s="84"/>
+        <v>1301</v>
+      </c>
+      <c r="H51" s="80">
+        <v>0</v>
+      </c>
+      <c r="I51" s="81">
+        <v>0</v>
+      </c>
+      <c r="J51" s="82">
+        <v>0</v>
+      </c>
+      <c r="K51" s="82">
+        <v>0</v>
+      </c>
+      <c r="L51" s="82">
+        <v>0</v>
+      </c>
+      <c r="M51" s="82">
+        <v>0</v>
+      </c>
+      <c r="N51" s="82">
+        <v>0</v>
+      </c>
+      <c r="O51" s="82">
+        <v>0</v>
+      </c>
+      <c r="P51" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="82">
+        <v>0</v>
+      </c>
+      <c r="R51" s="82">
+        <v>0</v>
+      </c>
+      <c r="S51" s="84">
+        <v>1301</v>
+      </c>
     </row>
     <row r="52" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="26"/>
@@ -52907,20 +53787,40 @@
       <c r="F52" s="19"/>
       <c r="G52" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H52" s="80"/>
-      <c r="I52" s="81"/>
+        <v>424</v>
+      </c>
+      <c r="H52" s="80">
+        <v>0</v>
+      </c>
+      <c r="I52" s="81">
+        <v>0</v>
+      </c>
       <c r="J52" s="82"/>
       <c r="K52" s="82"/>
-      <c r="L52" s="82"/>
-      <c r="M52" s="82"/>
-      <c r="N52" s="82"/>
-      <c r="O52" s="82"/>
-      <c r="P52" s="82"/>
-      <c r="Q52" s="82"/>
-      <c r="R52" s="82"/>
-      <c r="S52" s="84"/>
+      <c r="L52" s="82">
+        <v>0</v>
+      </c>
+      <c r="M52" s="82">
+        <v>254</v>
+      </c>
+      <c r="N52" s="82">
+        <v>0</v>
+      </c>
+      <c r="O52" s="82">
+        <v>0</v>
+      </c>
+      <c r="P52" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="82">
+        <v>0</v>
+      </c>
+      <c r="R52" s="82">
+        <v>0</v>
+      </c>
+      <c r="S52" s="84">
+        <v>170</v>
+      </c>
     </row>
     <row r="53" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="26"/>
@@ -52932,20 +53832,40 @@
       <c r="F53" s="19"/>
       <c r="G53" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H53" s="80"/>
-      <c r="I53" s="81"/>
+        <v>1578</v>
+      </c>
+      <c r="H53" s="80">
+        <v>0</v>
+      </c>
+      <c r="I53" s="81">
+        <v>0</v>
+      </c>
       <c r="J53" s="82"/>
       <c r="K53" s="82"/>
-      <c r="L53" s="82"/>
-      <c r="M53" s="82"/>
-      <c r="N53" s="82"/>
-      <c r="O53" s="82"/>
-      <c r="P53" s="82"/>
-      <c r="Q53" s="82"/>
-      <c r="R53" s="82"/>
-      <c r="S53" s="84"/>
+      <c r="L53" s="82">
+        <v>0</v>
+      </c>
+      <c r="M53" s="82">
+        <v>0</v>
+      </c>
+      <c r="N53" s="82">
+        <v>0</v>
+      </c>
+      <c r="O53" s="82">
+        <v>0</v>
+      </c>
+      <c r="P53" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="82">
+        <v>0</v>
+      </c>
+      <c r="R53" s="82">
+        <v>0</v>
+      </c>
+      <c r="S53" s="84">
+        <v>1578</v>
+      </c>
     </row>
     <row r="54" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="26"/>
@@ -52957,20 +53877,44 @@
       <c r="F54" s="20"/>
       <c r="G54" s="79">
         <f>SUM(H54:S54)</f>
-        <v>0</v>
-      </c>
-      <c r="H54" s="80"/>
-      <c r="I54" s="81"/>
-      <c r="J54" s="82"/>
-      <c r="K54" s="82"/>
-      <c r="L54" s="82"/>
-      <c r="M54" s="82"/>
-      <c r="N54" s="82"/>
-      <c r="O54" s="82"/>
-      <c r="P54" s="82"/>
-      <c r="Q54" s="82"/>
-      <c r="R54" s="82"/>
-      <c r="S54" s="84"/>
+        <v>2719</v>
+      </c>
+      <c r="H54" s="80">
+        <v>0</v>
+      </c>
+      <c r="I54" s="81">
+        <v>0</v>
+      </c>
+      <c r="J54" s="82">
+        <v>0</v>
+      </c>
+      <c r="K54" s="82">
+        <v>714</v>
+      </c>
+      <c r="L54" s="82">
+        <v>0</v>
+      </c>
+      <c r="M54" s="82">
+        <v>5</v>
+      </c>
+      <c r="N54" s="82">
+        <v>1218</v>
+      </c>
+      <c r="O54" s="82">
+        <v>398</v>
+      </c>
+      <c r="P54" s="82">
+        <v>92</v>
+      </c>
+      <c r="Q54" s="82">
+        <v>288</v>
+      </c>
+      <c r="R54" s="82">
+        <v>0</v>
+      </c>
+      <c r="S54" s="84">
+        <v>4</v>
+      </c>
     </row>
     <row r="55" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="26"/>
@@ -52982,20 +53926,44 @@
       <c r="F55" s="59"/>
       <c r="G55" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H55" s="80"/>
-      <c r="I55" s="81"/>
-      <c r="J55" s="82"/>
-      <c r="K55" s="82"/>
-      <c r="L55" s="82"/>
-      <c r="M55" s="82"/>
-      <c r="N55" s="82"/>
-      <c r="O55" s="82"/>
-      <c r="P55" s="82"/>
-      <c r="Q55" s="82"/>
-      <c r="R55" s="82"/>
-      <c r="S55" s="84"/>
+        <v>4957</v>
+      </c>
+      <c r="H55" s="80">
+        <v>0</v>
+      </c>
+      <c r="I55" s="81">
+        <v>0</v>
+      </c>
+      <c r="J55" s="82">
+        <v>0</v>
+      </c>
+      <c r="K55" s="82">
+        <v>1120</v>
+      </c>
+      <c r="L55" s="82">
+        <v>0</v>
+      </c>
+      <c r="M55" s="82">
+        <v>0</v>
+      </c>
+      <c r="N55" s="82">
+        <v>869</v>
+      </c>
+      <c r="O55" s="82">
+        <v>435</v>
+      </c>
+      <c r="P55" s="82">
+        <v>107</v>
+      </c>
+      <c r="Q55" s="82">
+        <v>89</v>
+      </c>
+      <c r="R55" s="82">
+        <v>0</v>
+      </c>
+      <c r="S55" s="84">
+        <v>2337</v>
+      </c>
     </row>
     <row r="56" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="26"/>
@@ -53007,20 +53975,40 @@
       <c r="F56" s="19"/>
       <c r="G56" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H56" s="80"/>
-      <c r="I56" s="81"/>
+        <v>56</v>
+      </c>
+      <c r="H56" s="80">
+        <v>0</v>
+      </c>
+      <c r="I56" s="81">
+        <v>0</v>
+      </c>
       <c r="J56" s="82"/>
       <c r="K56" s="82"/>
-      <c r="L56" s="82"/>
-      <c r="M56" s="82"/>
-      <c r="N56" s="82"/>
-      <c r="O56" s="82"/>
-      <c r="P56" s="82"/>
-      <c r="Q56" s="82"/>
-      <c r="R56" s="82"/>
-      <c r="S56" s="84"/>
+      <c r="L56" s="82">
+        <v>0</v>
+      </c>
+      <c r="M56" s="82">
+        <v>0</v>
+      </c>
+      <c r="N56" s="82">
+        <v>0</v>
+      </c>
+      <c r="O56" s="82">
+        <v>0</v>
+      </c>
+      <c r="P56" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="82">
+        <v>0</v>
+      </c>
+      <c r="R56" s="82">
+        <v>0</v>
+      </c>
+      <c r="S56" s="84">
+        <v>56</v>
+      </c>
     </row>
     <row r="57" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="26"/>
@@ -53032,20 +54020,44 @@
       <c r="F57" s="19"/>
       <c r="G57" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H57" s="80"/>
-      <c r="I57" s="81"/>
-      <c r="J57" s="82"/>
-      <c r="K57" s="82"/>
-      <c r="L57" s="82"/>
-      <c r="M57" s="82"/>
-      <c r="N57" s="82"/>
-      <c r="O57" s="82"/>
-      <c r="P57" s="82"/>
-      <c r="Q57" s="82"/>
-      <c r="R57" s="82"/>
-      <c r="S57" s="84"/>
+        <v>1378</v>
+      </c>
+      <c r="H57" s="80">
+        <v>0</v>
+      </c>
+      <c r="I57" s="81">
+        <v>0</v>
+      </c>
+      <c r="J57" s="82">
+        <v>0</v>
+      </c>
+      <c r="K57" s="82">
+        <v>0</v>
+      </c>
+      <c r="L57" s="82">
+        <v>0</v>
+      </c>
+      <c r="M57" s="82">
+        <v>0</v>
+      </c>
+      <c r="N57" s="82">
+        <v>373</v>
+      </c>
+      <c r="O57" s="82">
+        <v>397</v>
+      </c>
+      <c r="P57" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="82">
+        <v>0</v>
+      </c>
+      <c r="R57" s="82">
+        <v>0</v>
+      </c>
+      <c r="S57" s="84">
+        <v>608</v>
+      </c>
     </row>
     <row r="58" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="26"/>
@@ -53057,20 +54069,40 @@
       <c r="F58" s="20"/>
       <c r="G58" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H58" s="80"/>
-      <c r="I58" s="81"/>
+        <v>43</v>
+      </c>
+      <c r="H58" s="80">
+        <v>0</v>
+      </c>
+      <c r="I58" s="81">
+        <v>0</v>
+      </c>
       <c r="J58" s="82"/>
       <c r="K58" s="82"/>
-      <c r="L58" s="82"/>
-      <c r="M58" s="82"/>
-      <c r="N58" s="82"/>
-      <c r="O58" s="82"/>
-      <c r="P58" s="82"/>
-      <c r="Q58" s="82"/>
-      <c r="R58" s="82"/>
-      <c r="S58" s="84"/>
+      <c r="L58" s="82">
+        <v>0</v>
+      </c>
+      <c r="M58" s="82">
+        <v>0</v>
+      </c>
+      <c r="N58" s="82">
+        <v>0</v>
+      </c>
+      <c r="O58" s="82">
+        <v>0</v>
+      </c>
+      <c r="P58" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="82">
+        <v>0</v>
+      </c>
+      <c r="R58" s="82">
+        <v>0</v>
+      </c>
+      <c r="S58" s="84">
+        <v>43</v>
+      </c>
     </row>
     <row r="59" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="26"/>
@@ -53082,20 +54114,40 @@
       <c r="F59" s="20"/>
       <c r="G59" s="86">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H59" s="87"/>
-      <c r="I59" s="88"/>
+        <v>910</v>
+      </c>
+      <c r="H59" s="87">
+        <v>0</v>
+      </c>
+      <c r="I59" s="88">
+        <v>0</v>
+      </c>
       <c r="J59" s="89"/>
       <c r="K59" s="89"/>
-      <c r="L59" s="89"/>
-      <c r="M59" s="89"/>
-      <c r="N59" s="89"/>
-      <c r="O59" s="89"/>
-      <c r="P59" s="89"/>
-      <c r="Q59" s="89"/>
-      <c r="R59" s="89"/>
-      <c r="S59" s="101"/>
+      <c r="L59" s="89">
+        <v>0</v>
+      </c>
+      <c r="M59" s="89">
+        <v>0</v>
+      </c>
+      <c r="N59" s="89">
+        <v>166</v>
+      </c>
+      <c r="O59" s="89">
+        <v>1</v>
+      </c>
+      <c r="P59" s="89">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="89">
+        <v>707</v>
+      </c>
+      <c r="R59" s="89">
+        <v>0</v>
+      </c>
+      <c r="S59" s="101">
+        <v>33</v>
+      </c>
     </row>
     <row r="60" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="133" t="s">
@@ -53107,7 +54159,7 @@
       <c r="F60" s="22"/>
       <c r="G60" s="102">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>18421</v>
       </c>
       <c r="H60" s="103">
         <f t="shared" ref="H60:S60" si="6">SUM(H49:H59)</f>
@@ -53123,7 +54175,7 @@
       </c>
       <c r="K60" s="105">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1834</v>
       </c>
       <c r="L60" s="105">
         <f t="shared" si="6"/>
@@ -53131,23 +54183,23 @@
       </c>
       <c r="M60" s="105">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>552</v>
       </c>
       <c r="N60" s="105">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="O60" s="105">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2529</v>
       </c>
       <c r="P60" s="105">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>491</v>
       </c>
       <c r="Q60" s="105">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1195</v>
       </c>
       <c r="R60" s="105">
         <f t="shared" si="6"/>
@@ -53155,7 +54207,7 @@
       </c>
       <c r="S60" s="106">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>6520</v>
       </c>
     </row>
     <row r="61" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -53168,20 +54220,40 @@
       <c r="F61" s="20"/>
       <c r="G61" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H61" s="80"/>
-      <c r="I61" s="81"/>
+        <v>981</v>
+      </c>
+      <c r="H61" s="80">
+        <v>0</v>
+      </c>
+      <c r="I61" s="81">
+        <v>0</v>
+      </c>
       <c r="J61" s="82"/>
       <c r="K61" s="82"/>
-      <c r="L61" s="82"/>
-      <c r="M61" s="82"/>
-      <c r="N61" s="82"/>
-      <c r="O61" s="82"/>
-      <c r="P61" s="82"/>
-      <c r="Q61" s="82"/>
-      <c r="R61" s="82"/>
-      <c r="S61" s="84"/>
+      <c r="L61" s="82">
+        <v>0</v>
+      </c>
+      <c r="M61" s="82">
+        <v>0</v>
+      </c>
+      <c r="N61" s="82">
+        <v>0</v>
+      </c>
+      <c r="O61" s="82">
+        <v>0</v>
+      </c>
+      <c r="P61" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="82">
+        <v>0</v>
+      </c>
+      <c r="R61" s="82">
+        <v>981</v>
+      </c>
+      <c r="S61" s="84">
+        <v>0</v>
+      </c>
     </row>
     <row r="62" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="26"/>
@@ -53193,20 +54265,40 @@
       <c r="F62" s="20"/>
       <c r="G62" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H62" s="80"/>
-      <c r="I62" s="81"/>
+        <v>78</v>
+      </c>
+      <c r="H62" s="80">
+        <v>0</v>
+      </c>
+      <c r="I62" s="81">
+        <v>0</v>
+      </c>
       <c r="J62" s="82"/>
       <c r="K62" s="82"/>
-      <c r="L62" s="82"/>
-      <c r="M62" s="82"/>
-      <c r="N62" s="82"/>
-      <c r="O62" s="82"/>
-      <c r="P62" s="82"/>
-      <c r="Q62" s="82"/>
-      <c r="R62" s="82"/>
-      <c r="S62" s="84"/>
+      <c r="L62" s="82">
+        <v>0</v>
+      </c>
+      <c r="M62" s="82">
+        <v>0</v>
+      </c>
+      <c r="N62" s="82">
+        <v>0</v>
+      </c>
+      <c r="O62" s="82">
+        <v>0</v>
+      </c>
+      <c r="P62" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="82">
+        <v>0</v>
+      </c>
+      <c r="R62" s="82">
+        <v>78</v>
+      </c>
+      <c r="S62" s="84">
+        <v>0</v>
+      </c>
     </row>
     <row r="63" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="26"/>
@@ -53218,20 +54310,40 @@
       <c r="F63" s="20"/>
       <c r="G63" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H63" s="80"/>
-      <c r="I63" s="81"/>
+        <v>10649</v>
+      </c>
+      <c r="H63" s="80">
+        <v>0</v>
+      </c>
+      <c r="I63" s="81">
+        <v>0</v>
+      </c>
       <c r="J63" s="82"/>
       <c r="K63" s="82"/>
-      <c r="L63" s="82"/>
-      <c r="M63" s="82"/>
-      <c r="N63" s="82"/>
-      <c r="O63" s="82"/>
-      <c r="P63" s="82"/>
-      <c r="Q63" s="82"/>
-      <c r="R63" s="82"/>
-      <c r="S63" s="84"/>
+      <c r="L63" s="82">
+        <v>0</v>
+      </c>
+      <c r="M63" s="82">
+        <v>0</v>
+      </c>
+      <c r="N63" s="82">
+        <v>38</v>
+      </c>
+      <c r="O63" s="82">
+        <v>0</v>
+      </c>
+      <c r="P63" s="82">
+        <v>1258</v>
+      </c>
+      <c r="Q63" s="82">
+        <v>220</v>
+      </c>
+      <c r="R63" s="82">
+        <v>9133</v>
+      </c>
+      <c r="S63" s="84">
+        <v>0</v>
+      </c>
     </row>
     <row r="64" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="26"/>
@@ -53243,20 +54355,44 @@
       <c r="F64" s="20"/>
       <c r="G64" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H64" s="80"/>
-      <c r="I64" s="81"/>
-      <c r="J64" s="82"/>
-      <c r="K64" s="82"/>
-      <c r="L64" s="82"/>
-      <c r="M64" s="82"/>
-      <c r="N64" s="82"/>
-      <c r="O64" s="82"/>
-      <c r="P64" s="82"/>
-      <c r="Q64" s="82"/>
-      <c r="R64" s="82"/>
-      <c r="S64" s="84"/>
+        <v>11497</v>
+      </c>
+      <c r="H64" s="80">
+        <v>0</v>
+      </c>
+      <c r="I64" s="81">
+        <v>0</v>
+      </c>
+      <c r="J64" s="82">
+        <v>0</v>
+      </c>
+      <c r="K64" s="82">
+        <v>0</v>
+      </c>
+      <c r="L64" s="82">
+        <v>0</v>
+      </c>
+      <c r="M64" s="82">
+        <v>0</v>
+      </c>
+      <c r="N64" s="82">
+        <v>76</v>
+      </c>
+      <c r="O64" s="82">
+        <v>0</v>
+      </c>
+      <c r="P64" s="82">
+        <v>450</v>
+      </c>
+      <c r="Q64" s="82">
+        <v>99</v>
+      </c>
+      <c r="R64" s="82">
+        <v>10872</v>
+      </c>
+      <c r="S64" s="84">
+        <v>0</v>
+      </c>
     </row>
     <row r="65" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="26"/>
@@ -53268,20 +54404,40 @@
       <c r="F65" s="20"/>
       <c r="G65" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H65" s="80"/>
-      <c r="I65" s="81"/>
+        <v>5428</v>
+      </c>
+      <c r="H65" s="80">
+        <v>0</v>
+      </c>
+      <c r="I65" s="81">
+        <v>0</v>
+      </c>
       <c r="J65" s="82"/>
       <c r="K65" s="82"/>
-      <c r="L65" s="82"/>
-      <c r="M65" s="82"/>
-      <c r="N65" s="82"/>
-      <c r="O65" s="82"/>
-      <c r="P65" s="82"/>
-      <c r="Q65" s="82"/>
-      <c r="R65" s="82"/>
-      <c r="S65" s="84"/>
+      <c r="L65" s="82">
+        <v>0</v>
+      </c>
+      <c r="M65" s="82">
+        <v>86</v>
+      </c>
+      <c r="N65" s="82">
+        <v>203</v>
+      </c>
+      <c r="O65" s="82">
+        <v>113</v>
+      </c>
+      <c r="P65" s="82">
+        <v>58</v>
+      </c>
+      <c r="Q65" s="82">
+        <v>78</v>
+      </c>
+      <c r="R65" s="82">
+        <v>4890</v>
+      </c>
+      <c r="S65" s="84">
+        <v>0</v>
+      </c>
     </row>
     <row r="66" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="26"/>
@@ -53293,20 +54449,40 @@
       <c r="F66" s="20"/>
       <c r="G66" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H66" s="80"/>
-      <c r="I66" s="81"/>
+        <v>662</v>
+      </c>
+      <c r="H66" s="80">
+        <v>0</v>
+      </c>
+      <c r="I66" s="81">
+        <v>0</v>
+      </c>
       <c r="J66" s="82"/>
       <c r="K66" s="82"/>
-      <c r="L66" s="82"/>
-      <c r="M66" s="82"/>
-      <c r="N66" s="82"/>
-      <c r="O66" s="82"/>
-      <c r="P66" s="82"/>
-      <c r="Q66" s="82"/>
-      <c r="R66" s="82"/>
-      <c r="S66" s="84"/>
+      <c r="L66" s="82">
+        <v>0</v>
+      </c>
+      <c r="M66" s="82">
+        <v>0</v>
+      </c>
+      <c r="N66" s="82">
+        <v>0</v>
+      </c>
+      <c r="O66" s="82">
+        <v>0</v>
+      </c>
+      <c r="P66" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="82">
+        <v>6</v>
+      </c>
+      <c r="R66" s="82">
+        <v>656</v>
+      </c>
+      <c r="S66" s="84">
+        <v>0</v>
+      </c>
     </row>
     <row r="67" spans="2:19" ht="14.85" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="26"/>
@@ -53343,20 +54519,40 @@
       <c r="F68" s="20"/>
       <c r="G68" s="86">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H68" s="87"/>
-      <c r="I68" s="88"/>
+        <v>71</v>
+      </c>
+      <c r="H68" s="87">
+        <v>0</v>
+      </c>
+      <c r="I68" s="88">
+        <v>0</v>
+      </c>
       <c r="J68" s="89"/>
       <c r="K68" s="89"/>
-      <c r="L68" s="89"/>
-      <c r="M68" s="89"/>
-      <c r="N68" s="89"/>
-      <c r="O68" s="89"/>
-      <c r="P68" s="89"/>
-      <c r="Q68" s="89"/>
-      <c r="R68" s="89"/>
-      <c r="S68" s="101"/>
+      <c r="L68" s="89">
+        <v>0</v>
+      </c>
+      <c r="M68" s="89">
+        <v>0</v>
+      </c>
+      <c r="N68" s="89">
+        <v>0</v>
+      </c>
+      <c r="O68" s="89">
+        <v>0</v>
+      </c>
+      <c r="P68" s="89">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="89">
+        <v>0</v>
+      </c>
+      <c r="R68" s="89">
+        <v>71</v>
+      </c>
+      <c r="S68" s="101">
+        <v>0</v>
+      </c>
     </row>
     <row r="69" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="133" t="s">
@@ -53368,7 +54564,7 @@
       <c r="F69" s="22"/>
       <c r="G69" s="102">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>29366</v>
       </c>
       <c r="H69" s="103">
         <f>SUM(H61:H68)</f>
@@ -53392,27 +54588,27 @@
       </c>
       <c r="M69" s="105">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N69" s="105">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>317</v>
       </c>
       <c r="O69" s="105">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="P69" s="105">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1766</v>
       </c>
       <c r="Q69" s="105">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>403</v>
       </c>
       <c r="R69" s="105">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>26681</v>
       </c>
       <c r="S69" s="106">
         <f t="shared" si="7"/>
@@ -53429,20 +54625,36 @@
       <c r="F70" s="19"/>
       <c r="G70" s="96">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H70" s="97"/>
-      <c r="I70" s="98"/>
+        <v>7</v>
+      </c>
+      <c r="H70" s="97">
+        <v>0</v>
+      </c>
+      <c r="I70" s="98">
+        <v>0</v>
+      </c>
       <c r="J70" s="99"/>
       <c r="K70" s="99"/>
-      <c r="L70" s="99"/>
-      <c r="M70" s="99"/>
-      <c r="N70" s="99"/>
+      <c r="L70" s="99">
+        <v>0</v>
+      </c>
+      <c r="M70" s="99">
+        <v>0</v>
+      </c>
+      <c r="N70" s="99">
+        <v>0</v>
+      </c>
       <c r="O70" s="99"/>
       <c r="P70" s="99"/>
-      <c r="Q70" s="99"/>
-      <c r="R70" s="99"/>
-      <c r="S70" s="100"/>
+      <c r="Q70" s="99">
+        <v>7</v>
+      </c>
+      <c r="R70" s="99">
+        <v>0</v>
+      </c>
+      <c r="S70" s="100">
+        <v>0</v>
+      </c>
     </row>
     <row r="71" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="133" t="s">
@@ -53454,7 +54666,7 @@
       <c r="F71" s="22"/>
       <c r="G71" s="91">
         <f>G70</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H71" s="92">
         <f t="shared" ref="H71:S71" si="8">H70</f>
@@ -53494,7 +54706,7 @@
       </c>
       <c r="Q71" s="94">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R71" s="94">
         <f t="shared" si="8"/>
@@ -53535,20 +54747,40 @@
       <c r="F73" s="19"/>
       <c r="G73" s="74">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H73" s="75"/>
-      <c r="I73" s="76"/>
+        <v>15</v>
+      </c>
+      <c r="H73" s="75">
+        <v>0</v>
+      </c>
+      <c r="I73" s="76">
+        <v>0</v>
+      </c>
       <c r="J73" s="77"/>
       <c r="K73" s="77"/>
-      <c r="L73" s="77"/>
-      <c r="M73" s="77"/>
-      <c r="N73" s="77"/>
-      <c r="O73" s="77"/>
-      <c r="P73" s="77"/>
-      <c r="Q73" s="77"/>
-      <c r="R73" s="77"/>
-      <c r="S73" s="78"/>
+      <c r="L73" s="77">
+        <v>0</v>
+      </c>
+      <c r="M73" s="77">
+        <v>0</v>
+      </c>
+      <c r="N73" s="77">
+        <v>0</v>
+      </c>
+      <c r="O73" s="77">
+        <v>0</v>
+      </c>
+      <c r="P73" s="77">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="77">
+        <v>15</v>
+      </c>
+      <c r="R73" s="77">
+        <v>0</v>
+      </c>
+      <c r="S73" s="78">
+        <v>0</v>
+      </c>
     </row>
     <row r="74" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="26"/>
@@ -53560,20 +54792,36 @@
       <c r="F74" s="19"/>
       <c r="G74" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H74" s="80"/>
-      <c r="I74" s="81"/>
+        <v>12</v>
+      </c>
+      <c r="H74" s="80">
+        <v>0</v>
+      </c>
+      <c r="I74" s="81">
+        <v>0</v>
+      </c>
       <c r="J74" s="82"/>
       <c r="K74" s="82"/>
-      <c r="L74" s="82"/>
-      <c r="M74" s="82"/>
-      <c r="N74" s="82"/>
+      <c r="L74" s="82">
+        <v>0</v>
+      </c>
+      <c r="M74" s="82">
+        <v>0</v>
+      </c>
+      <c r="N74" s="82">
+        <v>0</v>
+      </c>
       <c r="O74" s="82"/>
       <c r="P74" s="82"/>
-      <c r="Q74" s="82"/>
-      <c r="R74" s="82"/>
-      <c r="S74" s="83"/>
+      <c r="Q74" s="82">
+        <v>12</v>
+      </c>
+      <c r="R74" s="82">
+        <v>0</v>
+      </c>
+      <c r="S74" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="75" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="26"/>
@@ -53585,20 +54833,36 @@
       <c r="F75" s="19"/>
       <c r="G75" s="79">
         <f t="shared" ref="G75:G105" si="9">SUM(H75:S75)</f>
-        <v>0</v>
-      </c>
-      <c r="H75" s="80"/>
-      <c r="I75" s="81"/>
+        <v>1083</v>
+      </c>
+      <c r="H75" s="80">
+        <v>0</v>
+      </c>
+      <c r="I75" s="81">
+        <v>0</v>
+      </c>
       <c r="J75" s="82"/>
       <c r="K75" s="82"/>
-      <c r="L75" s="82"/>
-      <c r="M75" s="82"/>
-      <c r="N75" s="82"/>
+      <c r="L75" s="82">
+        <v>0</v>
+      </c>
+      <c r="M75" s="82">
+        <v>1044</v>
+      </c>
+      <c r="N75" s="82">
+        <v>0</v>
+      </c>
       <c r="O75" s="82"/>
       <c r="P75" s="82"/>
-      <c r="Q75" s="82"/>
-      <c r="R75" s="82"/>
-      <c r="S75" s="84"/>
+      <c r="Q75" s="82">
+        <v>39</v>
+      </c>
+      <c r="R75" s="82">
+        <v>0</v>
+      </c>
+      <c r="S75" s="84">
+        <v>0</v>
+      </c>
     </row>
     <row r="76" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="26"/>
@@ -53612,18 +54876,34 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="H76" s="80"/>
-      <c r="I76" s="81"/>
+      <c r="H76" s="80">
+        <v>0</v>
+      </c>
+      <c r="I76" s="81">
+        <v>0</v>
+      </c>
       <c r="J76" s="82"/>
       <c r="K76" s="82"/>
-      <c r="L76" s="82"/>
-      <c r="M76" s="82"/>
-      <c r="N76" s="82"/>
+      <c r="L76" s="82">
+        <v>0</v>
+      </c>
+      <c r="M76" s="82">
+        <v>0</v>
+      </c>
+      <c r="N76" s="82">
+        <v>0</v>
+      </c>
       <c r="O76" s="82"/>
       <c r="P76" s="82"/>
-      <c r="Q76" s="82"/>
-      <c r="R76" s="82"/>
-      <c r="S76" s="85"/>
+      <c r="Q76" s="82">
+        <v>0</v>
+      </c>
+      <c r="R76" s="82">
+        <v>0</v>
+      </c>
+      <c r="S76" s="85">
+        <v>0</v>
+      </c>
     </row>
     <row r="77" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="26"/>
@@ -53635,20 +54915,36 @@
       <c r="F77" s="19"/>
       <c r="G77" s="79">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H77" s="80"/>
-      <c r="I77" s="81"/>
+        <v>11</v>
+      </c>
+      <c r="H77" s="80">
+        <v>0</v>
+      </c>
+      <c r="I77" s="81">
+        <v>0</v>
+      </c>
       <c r="J77" s="82"/>
       <c r="K77" s="82"/>
-      <c r="L77" s="82"/>
-      <c r="M77" s="82"/>
-      <c r="N77" s="82"/>
+      <c r="L77" s="82">
+        <v>0</v>
+      </c>
+      <c r="M77" s="82">
+        <v>0</v>
+      </c>
+      <c r="N77" s="82">
+        <v>0</v>
+      </c>
       <c r="O77" s="82"/>
       <c r="P77" s="82"/>
-      <c r="Q77" s="82"/>
-      <c r="R77" s="82"/>
-      <c r="S77" s="85"/>
+      <c r="Q77" s="82">
+        <v>11</v>
+      </c>
+      <c r="R77" s="82">
+        <v>0</v>
+      </c>
+      <c r="S77" s="85">
+        <v>0</v>
+      </c>
     </row>
     <row r="78" spans="2:19" ht="14.85" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="26"/>
@@ -53685,20 +54981,36 @@
       <c r="F79" s="19"/>
       <c r="G79" s="79">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H79" s="80"/>
-      <c r="I79" s="81"/>
+        <v>3611</v>
+      </c>
+      <c r="H79" s="80">
+        <v>0</v>
+      </c>
+      <c r="I79" s="81">
+        <v>0</v>
+      </c>
       <c r="J79" s="82"/>
       <c r="K79" s="82"/>
-      <c r="L79" s="82"/>
-      <c r="M79" s="82"/>
-      <c r="N79" s="82"/>
+      <c r="L79" s="82">
+        <v>0</v>
+      </c>
+      <c r="M79" s="82">
+        <v>2290</v>
+      </c>
+      <c r="N79" s="82">
+        <v>585</v>
+      </c>
       <c r="O79" s="82"/>
       <c r="P79" s="82"/>
-      <c r="Q79" s="82"/>
-      <c r="R79" s="82"/>
-      <c r="S79" s="85"/>
+      <c r="Q79" s="82">
+        <v>736</v>
+      </c>
+      <c r="R79" s="82">
+        <v>0</v>
+      </c>
+      <c r="S79" s="85">
+        <v>0</v>
+      </c>
     </row>
     <row r="80" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="26"/>
@@ -53710,20 +55022,40 @@
       <c r="F80" s="19"/>
       <c r="G80" s="79">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H80" s="80"/>
-      <c r="I80" s="81"/>
+        <v>127</v>
+      </c>
+      <c r="H80" s="80">
+        <v>0</v>
+      </c>
+      <c r="I80" s="81">
+        <v>0</v>
+      </c>
       <c r="J80" s="82"/>
       <c r="K80" s="82"/>
-      <c r="L80" s="82"/>
-      <c r="M80" s="82"/>
-      <c r="N80" s="82"/>
-      <c r="O80" s="82"/>
-      <c r="P80" s="82"/>
-      <c r="Q80" s="82"/>
-      <c r="R80" s="82"/>
-      <c r="S80" s="85"/>
+      <c r="L80" s="82">
+        <v>0</v>
+      </c>
+      <c r="M80" s="82">
+        <v>0</v>
+      </c>
+      <c r="N80" s="82">
+        <v>0</v>
+      </c>
+      <c r="O80" s="82">
+        <v>127</v>
+      </c>
+      <c r="P80" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="82">
+        <v>0</v>
+      </c>
+      <c r="R80" s="82">
+        <v>0</v>
+      </c>
+      <c r="S80" s="85">
+        <v>0</v>
+      </c>
     </row>
     <row r="81" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="26"/>
@@ -53735,20 +55067,36 @@
       <c r="F81" s="19"/>
       <c r="G81" s="79">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H81" s="80"/>
-      <c r="I81" s="81"/>
+        <v>896</v>
+      </c>
+      <c r="H81" s="80">
+        <v>0</v>
+      </c>
+      <c r="I81" s="81">
+        <v>0</v>
+      </c>
       <c r="J81" s="82"/>
       <c r="K81" s="82"/>
-      <c r="L81" s="82"/>
-      <c r="M81" s="82"/>
-      <c r="N81" s="82"/>
+      <c r="L81" s="82">
+        <v>0</v>
+      </c>
+      <c r="M81" s="82">
+        <v>0</v>
+      </c>
+      <c r="N81" s="82">
+        <v>0</v>
+      </c>
       <c r="O81" s="82"/>
       <c r="P81" s="82"/>
-      <c r="Q81" s="82"/>
-      <c r="R81" s="82"/>
-      <c r="S81" s="85"/>
+      <c r="Q81" s="82">
+        <v>896</v>
+      </c>
+      <c r="R81" s="82">
+        <v>0</v>
+      </c>
+      <c r="S81" s="85">
+        <v>0</v>
+      </c>
     </row>
     <row r="82" spans="2:19" ht="14.85" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="26"/>
@@ -53787,18 +55135,42 @@
         <f t="shared" ref="G83" si="10">SUM(H83:S83)</f>
         <v>0</v>
       </c>
-      <c r="H83" s="80"/>
-      <c r="I83" s="81"/>
-      <c r="J83" s="82"/>
-      <c r="K83" s="82"/>
-      <c r="L83" s="82"/>
-      <c r="M83" s="82"/>
-      <c r="N83" s="82"/>
-      <c r="O83" s="82"/>
-      <c r="P83" s="82"/>
-      <c r="Q83" s="82"/>
-      <c r="R83" s="82"/>
-      <c r="S83" s="85"/>
+      <c r="H83" s="80">
+        <v>0</v>
+      </c>
+      <c r="I83" s="81">
+        <v>0</v>
+      </c>
+      <c r="J83" s="82">
+        <v>0</v>
+      </c>
+      <c r="K83" s="82">
+        <v>0</v>
+      </c>
+      <c r="L83" s="82">
+        <v>0</v>
+      </c>
+      <c r="M83" s="82">
+        <v>0</v>
+      </c>
+      <c r="N83" s="82">
+        <v>0</v>
+      </c>
+      <c r="O83" s="82">
+        <v>0</v>
+      </c>
+      <c r="P83" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="82">
+        <v>0</v>
+      </c>
+      <c r="R83" s="82">
+        <v>0</v>
+      </c>
+      <c r="S83" s="85">
+        <v>0</v>
+      </c>
     </row>
     <row r="84" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="26"/>
@@ -53812,18 +55184,34 @@
         <f>SUM(H84:S84)</f>
         <v>0</v>
       </c>
-      <c r="H84" s="80"/>
-      <c r="I84" s="81"/>
+      <c r="H84" s="80">
+        <v>0</v>
+      </c>
+      <c r="I84" s="81">
+        <v>0</v>
+      </c>
       <c r="J84" s="82"/>
       <c r="K84" s="82"/>
-      <c r="L84" s="82"/>
-      <c r="M84" s="82"/>
-      <c r="N84" s="82"/>
+      <c r="L84" s="82">
+        <v>0</v>
+      </c>
+      <c r="M84" s="82">
+        <v>0</v>
+      </c>
+      <c r="N84" s="82">
+        <v>0</v>
+      </c>
       <c r="O84" s="82"/>
       <c r="P84" s="82"/>
-      <c r="Q84" s="82"/>
-      <c r="R84" s="82"/>
-      <c r="S84" s="85"/>
+      <c r="Q84" s="82">
+        <v>0</v>
+      </c>
+      <c r="R84" s="82">
+        <v>0</v>
+      </c>
+      <c r="S84" s="85">
+        <v>0</v>
+      </c>
     </row>
     <row r="85" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="26"/>
@@ -53837,18 +55225,34 @@
         <f t="shared" ref="G85" si="11">SUM(H85:S85)</f>
         <v>0</v>
       </c>
-      <c r="H85" s="80"/>
-      <c r="I85" s="81"/>
+      <c r="H85" s="80">
+        <v>0</v>
+      </c>
+      <c r="I85" s="81">
+        <v>0</v>
+      </c>
       <c r="J85" s="82"/>
       <c r="K85" s="82"/>
-      <c r="L85" s="82"/>
-      <c r="M85" s="82"/>
-      <c r="N85" s="82"/>
+      <c r="L85" s="82">
+        <v>0</v>
+      </c>
+      <c r="M85" s="82">
+        <v>0</v>
+      </c>
+      <c r="N85" s="82">
+        <v>0</v>
+      </c>
       <c r="O85" s="82"/>
       <c r="P85" s="82"/>
-      <c r="Q85" s="82"/>
-      <c r="R85" s="82"/>
-      <c r="S85" s="83"/>
+      <c r="Q85" s="82">
+        <v>0</v>
+      </c>
+      <c r="R85" s="82">
+        <v>0</v>
+      </c>
+      <c r="S85" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="86" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="26"/>
@@ -53860,20 +55264,44 @@
       <c r="F86" s="19"/>
       <c r="G86" s="79">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H86" s="80"/>
-      <c r="I86" s="81"/>
-      <c r="J86" s="82"/>
-      <c r="K86" s="82"/>
-      <c r="L86" s="82"/>
-      <c r="M86" s="82"/>
-      <c r="N86" s="82"/>
-      <c r="O86" s="82"/>
-      <c r="P86" s="82"/>
-      <c r="Q86" s="82"/>
-      <c r="R86" s="82"/>
-      <c r="S86" s="83"/>
+        <v>1065</v>
+      </c>
+      <c r="H86" s="80">
+        <v>0</v>
+      </c>
+      <c r="I86" s="81">
+        <v>0</v>
+      </c>
+      <c r="J86" s="82">
+        <v>0</v>
+      </c>
+      <c r="K86" s="82">
+        <v>0</v>
+      </c>
+      <c r="L86" s="82">
+        <v>0</v>
+      </c>
+      <c r="M86" s="82">
+        <v>574</v>
+      </c>
+      <c r="N86" s="82">
+        <v>0</v>
+      </c>
+      <c r="O86" s="82">
+        <v>139</v>
+      </c>
+      <c r="P86" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="82">
+        <v>352</v>
+      </c>
+      <c r="R86" s="82">
+        <v>0</v>
+      </c>
+      <c r="S86" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="87" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="26"/>
@@ -53885,20 +55313,44 @@
       <c r="F87" s="19"/>
       <c r="G87" s="79">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H87" s="80"/>
-      <c r="I87" s="81"/>
-      <c r="J87" s="82"/>
-      <c r="K87" s="82"/>
-      <c r="L87" s="82"/>
-      <c r="M87" s="82"/>
-      <c r="N87" s="82"/>
-      <c r="O87" s="82"/>
-      <c r="P87" s="82"/>
-      <c r="Q87" s="82"/>
-      <c r="R87" s="82"/>
-      <c r="S87" s="83"/>
+        <v>141</v>
+      </c>
+      <c r="H87" s="80">
+        <v>0</v>
+      </c>
+      <c r="I87" s="81">
+        <v>0</v>
+      </c>
+      <c r="J87" s="82">
+        <v>0</v>
+      </c>
+      <c r="K87" s="82">
+        <v>0</v>
+      </c>
+      <c r="L87" s="82">
+        <v>0</v>
+      </c>
+      <c r="M87" s="82">
+        <v>100</v>
+      </c>
+      <c r="N87" s="82">
+        <v>0</v>
+      </c>
+      <c r="O87" s="82">
+        <v>2</v>
+      </c>
+      <c r="P87" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="82">
+        <v>39</v>
+      </c>
+      <c r="R87" s="82">
+        <v>0</v>
+      </c>
+      <c r="S87" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="88" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="26"/>
@@ -53910,20 +55362,36 @@
       <c r="F88" s="19"/>
       <c r="G88" s="79">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H88" s="80"/>
-      <c r="I88" s="81"/>
+        <v>449</v>
+      </c>
+      <c r="H88" s="80">
+        <v>0</v>
+      </c>
+      <c r="I88" s="81">
+        <v>0</v>
+      </c>
       <c r="J88" s="82"/>
       <c r="K88" s="82"/>
-      <c r="L88" s="82"/>
-      <c r="M88" s="82"/>
-      <c r="N88" s="82"/>
+      <c r="L88" s="82">
+        <v>0</v>
+      </c>
+      <c r="M88" s="82">
+        <v>0</v>
+      </c>
+      <c r="N88" s="82">
+        <v>0</v>
+      </c>
       <c r="O88" s="82"/>
       <c r="P88" s="82"/>
-      <c r="Q88" s="82"/>
-      <c r="R88" s="82"/>
-      <c r="S88" s="83"/>
+      <c r="Q88" s="82">
+        <v>449</v>
+      </c>
+      <c r="R88" s="82">
+        <v>0</v>
+      </c>
+      <c r="S88" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="89" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="26"/>
@@ -53935,20 +55403,44 @@
       <c r="F89" s="19"/>
       <c r="G89" s="79">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H89" s="80"/>
-      <c r="I89" s="81"/>
-      <c r="J89" s="82"/>
-      <c r="K89" s="82"/>
-      <c r="L89" s="82"/>
-      <c r="M89" s="82"/>
-      <c r="N89" s="82"/>
-      <c r="O89" s="82"/>
-      <c r="P89" s="82"/>
-      <c r="Q89" s="82"/>
-      <c r="R89" s="82"/>
-      <c r="S89" s="83"/>
+        <v>395</v>
+      </c>
+      <c r="H89" s="80">
+        <v>0</v>
+      </c>
+      <c r="I89" s="81">
+        <v>0</v>
+      </c>
+      <c r="J89" s="82">
+        <v>0</v>
+      </c>
+      <c r="K89" s="82">
+        <v>0</v>
+      </c>
+      <c r="L89" s="82">
+        <v>0</v>
+      </c>
+      <c r="M89" s="82">
+        <v>0</v>
+      </c>
+      <c r="N89" s="82">
+        <v>0</v>
+      </c>
+      <c r="O89" s="82">
+        <v>0</v>
+      </c>
+      <c r="P89" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="82">
+        <v>395</v>
+      </c>
+      <c r="R89" s="82">
+        <v>0</v>
+      </c>
+      <c r="S89" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="90" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="57"/>
@@ -53962,18 +55454,38 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="H90" s="80"/>
-      <c r="I90" s="81"/>
+      <c r="H90" s="80">
+        <v>0</v>
+      </c>
+      <c r="I90" s="81">
+        <v>0</v>
+      </c>
       <c r="J90" s="82"/>
       <c r="K90" s="82"/>
-      <c r="L90" s="82"/>
-      <c r="M90" s="82"/>
-      <c r="N90" s="82"/>
-      <c r="O90" s="82"/>
-      <c r="P90" s="82"/>
-      <c r="Q90" s="82"/>
-      <c r="R90" s="82"/>
-      <c r="S90" s="83"/>
+      <c r="L90" s="82">
+        <v>0</v>
+      </c>
+      <c r="M90" s="82">
+        <v>0</v>
+      </c>
+      <c r="N90" s="82">
+        <v>0</v>
+      </c>
+      <c r="O90" s="82">
+        <v>0</v>
+      </c>
+      <c r="P90" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="82">
+        <v>0</v>
+      </c>
+      <c r="R90" s="82">
+        <v>0</v>
+      </c>
+      <c r="S90" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="91" spans="2:19" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="57"/>
@@ -53985,20 +55497,36 @@
       <c r="F91" s="19"/>
       <c r="G91" s="86">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H91" s="87"/>
-      <c r="I91" s="88"/>
+        <v>1456</v>
+      </c>
+      <c r="H91" s="87">
+        <v>0</v>
+      </c>
+      <c r="I91" s="88">
+        <v>0</v>
+      </c>
       <c r="J91" s="89"/>
       <c r="K91" s="89"/>
-      <c r="L91" s="89"/>
-      <c r="M91" s="89"/>
-      <c r="N91" s="89"/>
+      <c r="L91" s="89">
+        <v>0</v>
+      </c>
+      <c r="M91" s="89">
+        <v>0</v>
+      </c>
+      <c r="N91" s="89">
+        <v>400</v>
+      </c>
       <c r="O91" s="89"/>
       <c r="P91" s="89"/>
-      <c r="Q91" s="89"/>
-      <c r="R91" s="89"/>
-      <c r="S91" s="90"/>
+      <c r="Q91" s="89">
+        <v>1056</v>
+      </c>
+      <c r="R91" s="89">
+        <v>0</v>
+      </c>
+      <c r="S91" s="90">
+        <v>0</v>
+      </c>
     </row>
     <row r="92" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="133" t="s">
@@ -54010,7 +55538,7 @@
       <c r="F92" s="22"/>
       <c r="G92" s="102">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>9261</v>
       </c>
       <c r="H92" s="103">
         <f t="shared" ref="H92:S92" si="12">SUM(H73:H91)</f>
@@ -54034,15 +55562,15 @@
       </c>
       <c r="M92" s="105">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>4008</v>
       </c>
       <c r="N92" s="105">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>985</v>
       </c>
       <c r="O92" s="105">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="P92" s="105">
         <f t="shared" si="12"/>
@@ -54050,7 +55578,7 @@
       </c>
       <c r="Q92" s="105">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="R92" s="105">
         <f t="shared" si="12"/>
@@ -54091,20 +55619,40 @@
       <c r="F94" s="19"/>
       <c r="G94" s="74">
         <f t="shared" ref="G94" si="13">SUM(H94:S94)</f>
-        <v>0</v>
-      </c>
-      <c r="H94" s="75"/>
-      <c r="I94" s="76"/>
+        <v>600</v>
+      </c>
+      <c r="H94" s="75">
+        <v>0</v>
+      </c>
+      <c r="I94" s="76">
+        <v>0</v>
+      </c>
       <c r="J94" s="77"/>
       <c r="K94" s="77"/>
-      <c r="L94" s="77"/>
-      <c r="M94" s="77"/>
-      <c r="N94" s="77"/>
-      <c r="O94" s="77"/>
-      <c r="P94" s="77"/>
-      <c r="Q94" s="77"/>
-      <c r="R94" s="77"/>
-      <c r="S94" s="78"/>
+      <c r="L94" s="77">
+        <v>0</v>
+      </c>
+      <c r="M94" s="77">
+        <v>600</v>
+      </c>
+      <c r="N94" s="77">
+        <v>0</v>
+      </c>
+      <c r="O94" s="77">
+        <v>0</v>
+      </c>
+      <c r="P94" s="77">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="77">
+        <v>0</v>
+      </c>
+      <c r="R94" s="77">
+        <v>0</v>
+      </c>
+      <c r="S94" s="78">
+        <v>0</v>
+      </c>
     </row>
     <row r="95" spans="2:19" s="21" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="26"/>
@@ -54116,20 +55664,40 @@
       <c r="F95" s="19"/>
       <c r="G95" s="79">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H95" s="80"/>
-      <c r="I95" s="81"/>
+        <v>110</v>
+      </c>
+      <c r="H95" s="80">
+        <v>0</v>
+      </c>
+      <c r="I95" s="81">
+        <v>0</v>
+      </c>
       <c r="J95" s="82"/>
       <c r="K95" s="82"/>
-      <c r="L95" s="82"/>
-      <c r="M95" s="82"/>
-      <c r="N95" s="82"/>
-      <c r="O95" s="82"/>
-      <c r="P95" s="82"/>
-      <c r="Q95" s="82"/>
-      <c r="R95" s="82"/>
-      <c r="S95" s="83"/>
+      <c r="L95" s="82">
+        <v>0</v>
+      </c>
+      <c r="M95" s="82">
+        <v>80</v>
+      </c>
+      <c r="N95" s="82">
+        <v>6</v>
+      </c>
+      <c r="O95" s="82">
+        <v>0</v>
+      </c>
+      <c r="P95" s="82">
+        <v>19</v>
+      </c>
+      <c r="Q95" s="82">
+        <v>5</v>
+      </c>
+      <c r="R95" s="82">
+        <v>0</v>
+      </c>
+      <c r="S95" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="96" spans="2:19" s="21" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="26"/>
@@ -54141,20 +55709,44 @@
       <c r="F96" s="19"/>
       <c r="G96" s="79">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H96" s="80"/>
-      <c r="I96" s="81"/>
-      <c r="J96" s="82"/>
-      <c r="K96" s="82"/>
-      <c r="L96" s="82"/>
-      <c r="M96" s="82"/>
-      <c r="N96" s="82"/>
-      <c r="O96" s="82"/>
-      <c r="P96" s="82"/>
-      <c r="Q96" s="82"/>
-      <c r="R96" s="82"/>
-      <c r="S96" s="83"/>
+        <v>131</v>
+      </c>
+      <c r="H96" s="80">
+        <v>81</v>
+      </c>
+      <c r="I96" s="81">
+        <v>0</v>
+      </c>
+      <c r="J96" s="82">
+        <v>0</v>
+      </c>
+      <c r="K96" s="82">
+        <v>0</v>
+      </c>
+      <c r="L96" s="82">
+        <v>0</v>
+      </c>
+      <c r="M96" s="82">
+        <v>0</v>
+      </c>
+      <c r="N96" s="82">
+        <v>0</v>
+      </c>
+      <c r="O96" s="82">
+        <v>0</v>
+      </c>
+      <c r="P96" s="82">
+        <v>50</v>
+      </c>
+      <c r="Q96" s="82">
+        <v>0</v>
+      </c>
+      <c r="R96" s="82">
+        <v>0</v>
+      </c>
+      <c r="S96" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="97" spans="2:19" s="21" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="26"/>
@@ -54168,18 +55760,38 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="H97" s="80"/>
-      <c r="I97" s="81"/>
+      <c r="H97" s="80">
+        <v>0</v>
+      </c>
+      <c r="I97" s="81">
+        <v>0</v>
+      </c>
       <c r="J97" s="82"/>
       <c r="K97" s="82"/>
-      <c r="L97" s="82"/>
-      <c r="M97" s="82"/>
-      <c r="N97" s="82"/>
-      <c r="O97" s="82"/>
-      <c r="P97" s="82"/>
-      <c r="Q97" s="82"/>
-      <c r="R97" s="82"/>
-      <c r="S97" s="83"/>
+      <c r="L97" s="82">
+        <v>0</v>
+      </c>
+      <c r="M97" s="82">
+        <v>0</v>
+      </c>
+      <c r="N97" s="82">
+        <v>0</v>
+      </c>
+      <c r="O97" s="82">
+        <v>0</v>
+      </c>
+      <c r="P97" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="82">
+        <v>0</v>
+      </c>
+      <c r="R97" s="82">
+        <v>0</v>
+      </c>
+      <c r="S97" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="98" spans="2:19" s="21" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="26"/>
@@ -54193,18 +55805,38 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="H98" s="80"/>
-      <c r="I98" s="81"/>
+      <c r="H98" s="80">
+        <v>0</v>
+      </c>
+      <c r="I98" s="81">
+        <v>0</v>
+      </c>
       <c r="J98" s="82"/>
       <c r="K98" s="82"/>
-      <c r="L98" s="82"/>
-      <c r="M98" s="82"/>
-      <c r="N98" s="82"/>
-      <c r="O98" s="82"/>
-      <c r="P98" s="82"/>
-      <c r="Q98" s="82"/>
-      <c r="R98" s="82"/>
-      <c r="S98" s="83"/>
+      <c r="L98" s="82">
+        <v>0</v>
+      </c>
+      <c r="M98" s="82">
+        <v>0</v>
+      </c>
+      <c r="N98" s="82">
+        <v>0</v>
+      </c>
+      <c r="O98" s="82">
+        <v>0</v>
+      </c>
+      <c r="P98" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="82">
+        <v>0</v>
+      </c>
+      <c r="R98" s="82">
+        <v>0</v>
+      </c>
+      <c r="S98" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="99" spans="2:19" s="21" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="26"/>
@@ -54218,18 +55850,38 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="H99" s="80"/>
-      <c r="I99" s="81"/>
+      <c r="H99" s="80">
+        <v>0</v>
+      </c>
+      <c r="I99" s="81">
+        <v>0</v>
+      </c>
       <c r="J99" s="82"/>
       <c r="K99" s="82"/>
-      <c r="L99" s="82"/>
-      <c r="M99" s="82"/>
-      <c r="N99" s="82"/>
-      <c r="O99" s="82"/>
-      <c r="P99" s="82"/>
-      <c r="Q99" s="82"/>
-      <c r="R99" s="82"/>
-      <c r="S99" s="83"/>
+      <c r="L99" s="82">
+        <v>0</v>
+      </c>
+      <c r="M99" s="82">
+        <v>0</v>
+      </c>
+      <c r="N99" s="82">
+        <v>0</v>
+      </c>
+      <c r="O99" s="82">
+        <v>0</v>
+      </c>
+      <c r="P99" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="82">
+        <v>0</v>
+      </c>
+      <c r="R99" s="82">
+        <v>0</v>
+      </c>
+      <c r="S99" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="100" spans="2:19" s="21" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="26"/>
@@ -54241,20 +55893,40 @@
       <c r="F100" s="19"/>
       <c r="G100" s="79">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H100" s="80"/>
-      <c r="I100" s="81"/>
+        <v>1</v>
+      </c>
+      <c r="H100" s="80">
+        <v>0</v>
+      </c>
+      <c r="I100" s="81">
+        <v>0</v>
+      </c>
       <c r="J100" s="82"/>
       <c r="K100" s="82"/>
-      <c r="L100" s="82"/>
-      <c r="M100" s="82"/>
-      <c r="N100" s="82"/>
-      <c r="O100" s="82"/>
-      <c r="P100" s="82"/>
-      <c r="Q100" s="82"/>
-      <c r="R100" s="82"/>
-      <c r="S100" s="83"/>
+      <c r="L100" s="82">
+        <v>0</v>
+      </c>
+      <c r="M100" s="82">
+        <v>0</v>
+      </c>
+      <c r="N100" s="82">
+        <v>0</v>
+      </c>
+      <c r="O100" s="82">
+        <v>0</v>
+      </c>
+      <c r="P100" s="82">
+        <v>1</v>
+      </c>
+      <c r="Q100" s="82">
+        <v>0</v>
+      </c>
+      <c r="R100" s="82">
+        <v>0</v>
+      </c>
+      <c r="S100" s="83">
+        <v>0</v>
+      </c>
     </row>
     <row r="101" spans="2:19" s="21" customFormat="1" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="26"/>
@@ -54268,18 +55940,38 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="H101" s="87"/>
-      <c r="I101" s="88"/>
+      <c r="H101" s="87">
+        <v>0</v>
+      </c>
+      <c r="I101" s="88">
+        <v>0</v>
+      </c>
       <c r="J101" s="89"/>
       <c r="K101" s="89"/>
-      <c r="L101" s="89"/>
-      <c r="M101" s="89"/>
-      <c r="N101" s="89"/>
-      <c r="O101" s="89"/>
-      <c r="P101" s="89"/>
-      <c r="Q101" s="89"/>
-      <c r="R101" s="89"/>
-      <c r="S101" s="90"/>
+      <c r="L101" s="89">
+        <v>0</v>
+      </c>
+      <c r="M101" s="89">
+        <v>0</v>
+      </c>
+      <c r="N101" s="89">
+        <v>0</v>
+      </c>
+      <c r="O101" s="89">
+        <v>0</v>
+      </c>
+      <c r="P101" s="89">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="89">
+        <v>0</v>
+      </c>
+      <c r="R101" s="89">
+        <v>0</v>
+      </c>
+      <c r="S101" s="90">
+        <v>0</v>
+      </c>
     </row>
     <row r="102" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="133" t="s">
@@ -54291,11 +55983,11 @@
       <c r="F102" s="22"/>
       <c r="G102" s="91">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>842</v>
       </c>
       <c r="H102" s="92">
         <f>SUM(H94:H101)</f>
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="I102" s="93">
         <f t="shared" ref="I102:S102" si="14">SUM(I94:I101)</f>
@@ -54315,11 +56007,11 @@
       </c>
       <c r="M102" s="94">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>680</v>
       </c>
       <c r="N102" s="94">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O102" s="94">
         <f t="shared" si="14"/>
@@ -54327,11 +56019,11 @@
       </c>
       <c r="P102" s="94">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Q102" s="94">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R102" s="94">
         <f t="shared" si="14"/>
@@ -54372,55 +56064,55 @@
       <c r="F104" s="22"/>
       <c r="G104" s="112">
         <f>SUM(H104:S104)</f>
-        <v>0</v>
+        <v>285827</v>
       </c>
       <c r="H104" s="113">
         <f t="shared" ref="H104:S104" si="15">SUM(H31,H43,H46,H102,H48,H37,H60,H69,H71,H92)</f>
-        <v>0</v>
+        <v>54685</v>
       </c>
       <c r="I104" s="114">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>75857</v>
       </c>
       <c r="J104" s="115">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>8642</v>
       </c>
       <c r="K104" s="115">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>9307</v>
       </c>
       <c r="L104" s="115">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>50005</v>
       </c>
       <c r="M104" s="115">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>8529</v>
       </c>
       <c r="N104" s="115">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>15098</v>
       </c>
       <c r="O104" s="115">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>11219</v>
       </c>
       <c r="P104" s="115">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>4851</v>
       </c>
       <c r="Q104" s="115">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>14432</v>
       </c>
       <c r="R104" s="115">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>26682</v>
       </c>
       <c r="S104" s="116">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>6520</v>
       </c>
     </row>
     <row r="105" spans="2:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -54433,19 +56125,19 @@
       <c r="F105" s="22"/>
       <c r="G105" s="117">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>41139</v>
       </c>
       <c r="H105" s="118">
         <f>H8+H17+H18+H19+H20+H21+H22+H28+H30+H38+H39+H35+H36+H59+H62+H66+H70+H84+H85</f>
-        <v>0</v>
+        <v>13366</v>
       </c>
       <c r="I105" s="119">
         <f t="shared" ref="I105:S105" si="16">I8+I17+I18+I19+I20+I21+I22+I28+I30+I38+I39+I35+I36+I59+I62+I66+I70+I84+I85</f>
-        <v>0</v>
+        <v>2665</v>
       </c>
       <c r="J105" s="120">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1346</v>
       </c>
       <c r="K105" s="120">
         <f t="shared" si="16"/>
@@ -54453,35 +56145,35 @@
       </c>
       <c r="L105" s="120">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>19862</v>
       </c>
       <c r="M105" s="120">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>586</v>
       </c>
       <c r="N105" s="120">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="O105" s="120">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="P105" s="120">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="Q105" s="120">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1839</v>
       </c>
       <c r="R105" s="120">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>735</v>
       </c>
       <c r="S105" s="121">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="106" spans="2:19" ht="12.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -57866,6 +59558,30 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c0055658-978e-43b2-bfc9-eec157efd867" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db2d40b4-43c9-4295-8ebe-2cc6781de69d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x01010013D85B5B5653F2489CAAE3B6EC418735" ma:contentTypeVersion="19" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="b46cb40b7748bd8198cd2f3c88b660a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db2d40b4-43c9-4295-8ebe-2cc6781de69d" xmlns:ns3="c0055658-978e-43b2-bfc9-eec157efd867" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc595684c71e73e84ea90b99cd4b0e7e" ns2:_="" ns3:_="">
     <xsd:import namespace="db2d40b4-43c9-4295-8ebe-2cc6781de69d"/>
@@ -58126,31 +59842,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FA5A342-8028-49C9-A3CD-4B93C1D46C10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0211B702-3400-4B75-ADC0-DB74BCE777EC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c0055658-978e-43b2-bfc9-eec157efd867" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db2d40b4-43c9-4295-8ebe-2cc6781de69d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D521027-6D44-4439-B955-86C9A00FC71C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="c0055658-978e-43b2-bfc9-eec157efd867"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="db2d40b4-43c9-4295-8ebe-2cc6781de69d"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A6164D9-D4D7-4B6D-B8D0-658DD6EB7130}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -58167,37 +59892,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FA5A342-8028-49C9-A3CD-4B93C1D46C10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0211B702-3400-4B75-ADC0-DB74BCE777EC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D521027-6D44-4439-B955-86C9A00FC71C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="c0055658-978e-43b2-bfc9-eec157efd867"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="db2d40b4-43c9-4295-8ebe-2cc6781de69d"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>